--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -41,32 +41,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -137,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -152,25 +140,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -786,20 +771,20 @@
       <c r="C4" s="3" t="n">
         <v>351.3</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="10" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="10" t="n">
         <v>22.7</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="10" t="n">
         <v>28.1</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="10" t="n">
         <v>10.8</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>21</v>
+        <v>6.6</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>2.6</v>
@@ -835,10 +820,10 @@
         <v>28.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>156.1</v>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v>22</v>
+        <v>56.1</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>22.9</v>
       </c>
       <c r="V4" s="3" t="n">
         <v>28.6</v>
@@ -850,7 +835,7 @@
         <v>29.1</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>74.3</v>
+        <v>142.3</v>
       </c>
       <c r="Z4" s="3" t="n">
         <v>2.1</v>
@@ -871,16 +856,16 @@
       <c r="C5" s="3" t="n">
         <v>278.1</v>
       </c>
-      <c r="D5" s="9" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E5" s="9" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F5" s="9" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="G5" s="9" t="n">
+      <c r="D5" s="10" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G5" s="3" t="n">
         <v>10.3</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -893,13 +878,13 @@
         <v>3.1</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>1.9</v>
+        <v>19.1</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>20.4</v>
+        <v>21.4</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>25.4</v>
@@ -908,22 +893,22 @@
         <v>92</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="Q5" s="3" t="n">
         <v>26</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="S5" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>7.4</v>
+        <v>0.4</v>
       </c>
       <c r="V5" s="3" t="n">
         <v>22</v>
@@ -938,7 +923,7 @@
         <v>92</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>2.1</v>
+        <v>9.4</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -956,16 +941,16 @@
       <c r="C6" s="3" t="n">
         <v>368</v>
       </c>
-      <c r="D6" s="9" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="G6" s="9" t="n">
+      <c r="D6" s="10" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="G6" s="10" t="n">
         <v>10.3</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -978,7 +963,7 @@
         <v>3.5</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>21.6</v>
@@ -990,7 +975,7 @@
         <v>25.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>98.8</v>
+        <v>988.5</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0.7</v>
@@ -1002,7 +987,7 @@
         <v>24.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>27.3</v>
+        <v>22.3</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>59.6</v>
@@ -1016,14 +1001,14 @@
       <c r="W6" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="X6" s="3" t="n">
-        <v>29</v>
+      <c r="X6" s="12" t="n">
+        <v>92</v>
       </c>
       <c r="Y6" s="3" t="n">
         <v>75.40000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1041,74 +1026,74 @@
       <c r="C7" s="3" t="n">
         <v>418.2</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="10" t="n">
         <v>32.4</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="10" t="n">
         <v>26.7</v>
       </c>
-      <c r="G7" s="9" t="n">
-        <v>11.4</v>
+      <c r="G7" s="10" t="n">
+        <v>11.5</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>19.4</v>
+        <v>20.6</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J7" s="8" t="n">
-        <v>2.1</v>
+        <v>34.5</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>5.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>21.1</v>
+        <v>22.1</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>20.9</v>
+        <v>21.7</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>24.6</v>
+        <v>25.7</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>96.5</v>
+        <v>6.5</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q7" s="8" t="n">
-        <v>11.9</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>33.3</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="S7" s="3" t="n">
-        <v>28</v>
+        <v>25.6</v>
+      </c>
+      <c r="S7" s="12" t="n">
+        <v>72.90000000000001</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>59.5</v>
+        <v>54.8</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>19.1</v>
+        <v>23</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>28.7</v>
+        <v>28.1</v>
       </c>
       <c r="W7" s="3" t="n">
-        <v>24.8</v>
+        <v>24.4</v>
       </c>
       <c r="X7" s="3" t="n">
-        <v>28.8</v>
+        <v>28.4</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>73.2</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1126,74 +1111,74 @@
       <c r="C8" s="3" t="n">
         <v>368</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="10" t="n">
         <v>33.3</v>
       </c>
-      <c r="E8" s="9" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>11.5</v>
+      <c r="E8" s="11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>34.45</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>54.3</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>20.6</v>
+        <v>60.8</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>8.5</v>
+        <v>12</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>5.8</v>
+        <v>20.9</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>22.1</v>
+        <v>2</v>
+      </c>
+      <c r="L8" s="12" t="n">
+        <v>9.4</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>21.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>25.7</v>
+        <v>28.2</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>812.1</v>
+        <v>870.6</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>33.3</v>
+        <v>344.6</v>
       </c>
       <c r="R8" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="S8" s="3" t="n">
-        <v>27.9</v>
+        <v>24.4</v>
+      </c>
+      <c r="S8" s="12" t="n">
+        <v>57.8</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>54.8</v>
+        <v>308</v>
       </c>
       <c r="U8" s="3" t="n">
-        <v>23</v>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v>28.1</v>
+        <v>96.09999999999999</v>
+      </c>
+      <c r="V8" s="12" t="n">
+        <v>35.2</v>
       </c>
       <c r="W8" s="3" t="n">
-        <v>24.4</v>
+        <v>20</v>
       </c>
       <c r="X8" s="3" t="n">
-        <v>28.2</v>
+        <v>39.5</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>74.2</v>
+        <v>389.1</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>41.8</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1211,77 +1196,77 @@
       <c r="C9" s="3" t="n">
         <v>1783.6</v>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>161.7</v>
+      <c r="D9" s="10" t="n">
+        <v>32.3</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>1.4</v>
+        <v>21.5</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>54.3</v>
+        <v>26.9</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>10.8</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>1.8</v>
+        <v>26.4</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>20.9</v>
+        <v>4.2</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>2</v>
+        <v>7.4</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>109.4</v>
+        <v>21.9</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>2.2</v>
+        <v>21.6</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0.3</v>
+        <v>25.6</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>97.40000000000001</v>
-      </c>
-      <c r="P9" s="3" t="n">
-        <v>3.1</v>
+        <v>927.4</v>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 066
+</t>
+        </is>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>155.6</v>
+        <v>344.6</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>44.4</v>
+        <v>24.9</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="T9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">308 10
-</t>
-        </is>
+        <v>4.5</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>61.6</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>90.09999999999999</v>
+        <v>12</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>135.7</v>
+        <v>2.1</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>80.09999999999999</v>
+        <v>24</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>29.5</v>
+        <v>272.9</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>389.1</v>
+        <v>22.8</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>41.8</v>
+        <v>8.4</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1299,72 +1284,74 @@
       <c r="C10" s="3" t="n">
         <v>356.7</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="10" t="n">
         <v>32.3</v>
       </c>
-      <c r="E10" s="9" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>10.8</v>
+      <c r="E10" s="10" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>13.4</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>20.2</v>
+        <v>18.7</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>2.4</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K10" s="3" t="n"/>
+        <v>0.7</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
       <c r="L10" s="3" t="n">
-        <v>21.9</v>
+        <v>20.6</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>21.6</v>
+        <v>22.5</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>25.6</v>
+        <v>24</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>1.1</v>
+        <v>29</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.6</v>
+        <v>6.2</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>31.1</v>
+        <v>33.2</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>24.9</v>
+        <v>25.8</v>
       </c>
       <c r="S10" s="3" t="n">
-        <v>27.5</v>
+        <v>28.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>18</v>
+        <v>563.5</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>0.8</v>
       </c>
       <c r="V10" s="3" t="n">
-        <v>27.1</v>
+        <v>29.5</v>
       </c>
       <c r="W10" s="3" t="n">
-        <v>24</v>
+        <v>25.1</v>
       </c>
       <c r="X10" s="3" t="n">
-        <v>27.9</v>
+        <v>29</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>77.8</v>
+        <v>9.4</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>8.4</v>
+        <v>2.2</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1380,76 +1367,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>420.3</v>
-      </c>
-      <c r="D11" s="9" t="n">
-        <v>33.13</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="G11" s="9" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>88.7</v>
+        <v>426.3</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>4.1</v>
+        <v>0.4</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>20.5</v>
+        <v>20.1</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>24.8</v>
+        <v>23.3</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q11" s="8" t="n">
-        <v>933.2</v>
+        <v>0.7</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>32.8</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>56.3</v>
+        <v>58</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v>29.5</v>
+        <v>20.8</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>29.6</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>25.1</v>
+        <v>25.6</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>29</v>
+        <v>30.3</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>10.4</v>
+        <v>3.2</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1467,74 +1454,74 @@
       <c r="C12" s="3" t="n">
         <v>418.2</v>
       </c>
-      <c r="D12" s="9" t="n">
-        <v>32.8</v>
-      </c>
-      <c r="E12" s="9" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>12.6</v>
+      <c r="D12" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>18.6</v>
+        <v>19.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>4.8</v>
+        <v>11.6</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>20.4</v>
+        <v>21.3</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="N12" s="8" t="n">
-        <v>23.3</v>
+        <v>21</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>24.7</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>210.4</v>
+        <v>97</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0.7</v>
+        <v>67.2</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>32.8</v>
+        <v>29.1</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>25.8</v>
+        <v>24.3</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>28.7</v>
+        <v>27.3</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>158</v>
+        <v>62.9</v>
       </c>
       <c r="U12" s="3" t="n">
-        <v>20.8</v>
+        <v>13</v>
       </c>
       <c r="V12" s="3" t="n">
-        <v>29.6</v>
+        <v>26.4</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="X12" s="3" t="n">
-        <v>30.3</v>
+        <v>23.8</v>
+      </c>
+      <c r="X12" s="12" t="n">
+        <v>72.8</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>73.2</v>
+        <v>80.8</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>11.1</v>
+        <v>6.6</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1550,76 +1537,76 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="D13" s="9" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>8.300000000000001</v>
+        <v>2362.1</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>29.25</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>8.1</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>19.6</v>
+        <v>17.8</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>11.6</v>
+        <v>0</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="M13" s="3" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>97</v>
+        <v>998</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="Q13" s="3" t="n">
-        <v>29.1</v>
+        <v>8.4</v>
+      </c>
+      <c r="Q13" s="12" t="n">
+        <v>72.3</v>
       </c>
       <c r="R13" s="3" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="S13" s="3" t="n">
-        <v>27.3</v>
+        <v>28.2</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>67.90000000000001</v>
+        <v>27.8</v>
       </c>
       <c r="U13" s="3" t="n">
-        <v>13</v>
+        <v>8.1</v>
       </c>
       <c r="V13" s="3" t="n">
-        <v>26.4</v>
+        <v>26</v>
       </c>
       <c r="W13" s="3" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="X13" s="3" t="n">
-        <v>27.8</v>
+        <v>28.6</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>80.8</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>6.6</v>
+        <v>5</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1635,76 +1622,80 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>121.4</v>
-      </c>
-      <c r="D14" s="9" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="E14" s="9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F14" s="9" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G14" s="9" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>17.8</v>
+        <v>0.6</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+1
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>1.4</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="K14" s="3" t="n">
-        <v>0</v>
+        <v>4.8</v>
+      </c>
+      <c r="K14" s="12" t="n">
+        <v>60.6</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>21.1</v>
+        <v>13.5</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>20.9</v>
+        <v>19.4</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>24.6</v>
+        <v>22.4</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>98</v>
+        <v>9.6</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q14" s="3" t="n">
-        <v>27.3</v>
+        <v>6.2</v>
+      </c>
+      <c r="Q14" s="12" t="n">
+        <v>60</v>
       </c>
       <c r="R14" s="3" t="n">
-        <v>24.2</v>
+        <v>25.6</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>28.2</v>
+        <v>30</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>77.8</v>
+        <v>41</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>8.1</v>
+        <v>12.3</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>24</v>
+        <v>21.9</v>
       </c>
       <c r="X14" s="3" t="n">
-        <v>28.6</v>
+        <v>24.3</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1722,74 +1713,74 @@
       <c r="C15" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="D15" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="E15" s="9" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>12.1</v>
+      <c r="E15" s="3" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>54.5</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>17.4</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>20.5</v>
+        <v>2.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>4</v>
+        <v>19.2</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>19.5</v>
+        <v>0.1</v>
+      </c>
+      <c r="L15" s="12" t="n">
+        <v>2.9</v>
       </c>
       <c r="M15" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="N15" s="3" t="n">
-        <v>22.4</v>
+        <v>7.3</v>
+      </c>
+      <c r="N15" s="12" t="n">
+        <v>33.7</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>99</v>
+        <v>496</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q15" s="3" t="n">
-        <v>30</v>
+        <v>2.2</v>
+      </c>
+      <c r="Q15" s="12" t="n">
+        <v>51.4</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="S15" s="3" t="n">
-        <v>30</v>
+        <v>42.7</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>71</v>
+        <v>331</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="V15" s="3" t="n">
-        <v>25</v>
+        <v>76.3</v>
+      </c>
+      <c r="V15" s="12" t="n">
+        <v>36.5</v>
       </c>
       <c r="W15" s="3" t="n">
-        <v>21.9</v>
+        <v>1.4</v>
       </c>
       <c r="X15" s="3" t="n">
-        <v>24.3</v>
+        <v>75.8</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>386.1</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>3.4</v>
+        <v>42.4</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1805,76 +1796,76 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>5304.1</v>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>1524.2</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>126.8</v>
-      </c>
-      <c r="G16" s="3" t="n">
+        <v>1530.8</v>
+      </c>
+      <c r="D16" s="13" t="n">
         <v>54.5</v>
       </c>
+      <c r="E16" s="13" t="n">
+        <v>199.2</v>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>10.7</v>
+      </c>
       <c r="H16" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>18.4</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>14.6</v>
+        <v>11.6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>19.7</v>
+        <v>32.9</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>16.4</v>
+        <v>4.7</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>28.9</v>
+        <v>206.6</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>1.9</v>
+        <v>20.4</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>23.8</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>490</v>
+        <v>98</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>152.4</v>
+        <v>3606.5</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>85.8</v>
+        <v>25.1</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>0.4</v>
+        <v>28.5</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>331</v>
+        <v>66.8</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>176.3</v>
+        <v>15.3</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>136.5</v>
+        <v>22.3</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>1.4</v>
+        <v>24.1</v>
       </c>
       <c r="X16" s="3" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>386.1</v>
+        <v>725.6</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>4.2</v>
+        <v>8.5</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1890,76 +1881,76 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>306.2</v>
-      </c>
-      <c r="D17" s="9" t="n">
+        <v>606.4</v>
+      </c>
+      <c r="D17" s="13" t="n">
         <v>30.8</v>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <v>10.9</v>
+      <c r="E17" s="13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>13</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>18.4</v>
+        <v>17.5</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>51.9</v>
+        <v>4</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>1.4</v>
+        <v>0.1</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="M17" s="3" t="n">
-        <v>20.4</v>
+        <v>19.2</v>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>39.4</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>23.8</v>
+        <v>22.3</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>1.4</v>
+        <v>6.7</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>30.5</v>
+        <v>32.2</v>
       </c>
       <c r="R17" s="3" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="W17" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="S17" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="T17" s="3" t="n">
-        <v>66.8</v>
-      </c>
-      <c r="U17" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>41.3</v>
-      </c>
-      <c r="W17" s="3" t="n">
-        <v>6.4</v>
-      </c>
       <c r="X17" s="3" t="n">
-        <v>22.9</v>
+        <v>6.1</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1975,76 +1966,76 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="G18" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>17.2</v>
+        <v>336.5</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>18.8</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="8" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>19.4</v>
+        <v>42.1</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>20.7</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>22.3</v>
+        <v>24.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>10.7</v>
+        <v>15.4</v>
       </c>
       <c r="Q18" s="3" t="n">
-        <v>32.2</v>
+        <v>31.1</v>
       </c>
       <c r="R18" s="3" t="n">
         <v>25.3</v>
       </c>
       <c r="S18" s="3" t="n">
-        <v>27.8</v>
+        <v>28.2</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>58</v>
+        <v>60.5</v>
       </c>
       <c r="U18" s="3" t="n">
-        <v>20.1</v>
+        <v>18.4</v>
       </c>
       <c r="V18" s="3" t="n">
-        <v>28.3</v>
+        <v>25.2</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>25.1</v>
+        <v>0.4</v>
       </c>
       <c r="X18" s="3" t="n">
-        <v>29.8</v>
+        <v>29.2</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>21.6</v>
+        <v>88.5</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>8.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2060,76 +2051,76 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>326.2</v>
-      </c>
-      <c r="D19" s="9" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E19" s="9" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="G19" s="9" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H19" s="8" t="n">
-        <v>18.8</v>
+        <v>299</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.6</v>
+        <v>1.8</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>4.2</v>
+        <v>42.1</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>20.9</v>
+        <v>19.8</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>20.7</v>
+        <v>19.2</v>
       </c>
       <c r="N19" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>10.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q19" s="3" t="n">
-        <v>21.7</v>
+        <v>2.9</v>
       </c>
       <c r="R19" s="3" t="n">
-        <v>25.3</v>
+        <v>23.8</v>
       </c>
       <c r="S19" s="3" t="n">
-        <v>28.2</v>
+        <v>26.9</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>60.5</v>
+        <v>1.6</v>
       </c>
       <c r="U19" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v>25.7</v>
+        <v>10.6</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>25</v>
       </c>
       <c r="W19" s="3" t="n">
-        <v>24.2</v>
+        <v>22.8</v>
       </c>
       <c r="X19" s="3" t="n">
-        <v>29.2</v>
+        <v>26.3</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>88.5</v>
+        <v>83</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2145,76 +2136,76 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>299</v>
-      </c>
-      <c r="D20" s="9" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="E20" s="9" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F20" s="9" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="G20" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>88.40000000000001</v>
+        <v>35.5</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>6.4</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>2.2</v>
+        <v>0.1</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>19.8</v>
+        <v>18.4</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>19.7</v>
+        <v>18.9</v>
       </c>
       <c r="N20" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>99</v>
+        <v>1006.8</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.2</v>
+        <v>6</v>
       </c>
       <c r="Q20" s="3" t="n">
-        <v>27.9</v>
+        <v>30.1</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>23.8</v>
+        <v>24.4</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>71.59999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>10.6</v>
+        <v>15.7</v>
       </c>
       <c r="V20" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="W20" s="3" t="n">
-        <v>22.8</v>
+        <v>26.3</v>
+      </c>
+      <c r="W20" s="12" t="n">
+        <v>42.4</v>
       </c>
       <c r="X20" s="3" t="n">
-        <v>26.3</v>
+        <v>6.6</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>83</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>51.4</v>
+        <v>35.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2230,37 +2221,40 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>357.5</v>
-      </c>
-      <c r="D21" s="9" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>12.1</v>
+        <v>294.9</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>28.5</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>6.4</v>
+        <v>12.4</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="8" t="n">
-        <v>18.9</v>
+        <v>3.5</v>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">61 1
+</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="N21" s="3" t="n">
         <v>22.1</v>
@@ -2269,37 +2263,37 @@
         <v>100</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="Q21" s="3" t="n">
-        <v>30.1</v>
+        <v>31</v>
       </c>
       <c r="R21" s="3" t="n">
-        <v>24.4</v>
+        <v>25.8</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>26.9</v>
+        <v>22.9</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>63.1</v>
+        <v>66.8</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>15.7</v>
+        <v>14.8</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>463.1</v>
+        <v>24</v>
       </c>
       <c r="W21" s="3" t="n">
-        <v>24.2</v>
+        <v>22.6</v>
       </c>
       <c r="X21" s="3" t="n">
-        <v>28.8</v>
+        <v>26.5</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2315,76 +2309,76 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>294.9</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>26.6</v>
+        <v>1.6</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>96.09999999999999</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="G22" s="3" t="n">
-        <v>12.8</v>
+        <v>7.3</v>
+      </c>
+      <c r="G22" s="11" t="n">
+        <v>31.6</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>17.4</v>
+        <v>88.2</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>1.9</v>
+        <v>10.4</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>3.5</v>
+        <v>18.4</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L22" s="8" t="n">
-        <v>19.1</v>
+        <v>65.09999999999999</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>98.40000000000001</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>19.1</v>
+        <v>97.8</v>
       </c>
       <c r="N22" s="3" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>494</v>
+      </c>
+      <c r="P22" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="O22" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="R22" s="3" t="n">
-        <v>25.8</v>
+      <c r="Q22" s="12" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="R22" s="12" t="n">
+        <v>24.6</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>29.9</v>
+        <v>39.7</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>166.8</v>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="V22" s="3" t="n">
-        <v>24</v>
+        <v>320</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="V22" s="12" t="n">
+        <v>29.3</v>
       </c>
       <c r="W22" s="3" t="n">
-        <v>22.6</v>
+        <v>78.3</v>
       </c>
       <c r="X22" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Y22" s="3" t="n">
+        <v>442</v>
+      </c>
+      <c r="Z22" s="3" t="n">
         <v>26.5</v>
-      </c>
-      <c r="Y22" s="3" t="n">
-        <v>88.8</v>
-      </c>
-      <c r="Z22" s="3" t="n">
-        <v>3.3</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2400,76 +2394,79 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1610.1</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>15051.9</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>96.2</v>
-      </c>
-      <c r="F23" s="10" t="n">
-        <v>75.8</v>
+        <v>322</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>25.5</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>59.8</v>
+        <v>11.9</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>88.2</v>
+        <v>17.6</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>18.4</v>
+        <v>2.1</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 2
+</t>
+        </is>
       </c>
       <c r="K23" s="3" t="n">
-        <v>6.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>198.5</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>972.8</v>
+        <v>19.6</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>122.7</v>
+        <v>22.7</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>494</v>
+        <v>98.8</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="Q23" s="3" t="n">
-        <v>1252.9</v>
+        <v>30.6</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1911.6</v>
+        <v>24.9</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>3941.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>320</v>
+        <v>64</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>15.9</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>1899.3</v>
+        <v>25.9</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>18.9</v>
+        <v>23.8</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>405.6</v>
+        <v>28.1</v>
       </c>
       <c r="Y23" s="3" t="n">
-        <v>422</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>26.5</v>
+        <v>2.2</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2485,68 +2482,81 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>322</v>
-      </c>
-      <c r="D24" s="9" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F24" s="9" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="G24" s="9" t="n">
-        <v>11.9</v>
+        <v>0.1</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>10.3</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>17.6</v>
+        <v>18.6</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="8" t="n">
-        <v>117</v>
-      </c>
-      <c r="M24" s="3" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3 2
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>351.6</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74
+15156
+</t>
+        </is>
       </c>
       <c r="N24" s="3" t="n">
-        <v>2.6</v>
+        <v>0.1</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="Q24" s="3" t="n"/>
       <c r="R24" s="3" t="n">
-        <v>24.9</v>
+        <v>0.1</v>
       </c>
       <c r="S24" s="3" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W24" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="X24" s="3" t="n"/>
+        <v>0.1</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="Y24" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2562,58 +2572,64 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>177.8</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F25" s="12" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="G25" s="12" t="n">
-        <v>10.3</v>
+        <v>12.8</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>11.2</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I25" s="3" t="n"/>
+        <v>18.6</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>2.4</v>
+      </c>
       <c r="J25" s="3" t="n">
-        <v>41.3</v>
+        <v>0.3</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>31.6</v>
+        <v>14.4</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M25" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="N25" s="3" t="n">
+      <c r="M25" s="12" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="N25" s="12" t="n">
         <v>22.9</v>
       </c>
       <c r="O25" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P25" s="3" t="n"/>
+      <c r="P25" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q25" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="R25" s="3" t="n"/>
+        <v>6.9</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>22.1</v>
+      </c>
       <c r="S25" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>93.59999999999999</v>
+        <v>23.6</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>15.2</v>
+        <v>1.8</v>
       </c>
       <c r="V25" s="3" t="n">
-        <v>20.5</v>
+        <v>21.5</v>
       </c>
       <c r="W25" s="3" t="n">
         <v>21</v>
@@ -2622,10 +2638,10 @@
         <v>24.5</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>95.2</v>
+        <v>952.6</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2643,35 +2659,35 @@
       <c r="C26" s="3" t="n">
         <v>345</v>
       </c>
-      <c r="D26" s="9" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E26" s="9" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F26" s="9" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="G26" s="9" t="n">
-        <v>11.2</v>
+      <c r="D26" s="3" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>68.61</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>13.7</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>18.6</v>
+        <v>12.6</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>4.4</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>20.6</v>
+        <v>26.6</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>20.4</v>
+        <v>26.4</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>23.8</v>
@@ -2680,13 +2696,13 @@
         <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q26" s="3" t="n">
         <v>31.4</v>
       </c>
       <c r="R26" s="3" t="n">
-        <v>24.8</v>
+        <v>24.1</v>
       </c>
       <c r="S26" s="3" t="n">
         <v>25.3</v>
@@ -2694,23 +2710,23 @@
       <c r="T26" s="3" t="n">
         <v>55.2</v>
       </c>
-      <c r="U26" s="3" t="n">
-        <v>20.6</v>
+      <c r="U26" s="12" t="n">
+        <v>6.6</v>
       </c>
       <c r="V26" s="3" t="n">
-        <v>27.2</v>
+        <v>22.2</v>
       </c>
       <c r="W26" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>16.2</v>
+        <v>26.8</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>74.3</v>
+        <v>4.3</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2726,46 +2742,46 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>418.2</v>
+        <v>48.2</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>32.9</v>
+        <v>32.6</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="F27" s="12" t="n">
-        <v>86.09999999999999</v>
+      <c r="F27" s="3" t="n">
+        <v>26.8</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>18.7</v>
+        <v>12.8</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>17.6</v>
+        <v>18.4</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>15.2</v>
+        <v>52.4</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M27" s="8" t="n">
+      <c r="M27" s="3" t="n">
         <v>19.5</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>99</v>
+        <v>994</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.2</v>
+        <v>6.2</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>32.9</v>
@@ -2786,16 +2802,16 @@
         <v>29.3</v>
       </c>
       <c r="W27" s="3" t="n">
-        <v>25.5</v>
+        <v>65.5</v>
       </c>
       <c r="X27" s="3" t="n">
         <v>30.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>74.2</v>
+        <v>0.2</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>1</v>
+        <v>4.3</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2813,47 +2829,47 @@
       <c r="C28" s="3" t="n">
         <v>282.3</v>
       </c>
-      <c r="D28" s="9" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E28" s="9" t="n">
+      <c r="D28" s="11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E28" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F28" s="9" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="G28" s="9" t="n">
-        <v>12.8</v>
+      <c r="F28" s="3" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>18.4</v>
+        <v>190.8</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="8" t="n">
-        <v>220.1</v>
-      </c>
-      <c r="M28" s="3" t="n">
-        <v>19.9</v>
+        <v>18.1</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="M28" s="12" t="n">
+        <v>29.9</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>23.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>29.7</v>
+        <v>29.2</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>25.1</v>
@@ -2865,7 +2881,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>12.7</v>
+        <v>14.7</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>24.4</v>
@@ -2877,10 +2893,10 @@
         <v>26.3</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2898,29 +2914,29 @@
       <c r="C29" s="3" t="n">
         <v>140.2</v>
       </c>
-      <c r="D29" s="9" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E29" s="9" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F29" s="9" t="n">
-        <v>24.8</v>
+      <c r="D29" s="11" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>24.7</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>18.9</v>
+        <v>5.2</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>19</v>
+        <v>2.2</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>1.1</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>68.40000000000001</v>
+        <v>23.7</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>21.9</v>
@@ -2935,7 +2951,7 @@
         <v>96.5</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.9</v>
+        <v>6.9</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>28.6</v>
@@ -2947,7 +2963,7 @@
         <v>28.8</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>73.7</v>
+        <v>3.7</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>10.3</v>
@@ -2962,10 +2978,10 @@
         <v>25.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>24.2</v>
+        <v>21.6</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>5.8</v>
+        <v>30.2</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2983,53 +2999,53 @@
       <c r="C30" s="3" t="n">
         <v>1363.5</v>
       </c>
-      <c r="D30" s="10" t="n">
-        <v>1506.5</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>99</v>
-      </c>
-      <c r="F30" s="10" t="n">
-        <v>28</v>
+      <c r="D30" s="13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="E30" s="13" t="n">
+        <v>996.1</v>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>25.6</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>56.9</v>
+        <v>1.4</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>92.2</v>
+        <v>0.4</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>17.9</v>
+        <v>172.1</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>23.7</v>
+        <v>5.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>102.2</v>
+        <v>20.4</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>10.1</v>
+        <v>11.1</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>0.7</v>
+        <v>172.8</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>489.5</v>
+        <v>429.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="Q30" s="3" t="n">
         <v>145.5</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>3545.1</v>
+        <v>3.3</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>344.5</v>
@@ -3038,19 +3054,23 @@
         <v>68.8</v>
       </c>
       <c r="V30" s="3" t="n">
-        <v>22.1</v>
+        <v>22.4</v>
       </c>
       <c r="W30" s="3" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="X30" s="3" t="n">
-        <v>26.7</v>
+        <v>15.3</v>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+4
+</t>
+        </is>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>411.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>30.9</v>
+        <v>0.4</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3068,54 +3088,59 @@
       <c r="C31" s="3" t="n">
         <v>272.7</v>
       </c>
-      <c r="D31" s="9" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>25.6</v>
+      <c r="D31" s="13" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="E31" s="13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>16</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1.1</v>
+        <v>8.6</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>18.4</v>
+        <v>19.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K31" s="3" t="n"/>
+      <c r="K31" s="3" t="n">
+        <v>34.1</v>
+      </c>
       <c r="L31" s="3" t="n">
-        <v>20.4</v>
+        <v>61.6</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>71.8</v>
+        <v>26.2</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>97.90000000000001</v>
+        <v>978.9</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q31" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="R31" s="3" t="n">
-        <v>84.2</v>
+      <c r="Q31" s="12" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="R31" s="12" t="n">
+        <v>42.4</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="T31" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>22.1</v>
+      </c>
+      <c r="T31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 89
+</t>
+        </is>
       </c>
       <c r="U31" s="3" t="n">
         <v>13.8</v>
@@ -3124,16 +3149,21 @@
         <v>25.5</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>23.1</v>
+        <v>0.2</v>
       </c>
       <c r="X31" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="Y31" s="3" t="n">
-        <v>82.3</v>
+        <v>2.1</v>
+      </c>
+      <c r="Y31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1141
+22
+171971191 7
+</t>
+        </is>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3151,32 +3181,32 @@
       <c r="C32" s="3" t="n">
         <v>263.5</v>
       </c>
-      <c r="D32" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="E32" s="9" t="n">
+      <c r="D32" s="3" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E32" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="G32" s="9" t="n">
-        <v>8.6</v>
+      <c r="G32" s="3" t="n">
+        <v>4.6</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>19.4</v>
+        <v>19</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>1.3</v>
+        <v>2.5</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>21.6</v>
+        <v>20.8</v>
       </c>
       <c r="M32" s="3" t="n">
         <v>21.5</v>
@@ -3187,7 +3217,9 @@
       <c r="O32" s="3" t="n">
         <v>99</v>
       </c>
-      <c r="P32" s="3" t="n"/>
+      <c r="P32" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q32" s="3" t="n">
         <v>29</v>
       </c>
@@ -3195,16 +3227,16 @@
         <v>24.5</v>
       </c>
       <c r="S32" s="3" t="n">
-        <v>27.9</v>
+        <v>22.9</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>638.2</v>
+        <v>69.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="V32" s="3" t="n">
-        <v>27.1</v>
+      <c r="V32" s="12" t="n">
+        <v>83.09999999999999</v>
       </c>
       <c r="W32" s="3" t="n">
         <v>24.5</v>
@@ -3213,10 +3245,15 @@
         <v>25.8</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="Z32" s="3" t="n">
-        <v>6.7</v>
+        <v>0.8</v>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1717177
+23
+83
+</t>
+        </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3234,32 +3271,32 @@
       <c r="C33" s="3" t="n">
         <v>44.1</v>
       </c>
-      <c r="D33" s="9" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>20.6</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="G33" s="9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H33" s="8" t="n">
-        <v>29</v>
+      <c r="D33" s="10" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>17.8</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>10.3</v>
+        <v>1.3</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>20.8</v>
+        <v>2.1</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>20.6</v>
@@ -3268,10 +3305,10 @@
         <v>24.1</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>98</v>
+        <v>980.8</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>0.4</v>
+        <v>20.4</v>
       </c>
       <c r="Q33" s="3" t="n">
         <v>24.2</v>
@@ -3280,7 +3317,7 @@
         <v>22.1</v>
       </c>
       <c r="S33" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="T33" s="3" t="n">
         <v>83.40000000000001</v>
@@ -3298,10 +3335,10 @@
         <v>21.4</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>948.1</v>
+        <v>28.7</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>0.3</v>
+        <v>12.8</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3317,47 +3354,52 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="D34" s="9" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E34" s="9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="E34" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="F34" s="9" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G34" s="9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H34" s="8" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="I34" s="3" t="n"/>
+      <c r="F34" s="11" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J34" s="3" t="n">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="M34" s="3" t="n">
-        <v>20.1</v>
+        <v>19</v>
+      </c>
+      <c r="M34" s="12" t="n">
+        <v>61.2</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>980.8</v>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 20
+</t>
+        </is>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>30.1</v>
+        <v>32.1</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>25.6</v>
@@ -3366,13 +3408,13 @@
         <v>29.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>70.2</v>
+        <v>76.2</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V34" s="3" t="n">
-        <v>26.3</v>
+      <c r="V34" s="12" t="n">
+        <v>63.5</v>
       </c>
       <c r="W34" s="3" t="n">
         <v>21</v>
@@ -3384,7 +3426,7 @@
         <v>62.5</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>12.8</v>
+        <v>4.9</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3402,38 +3444,44 @@
       <c r="C35" s="3" t="n">
         <v>284.4</v>
       </c>
-      <c r="D35" s="9" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="E35" s="9" t="n">
+      <c r="D35" s="3" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E35" s="3" t="n">
         <v>18.8</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="G35" s="9" t="n">
-        <v>10.7</v>
+      <c r="G35" s="3" t="n">
+        <v>2.5</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>1.5</v>
+        <v>19</v>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 6
+</t>
+        </is>
       </c>
       <c r="J35" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13 72
+</t>
+        </is>
       </c>
       <c r="L35" s="3" t="n">
-        <v>19</v>
+        <v>21.9</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>19</v>
+        <v>0.4</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>20.9</v>
+        <v>25.8</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>100</v>
@@ -3457,7 +3505,7 @@
         <v>9.4</v>
       </c>
       <c r="V35" s="3" t="n">
-        <v>66.3</v>
+        <v>26.3</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>24.4</v>
@@ -3469,7 +3517,7 @@
         <v>85.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>4.9</v>
+        <v>1.3</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3487,29 +3535,39 @@
       <c r="C36" s="3" t="n">
         <v>117.2</v>
       </c>
-      <c r="D36" s="9" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E36" s="9" t="n">
+      <c r="D36" s="3" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E36" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="F36" s="9" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G36" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H36" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="I36" s="3" t="n">
-        <v>0.6</v>
+      <c r="F36" s="11" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222725
+1142811042
+</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0 6
+</t>
+        </is>
       </c>
       <c r="J36" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K36" s="3" t="n">
-        <v>1.3</v>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13 72
+</t>
+        </is>
       </c>
       <c r="L36" s="3" t="n">
         <v>21.9</v>
@@ -3518,13 +3576,13 @@
         <v>21.7</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>25.8</v>
+        <v>20.9</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.4</v>
+        <v>6.4</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>21.5</v>
@@ -3541,20 +3599,20 @@
       <c r="U36" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="V36" s="3" t="n">
-        <v>21.4</v>
+      <c r="V36" s="12" t="n">
+        <v>41.4</v>
       </c>
       <c r="W36" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="X36" s="3" t="n">
-        <v>2.2</v>
+        <v>24.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>24.2</v>
+        <v>4.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3570,16 +3628,16 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>826.4</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>142.9</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="F37" s="10" t="n">
-        <v>245.1</v>
+        <v>22.6</v>
+      </c>
+      <c r="D37" s="13" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E37" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>1.5</v>
       </c>
       <c r="G37" s="3" t="n">
         <v>42.9</v>
@@ -3591,34 +3649,39 @@
         <v>5.8</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>17.9</v>
+        <v>17.3</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>1203444.6</v>
-      </c>
-      <c r="M37" s="3" t="n">
-        <v>44.4</v>
+        <v>1034.4</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">777
+22
+7
+</t>
+        </is>
       </c>
       <c r="N37" s="3" t="n">
-        <v>214.9</v>
+        <v>20.9</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>495</v>
+        <v>425</v>
       </c>
       <c r="P37" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>133.1</v>
+        <v>1334.1</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>11287.9</v>
+        <v>117.9</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>27.3</v>
+        <v>86.3</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>393.6</v>
@@ -3630,16 +3693,14 @@
         <v>124.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="X37" s="3" t="n">
-        <v>26</v>
-      </c>
+        <v>26.5</v>
+      </c>
+      <c r="X37" s="3" t="n"/>
       <c r="Y37" s="3" t="n">
         <v>416</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>5.6</v>
+        <v>0.7</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3657,23 +3718,23 @@
       <c r="C38" s="3" t="n">
         <v>165.3</v>
       </c>
-      <c r="D38" s="9" t="n">
+      <c r="D38" s="10" t="n">
         <v>28.6</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="10" t="n">
         <v>24.3</v>
       </c>
-      <c r="G38" s="9" t="n">
-        <v>8.6</v>
+      <c r="G38" s="10" t="n">
+        <v>8.5</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>1.8</v>
@@ -3683,7 +3744,7 @@
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>20.6</v>
+        <v>61.3</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>24.2</v>
@@ -3692,17 +3753,19 @@
         <v>99</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q38" s="3" t="n"/>
+        <v>6.2</v>
+      </c>
+      <c r="Q38" s="3" t="n">
+        <v>26.6</v>
+      </c>
       <c r="R38" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>29.3</v>
+        <v>73.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>78.7</v>
+        <v>78.2</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>8.1</v>
@@ -3711,13 +3774,13 @@
         <v>84.8</v>
       </c>
       <c r="W38" s="3" t="n">
-        <v>46.5</v>
+        <v>26.5</v>
       </c>
       <c r="X38" s="3" t="n">
-        <v>27.2</v>
+        <v>26</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>83.2</v>
+        <v>8324.799999999999</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>5.6</v>
@@ -3736,72 +3799,78 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="D39" s="9" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F39" s="9" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="F39" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="G39" s="9" t="n">
+      <c r="G39" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>545.5</v>
+        <v>1.8</v>
       </c>
       <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="n">
-        <v>19.5</v>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 29
+15
+</t>
+        </is>
       </c>
       <c r="M39" s="3" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="N39" s="3" t="n"/>
+        <v>10.6</v>
+      </c>
+      <c r="N39" s="3" t="n">
+        <v>72.59999999999999</v>
+      </c>
       <c r="O39" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q39" s="3" t="n">
-        <v>30.7</v>
+        <v>10.1</v>
       </c>
       <c r="R39" s="3" t="n">
-        <v>25.3</v>
+        <v>25.5</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>28.8</v>
+        <v>89.3</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="U39" s="3" t="n">
-        <v>15.2</v>
+        <v>666.1</v>
+      </c>
+      <c r="U39" s="12" t="n">
+        <v>42.7</v>
       </c>
       <c r="V39" s="3" t="n">
-        <v>28</v>
+        <v>61.2</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>24</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="X39" s="3" t="n">
-        <v>27.3</v>
+        <v>22.6</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>23.4</v>
+        <v>2.2</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>0.5</v>
+        <v>6.1</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3817,76 +3886,74 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>242.6</v>
-      </c>
-      <c r="D40" s="9" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="E40" s="9" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F40" s="9" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="G40" s="9" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>19.4</v>
+        <v>28.1</v>
+      </c>
+      <c r="D40" s="10" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="E40" s="12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>0</v>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="K40" s="3" t="n"/>
       <c r="L40" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="M40" s="8" t="n">
-        <v>29.2</v>
+        <v>19.5</v>
+      </c>
+      <c r="M40" s="3" t="n">
+        <v>19.5</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>23.2</v>
+        <v>24.6</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>98.8</v>
+        <v>990.6</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>29.3</v>
+        <v>36.7</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>24.9</v>
+        <v>25.3</v>
       </c>
       <c r="S40" s="3" t="n">
-        <v>28.7</v>
+        <v>28.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>70.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>12</v>
+        <v>15.2</v>
       </c>
       <c r="V40" s="3" t="n">
-        <v>27.1</v>
+        <v>28</v>
       </c>
       <c r="W40" s="3" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="X40" s="3" t="n">
-        <v>29.1</v>
+        <v>27.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>24.4</v>
+        <v>0.1</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>6.7</v>
+        <v>10.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3902,76 +3969,80 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>288.6</v>
-      </c>
-      <c r="D41" s="9" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E41" s="9" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F41" s="9" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G41" s="9" t="n">
-        <v>10.5</v>
+        <v>242.6</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>18.6</v>
+        <v>19.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>5</v>
+        <v>1.5</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>11.1</v>
+        <v>8</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="M41" s="8" t="n">
-        <v>29.2</v>
+        <v>21</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">442
+111
+</t>
+        </is>
       </c>
       <c r="N41" s="3" t="n">
-        <v>25.2</v>
+        <v>23.2</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>30.9</v>
+        <v>29.3</v>
       </c>
       <c r="R41" s="3" t="n">
-        <v>21.7</v>
+        <v>24.9</v>
       </c>
       <c r="S41" s="3" t="n">
-        <v>27.6</v>
+        <v>28.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>62</v>
-      </c>
-      <c r="U41" s="3" t="n">
-        <v>17</v>
+        <v>20.5</v>
+      </c>
+      <c r="U41" s="12" t="n">
+        <v>26</v>
       </c>
       <c r="V41" s="3" t="n">
-        <v>27.1</v>
+        <v>22.1</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="X41" s="3" t="n">
-        <v>29.3</v>
+        <v>22.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>81.8</v>
+        <v>24.4</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -3987,74 +4058,76 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>311.6</v>
-      </c>
-      <c r="D42" s="9" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F42" s="9" t="n">
-        <v>25.9</v>
+        <v>288.6</v>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>25.6</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="H42" s="8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H42" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>18.6</v>
+        <v>1.5</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="K42" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="M42" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="N42" s="12" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>10618.2</v>
+      </c>
+      <c r="P42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="M42" s="3" t="n"/>
-      <c r="N42" s="3" t="n">
+      <c r="Q42" s="3" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="R42" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="O42" s="3" t="n">
-        <v>99</v>
-      </c>
-      <c r="P42" s="3" t="n">
+      <c r="S42" s="3" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="Y42" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q42" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="R42" s="3" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="S42" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="T42" s="3" t="n">
-        <v>77</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="W42" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="X42" s="3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="Y42" s="3" t="n">
-        <v>84.3</v>
-      </c>
       <c r="Z42" s="3" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4070,29 +4143,31 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>7779.7</v>
-      </c>
-      <c r="D43" s="9" t="n">
+        <v>311.6</v>
+      </c>
+      <c r="D43" s="10" t="n">
         <v>30.8</v>
       </c>
-      <c r="E43" s="9" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F43" s="9" t="n">
-        <v>25.9</v>
+      <c r="E43" s="10" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>25.6</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="H43" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H43" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="I43" s="8" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="J43" s="3" t="n"/>
+      <c r="I43" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>5</v>
+      </c>
       <c r="K43" s="3" t="n">
-        <v>39.5</v>
+        <v>0.2</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>21.2</v>
@@ -4101,31 +4176,41 @@
       <c r="N43" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="O43" s="3" t="n"/>
+      <c r="O43" s="3" t="n">
+        <v>99</v>
+      </c>
       <c r="P43" s="3" t="n">
-        <v>0.2</v>
+        <v>6.4</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="3" t="n"/>
-      <c r="S43" s="3" t="n"/>
+      <c r="R43" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>24</v>
+      </c>
       <c r="T43" s="3" t="n">
-        <v>77</v>
+        <v>726</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>7.1</v>
+        <v>2.1</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="n"/>
+      <c r="W43" s="3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>95.09999999999999</v>
+      </c>
       <c r="Y43" s="3" t="n">
-        <v>392.3</v>
+        <v>84.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>32.3</v>
+        <v>4.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4141,55 +4226,79 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>7779.7</v>
-      </c>
-      <c r="D44" s="13" t="n"/>
-      <c r="E44" s="13" t="n"/>
-      <c r="F44" s="9" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="H44" s="3" t="n">
-        <v>934.6</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="8" t="n">
-        <v>14.9</v>
-      </c>
+        <v>311.6</v>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G44" s="11" t="n">
+        <v>546.5</v>
+      </c>
+      <c r="H44" s="12" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42424
+211
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L44" s="8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="n"/>
-      <c r="O44" s="3" t="n">
-        <v>491.8</v>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+111562
+</t>
+        </is>
+      </c>
+      <c r="N44" s="12" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="O44" s="3" t="n"/>
       <c r="P44" s="3" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="Q44" s="8" t="n">
-        <v>2461.2</v>
-      </c>
-      <c r="R44" s="3" t="n"/>
-      <c r="S44" s="3" t="n"/>
-      <c r="T44" s="3" t="n"/>
+        <v>6.4</v>
+      </c>
+      <c r="Q44" s="12" t="n">
+        <v>46.3</v>
+      </c>
+      <c r="R44" s="12" t="n">
+        <v>373.3</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>726</v>
+      </c>
       <c r="U44" s="3" t="n">
-        <v>66</v>
-      </c>
-      <c r="V44" s="3" t="n"/>
-      <c r="W44" s="3" t="n"/>
-      <c r="X44" s="3" t="n"/>
-      <c r="Y44" s="3" t="n"/>
-      <c r="Z44" s="3" t="n">
-        <v>32.3</v>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="X44" s="12" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="Y44" s="3" t="n">
+        <v>3242.3</v>
+      </c>
+      <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4204,58 +4313,60 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>290.7</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>305.1</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>25.8</v>
+        <v>1453.4</v>
+      </c>
+      <c r="D45" s="13" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E45" s="13" t="n">
+        <v>779.7</v>
+      </c>
+      <c r="F45" s="13" t="n">
+        <v>127.4</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>10.1</v>
+        <v>50.6</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>934.6</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="J45" s="3" t="n"/>
+      <c r="J45" s="3" t="n">
+        <v>45.9</v>
+      </c>
       <c r="K45" s="3" t="n"/>
-      <c r="L45" s="3" t="n"/>
+      <c r="L45" s="3" t="n">
+        <v>113.8</v>
+      </c>
       <c r="M45" s="3" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>24.1</v>
+        <v>4.4</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>98.40000000000001</v>
-      </c>
-      <c r="P45" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>494.2</v>
+      </c>
+      <c r="P45" s="3" t="n"/>
       <c r="Q45" s="3" t="n">
-        <v>29.3</v>
+        <v>146.3</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>64.5</v>
+        <v>24.5</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>27.7</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>68.3</v>
+        <v>341.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>13.2</v>
+        <v>66.2</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>26.8</v>
+        <v>71.7</v>
       </c>
       <c r="W45" s="3" t="n">
         <v>23.8</v>
@@ -4264,10 +4375,10 @@
         <v>27.6</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>78.5</v>
+        <v>3242.3</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>7.7</v>
+        <v>38.3</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4282,56 +4393,78 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n"/>
-      <c r="D46" s="14" t="n"/>
-      <c r="E46" s="14" t="n"/>
-      <c r="F46" s="9" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="G46" s="3" t="n">
+      <c r="C46" s="3" t="n">
+        <v>290.7</v>
+      </c>
+      <c r="D46" s="10" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G46" s="10" t="n">
         <v>10.1</v>
       </c>
-      <c r="H46" s="8" t="n">
+      <c r="H46" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>16.7</v>
+        <v>1.7</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n">
-        <v>20.8</v>
+      <c r="K46" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="L46" s="12" t="n">
+        <v>68.40000000000001</v>
       </c>
       <c r="M46" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="S46" s="12" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="U46" s="12" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W46" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="N46" s="3" t="n"/>
-      <c r="O46" s="3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="P46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U46" s="3" t="n"/>
-      <c r="V46" s="3" t="n"/>
-      <c r="W46" s="3" t="n"/>
       <c r="X46" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
+        <v>0.1</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>2.7</v>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -41,6 +41,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0075696F"/>
         <bgColor rgb="0075696F"/>
       </patternFill>
@@ -49,12 +61,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -140,10 +146,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -152,10 +158,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -771,74 +774,74 @@
       <c r="C4" s="3" t="n">
         <v>351.3</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="12" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="12" t="n">
         <v>22.7</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="12" t="n">
         <v>28.1</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="12" t="n">
         <v>10.8</v>
       </c>
-      <c r="H4" s="3" t="n">
-        <v>6.6</v>
+      <c r="H4" s="8" t="n">
+        <v>21</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>2.6</v>
+        <v>21.6</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>4.4</v>
+        <v>14.4</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="N4" s="3" t="n">
         <v>27.4</v>
       </c>
       <c r="O4" s="3" t="n">
-        <v>98</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q4" s="3" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="P4" s="8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q4" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="S4" s="3" t="n">
-        <v>28.1</v>
+      <c r="S4" s="8" t="n">
+        <v>1281.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="V4" s="3" t="n">
+        <v>156.1</v>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="V4" s="8" t="n">
         <v>28.6</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="X4" s="3" t="n">
+      <c r="X4" s="8" t="n">
         <v>29.1</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>142.3</v>
+        <v>174.3</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>2.1</v>
+        <v>110</v>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -856,16 +859,16 @@
       <c r="C5" s="3" t="n">
         <v>278.1</v>
       </c>
-      <c r="D5" s="10" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>19</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="G5" s="3" t="n">
+      <c r="D5" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G5" s="12" t="n">
         <v>10.3</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -878,52 +881,52 @@
         <v>3.1</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="L5" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L5" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="8" t="n">
         <v>21.4</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>25.4</v>
+        <v>0.5</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>92</v>
+        <v>198</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q5" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q5" s="8" t="n">
         <v>26</v>
       </c>
       <c r="R5" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="S5" s="3" t="n">
+        <v>23</v>
+      </c>
+      <c r="S5" s="8" t="n">
         <v>26.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="V5" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="V5" s="8" t="n">
         <v>22</v>
       </c>
       <c r="W5" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X5" s="3" t="n">
+      <c r="X5" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>92</v>
+        <v>192</v>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>9.4</v>
+        <v>2.1</v>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -939,58 +942,56 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>368</v>
-      </c>
-      <c r="D6" s="10" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="F6" s="10" t="n">
-        <v>26.2</v>
+        <v>12368</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>206.3</v>
       </c>
       <c r="G6" s="10" t="n">
-        <v>10.3</v>
+        <v>41</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L6" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
+      <c r="K6" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L6" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="N6" s="8" t="n">
         <v>25.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>988.5</v>
+        <v>197</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="Q6" s="3" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="Q6" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>22.3</v>
+        <v>41.3</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>59.6</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>18.6</v>
@@ -998,17 +999,17 @@
       <c r="V6" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="X6" s="12" t="n">
-        <v>92</v>
+      <c r="X6" s="8" t="n">
+        <v>29</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1026,74 +1027,74 @@
       <c r="C7" s="3" t="n">
         <v>418.2</v>
       </c>
-      <c r="D7" s="10" t="n">
-        <v>32.4</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>21</v>
-      </c>
-      <c r="F7" s="10" t="n">
+      <c r="D7" s="12" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F7" s="12" t="n">
         <v>26.7</v>
       </c>
-      <c r="G7" s="10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>20.6</v>
+      <c r="G7" s="12" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H7" s="8" t="n">
+        <v>944.4</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>34.5</v>
+        <v>20.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>14.1</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>11.3</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>21.7</v>
+        <v>20.9</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>25.7</v>
+        <v>46.1</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>6.5</v>
+        <v>1980.8</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q7" s="3" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="R7" s="3" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="S7" s="12" t="n">
-        <v>72.90000000000001</v>
+        <v>10.4</v>
+      </c>
+      <c r="Q7" s="8" t="n">
+        <v>311.9</v>
+      </c>
+      <c r="R7" s="8" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>28</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="U7" s="3" t="n">
-        <v>23</v>
+        <v>159.5</v>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v>19.1</v>
       </c>
       <c r="V7" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="W7" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="X7" s="3" t="n">
-        <v>28.4</v>
+        <v>28.7</v>
+      </c>
+      <c r="W7" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="X7" s="8" t="n">
+        <v>28.8</v>
       </c>
       <c r="Y7" s="3" t="n">
-        <v>94.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AA7" s="3" t="inlineStr">
         <is>
@@ -1109,76 +1110,76 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>368</v>
-      </c>
-      <c r="D8" s="10" t="n">
+        <v>19368</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="M8" s="8" t="n">
+        <v>41.7</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>196.5</v>
+      </c>
+      <c r="P8" s="8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q8" s="8" t="n">
         <v>33.3</v>
       </c>
-      <c r="E8" s="11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>34.45</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="H8" s="3" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="I8" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="L8" s="12" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="M8" s="3" t="n">
-        <v>78.59999999999999</v>
-      </c>
-      <c r="N8" s="3" t="n">
+      <c r="R8" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>194.8</v>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="X8" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="O8" s="3" t="n">
-        <v>870.6</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Q8" s="3" t="n">
-        <v>344.6</v>
-      </c>
-      <c r="R8" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="S8" s="12" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>308</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>96.09999999999999</v>
-      </c>
-      <c r="V8" s="12" t="n">
-        <v>35.2</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>39.5</v>
-      </c>
       <c r="Y8" s="3" t="n">
-        <v>389.1</v>
+        <v>74.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>41.8</v>
+        <v>19.8</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1194,79 +1195,52 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1783.6</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="G9" s="10" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H9" s="3" t="n">
-        <v>26.4</v>
-      </c>
+        <v>17183.6</v>
+      </c>
+      <c r="D9" s="9" t="inlineStr"/>
+      <c r="E9" s="9" t="inlineStr"/>
+      <c r="F9" s="9" t="inlineStr"/>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="n">
-        <v>2.4</v>
+        <v>112</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>4.2</v>
+        <v>120.9</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="M9" s="3" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="N9" s="3" t="n">
-        <v>25.6</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr"/>
+      <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="n">
-        <v>927.4</v>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 066
-</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="n">
-        <v>344.6</v>
-      </c>
-      <c r="R9" s="3" t="n">
-        <v>24.9</v>
-      </c>
+        <v>487</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr"/>
       <c r="S9" s="3" t="n">
-        <v>4.5</v>
+        <v>1371.5</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>61.6</v>
+        <v>908</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="W9" s="3" t="n">
-        <v>24</v>
-      </c>
+        <v>190.1</v>
+      </c>
+      <c r="V9" s="3" t="inlineStr"/>
+      <c r="W9" s="3" t="inlineStr"/>
       <c r="X9" s="3" t="n">
-        <v>272.9</v>
+        <v>1032.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>22.8</v>
+        <v>1389.1</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>8.4</v>
+        <v>41.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1282,76 +1256,74 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>356.7</v>
-      </c>
-      <c r="D10" s="10" t="n">
+        <v>2356.7</v>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>32.3</v>
       </c>
-      <c r="E10" s="10" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="H10" s="3" t="n">
-        <v>18.7</v>
+      <c r="E10" s="12" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>20.2</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>77.09999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
+        <v>4.2</v>
+      </c>
+      <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="n">
-        <v>20.6</v>
+        <v>21.9</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>22.5</v>
+        <v>21.6</v>
       </c>
       <c r="N10" s="3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>197.4</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q10" s="8" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="R10" s="8" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="S10" s="8" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="W10" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="O10" s="3" t="n">
-        <v>29</v>
-      </c>
-      <c r="P10" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q10" s="3" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="R10" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S10" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>563.5</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="V10" s="3" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>29</v>
+      <c r="X10" s="8" t="n">
+        <v>27.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>9.4</v>
+        <v>177.8</v>
       </c>
       <c r="Z10" s="3" t="n">
-        <v>2.2</v>
+        <v>18.4</v>
       </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
@@ -1367,76 +1339,76 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>426.3</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>32.8</v>
+        <v>453.1</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>93.3</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="G11" s="10" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>18.6</v>
+        <v>89.8</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>18.7</v>
       </c>
       <c r="I11" s="3" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="K11" s="8" t="n">
         <v>0.4</v>
       </c>
-      <c r="J11" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="K11" s="3" t="n">
-        <v>4.8</v>
-      </c>
       <c r="L11" s="3" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>23.3</v>
+        <v>24</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>97</v>
+        <v>199</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>0.7</v>
+        <v>10.2</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>32.8</v>
+        <v>33.2</v>
       </c>
       <c r="R11" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="S11" s="3" t="n">
-        <v>28.7</v>
+      <c r="S11" s="8" t="n">
+        <v>28.5</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>58</v>
-      </c>
-      <c r="U11" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="V11" s="3" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="W11" s="3" t="n">
-        <v>25.6</v>
+        <v>156.3</v>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="W11" s="8" t="n">
+        <v>655.1</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>30.3</v>
+        <v>29</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>3.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1452,76 +1424,76 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>418.2</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="E12" s="10" t="n">
+        <v>141824</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="N12" s="8" t="n">
+        <v>220.3</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>197</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="T12" s="3" t="n">
+        <v>1958</v>
+      </c>
+      <c r="U12" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G12" s="10" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H12" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="J12" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K12" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>21.3</v>
-      </c>
-      <c r="M12" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="N12" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="O12" s="3" t="n">
-        <v>97</v>
-      </c>
-      <c r="P12" s="3" t="n">
-        <v>67.2</v>
-      </c>
-      <c r="Q12" s="3" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="R12" s="3" t="n">
-        <v>24.3</v>
-      </c>
-      <c r="S12" s="3" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="T12" s="3" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="U12" s="3" t="n">
-        <v>13</v>
-      </c>
-      <c r="V12" s="3" t="n">
-        <v>26.4</v>
+      <c r="V12" s="8" t="n">
+        <v>29.6</v>
       </c>
       <c r="W12" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X12" s="12" t="n">
-        <v>72.8</v>
+        <v>25.6</v>
+      </c>
+      <c r="X12" s="8" t="n">
+        <v>30.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>80.8</v>
+        <v>713.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>6.6</v>
+        <v>11.1</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1537,76 +1509,74 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2362.1</v>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>92.09999999999999</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>17.8</v>
+        <v>1230.1</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>19.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="J13" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="M13" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="N13" s="3" t="n">
-        <v>24.6</v>
+      <c r="K13" s="8" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="L13" s="8" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="M13" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>24.7</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>998</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Q13" s="12" t="n">
-        <v>72.3</v>
-      </c>
-      <c r="R13" s="3" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="S13" s="3" t="n">
-        <v>28.2</v>
+        <v>197</v>
+      </c>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="8" t="n">
+        <v>229.1</v>
+      </c>
+      <c r="R13" s="8" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="S13" s="8" t="n">
+        <v>27.3</v>
       </c>
       <c r="T13" s="3" t="n">
+        <v>167.9</v>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W13" s="3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X13" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="U13" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="V13" s="3" t="n">
-        <v>26</v>
-      </c>
-      <c r="W13" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>28.6</v>
-      </c>
       <c r="Y13" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>5</v>
+        <v>16.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1622,80 +1592,76 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-1
-</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="H14" s="3" t="n">
-        <v>1.4</v>
+        <v>1821.4</v>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>17.8</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="K14" s="12" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>13.5</v>
+        <v>18.6</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>41.1</v>
       </c>
       <c r="M14" s="3" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="N14" s="3" t="n">
-        <v>22.4</v>
+        <v>20.9</v>
+      </c>
+      <c r="N14" s="8" t="n">
+        <v>24.6</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>9.6</v>
+        <v>198</v>
       </c>
       <c r="P14" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q14" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="R14" s="3" t="n">
-        <v>25.6</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q14" s="8" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="R14" s="8" t="n">
+        <v>24.8</v>
       </c>
       <c r="S14" s="3" t="n">
-        <v>30</v>
+        <v>28.2</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>41</v>
+        <v>77.8</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>12.3</v>
+        <v>18.1</v>
       </c>
       <c r="V14" s="3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W14" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>24.3</v>
+        <v>24</v>
+      </c>
+      <c r="X14" s="8" t="n">
+        <v>28.6</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>76.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1713,74 +1679,74 @@
       <c r="C15" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D15" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>54.5</v>
+      <c r="D15" s="12" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>12.1</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>92.09999999999999</v>
+        <v>17.4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>2.5</v>
+        <v>94.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="K15" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L15" s="12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M15" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="N15" s="12" t="n">
-        <v>33.7</v>
+        <v>4</v>
+      </c>
+      <c r="K15" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="M15" s="8" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="N15" s="8" t="n">
+        <v>22.4</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>496</v>
+        <v>199</v>
       </c>
       <c r="P15" s="3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q15" s="12" t="n">
-        <v>51.4</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q15" s="8" t="n">
+        <v>30</v>
       </c>
       <c r="R15" s="3" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="S15" s="3" t="n">
-        <v>42.7</v>
+        <v>25.6</v>
+      </c>
+      <c r="S15" s="8" t="n">
+        <v>30</v>
       </c>
       <c r="T15" s="3" t="n">
-        <v>331</v>
+        <v>71</v>
       </c>
       <c r="U15" s="3" t="n">
-        <v>76.3</v>
-      </c>
-      <c r="V15" s="12" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="W15" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X15" s="3" t="n">
-        <v>75.8</v>
+        <v>12.3</v>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="W15" s="8" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="X15" s="8" t="n">
+        <v>24.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>386.1</v>
+        <v>16.6</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>42.4</v>
+        <v>17.4</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1795,77 +1761,57 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="n">
-        <v>1530.8</v>
-      </c>
-      <c r="D16" s="13" t="n">
-        <v>54.5</v>
-      </c>
-      <c r="E16" s="13" t="n">
-        <v>199.2</v>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="G16" s="11" t="n">
-        <v>10.7</v>
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="9" t="inlineStr"/>
+      <c r="E16" s="11" t="n">
+        <v>99.7</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>15.4</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>18.4</v>
+        <v>192.1</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>32.9</v>
+        <v>19.7</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>206.6</v>
-      </c>
-      <c r="M16" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="N16" s="3" t="n">
-        <v>23.8</v>
-      </c>
+        <v>186.4</v>
+      </c>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr"/>
+      <c r="N16" s="3" t="inlineStr"/>
       <c r="O16" s="3" t="n">
-        <v>98</v>
+        <v>1490</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0</v>
+        <v>21.2</v>
       </c>
       <c r="Q16" s="3" t="n">
-        <v>3606.5</v>
-      </c>
-      <c r="R16" s="3" t="n">
-        <v>25.1</v>
-      </c>
-      <c r="S16" s="3" t="n">
-        <v>28.5</v>
-      </c>
+        <v>152.4</v>
+      </c>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr"/>
       <c r="T16" s="3" t="n">
-        <v>66.8</v>
+        <v>1331</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="V16" s="3" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>28</v>
-      </c>
+        <v>176.3</v>
+      </c>
+      <c r="V16" s="3" t="inlineStr"/>
+      <c r="W16" s="3" t="inlineStr"/>
+      <c r="X16" s="3" t="inlineStr"/>
       <c r="Y16" s="3" t="n">
-        <v>725.6</v>
+        <v>1386.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>8.5</v>
+        <v>42.3</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1881,76 +1827,72 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>606.4</v>
-      </c>
-      <c r="D17" s="13" t="n">
+        <v>306.2</v>
+      </c>
+      <c r="D17" s="12" t="n">
         <v>30.8</v>
       </c>
-      <c r="E17" s="13" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>25.7</v>
-      </c>
-      <c r="G17" s="3" t="n">
-        <v>13</v>
+      <c r="E17" s="12" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>10.9</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>17.5</v>
+        <v>18.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>4.5</v>
+        <v>23.5</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0.1</v>
-      </c>
+        <v>3.9</v>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
       <c r="L17" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="M17" s="12" t="n">
-        <v>39.4</v>
+        <v>20.6</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>20.4</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>22.3</v>
+        <v>23.8</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>41</v>
+        <v>198</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>6.7</v>
+        <v>10.4</v>
       </c>
       <c r="Q17" s="3" t="n">
-        <v>32.2</v>
+        <v>90.5</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="S17" s="3" t="n">
-        <v>27.8</v>
+        <v>25.8</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>58</v>
+        <v>166.2</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="V17" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="W17" s="3" t="n">
-        <v>25.1</v>
-      </c>
+        <v>15.3</v>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="W17" s="3" t="inlineStr"/>
       <c r="X17" s="3" t="n">
-        <v>6.1</v>
+        <v>28</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>11.6</v>
+        <v>1717.2</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>8.6</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1966,76 +1908,76 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>336.5</v>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H18" s="3" t="n">
-        <v>18.8</v>
+        <v>332.5</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>67.2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>2.1</v>
+        <v>20.4</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>42.1</v>
+        <v>14</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>8.4</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="M18" s="3" t="n">
-        <v>20.7</v>
+        <v>19.7</v>
+      </c>
+      <c r="M18" s="8" t="n">
+        <v>89.40000000000001</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>24.3</v>
+        <v>22.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>98</v>
+        <v>197</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>15.4</v>
-      </c>
-      <c r="Q18" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="R18" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q18" s="8" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="R18" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="S18" s="3" t="n">
-        <v>28.2</v>
+      <c r="S18" s="8" t="n">
+        <v>27.8</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="U18" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="V18" s="3" t="n">
-        <v>25.2</v>
+        <v>158</v>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v>28.3</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="X18" s="3" t="n">
-        <v>29.2</v>
+        <v>25.1</v>
+      </c>
+      <c r="X18" s="8" t="n">
+        <v>229.8</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>88.5</v>
+        <v>177.6</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>3.8</v>
+        <v>8.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2051,76 +1993,76 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>299</v>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="G19" s="10" t="n">
-        <v>10</v>
+        <v>1326.2</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>11.7</v>
       </c>
       <c r="H19" s="3" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="L19" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M19" s="8" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="N19" s="8" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>198</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q19" s="8" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="R19" s="8" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="S19" s="8" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="U19" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="I19" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M19" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="N19" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="O19" s="3" t="n">
-        <v>93</v>
-      </c>
-      <c r="P19" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Q19" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R19" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="S19" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="T19" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="U19" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="V19" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="W19" s="3" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="X19" s="3" t="n">
-        <v>26.3</v>
+      <c r="V19" s="8" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="W19" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="X19" s="8" t="n">
+        <v>29.2</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>83</v>
+        <v>188.5</v>
       </c>
       <c r="Z19" s="3" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA19" s="3" t="inlineStr">
         <is>
@@ -2136,76 +2078,74 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="D20" s="10" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="F20" s="10" t="n">
-        <v>24.5</v>
+        <v>1299</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>24.7</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H20" s="3" t="n">
-        <v>6.4</v>
+        <v>10</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>18.4</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>3.8</v>
+        <v>31.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M20" s="3" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="L20" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="M20" s="8" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="n">
         <v>18.9</v>
       </c>
-      <c r="N20" s="3" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="O20" s="3" t="n">
-        <v>1006.8</v>
-      </c>
-      <c r="P20" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q20" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="R20" s="3" t="n">
-        <v>24.4</v>
+      <c r="Q20" s="8" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="R20" s="8" t="n">
+        <v>238.4</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>63.4</v>
+        <v>171.6</v>
       </c>
       <c r="U20" s="3" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="V20" s="3" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="W20" s="8" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="X20" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W20" s="12" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="X20" s="3" t="n">
-        <v>6.6</v>
-      </c>
       <c r="Y20" s="3" t="n">
-        <v>84.09999999999999</v>
+        <v>183</v>
       </c>
       <c r="Z20" s="3" t="n">
-        <v>35.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
@@ -2221,79 +2161,74 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>294.9</v>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="F21" s="10" t="n">
-        <v>29</v>
-      </c>
-      <c r="G21" s="3" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="H21" s="3" t="n">
-        <v>12.4</v>
-      </c>
+        <v>1357.5</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H21" s="3" t="inlineStr"/>
       <c r="I21" s="3" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61 1
-</t>
-        </is>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>19.1</v>
+        <v>3.8</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L21" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="N21" s="3" t="n">
-        <v>22.1</v>
+        <v>18.9</v>
+      </c>
+      <c r="N21" s="8" t="n">
+        <v>12.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="P21" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Q21" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="R21" s="3" t="n">
-        <v>25.8</v>
+        <v>1001</v>
+      </c>
+      <c r="P21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="8" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="R21" s="8" t="n">
+        <v>24.4</v>
       </c>
       <c r="S21" s="3" t="n">
-        <v>22.9</v>
+        <v>26.9</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>66.8</v>
+        <v>163.1</v>
       </c>
       <c r="U21" s="3" t="n">
-        <v>14.8</v>
+        <v>15.7</v>
       </c>
       <c r="V21" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="W21" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="X21" s="3" t="n">
-        <v>26.5</v>
+        <v>26.3</v>
+      </c>
+      <c r="W21" s="8" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="X21" s="8" t="n">
+        <v>28.8</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>88.8</v>
+        <v>184.1</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>3.3</v>
+        <v>5.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2309,76 +2244,74 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>96.09999999999999</v>
+        <v>1294.9</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>531.2</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>18.8</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="G22" s="11" t="n">
-        <v>31.6</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>88.2</v>
+        <v>4</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>17.4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>18.4</v>
-      </c>
+        <v>16.9</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr"/>
       <c r="K22" s="3" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>10.1</v>
+      </c>
+      <c r="L22" s="8" t="n">
+        <v>69.09999999999999</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>97.8</v>
+        <v>19.1</v>
       </c>
       <c r="N22" s="3" t="n">
-        <v>7.3</v>
+        <v>22.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>494</v>
-      </c>
-      <c r="P22" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Q22" s="12" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="R22" s="12" t="n">
-        <v>24.6</v>
+        <v>100</v>
+      </c>
+      <c r="P22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="8" t="n">
+        <v>31</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="S22" s="3" t="n">
-        <v>39.7</v>
+        <v>29.9</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>320</v>
+        <v>166.8</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="V22" s="12" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="W22" s="3" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="X22" s="3" t="n">
-        <v>10.6</v>
+        <v>14.8</v>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="W22" s="8" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="X22" s="8" t="n">
+        <v>216.5</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>442</v>
+        <v>88.8</v>
       </c>
       <c r="Z22" s="3" t="n">
-        <v>26.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -2393,80 +2326,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="n">
-        <v>322</v>
-      </c>
-      <c r="D23" s="13" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E23" s="13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F23" s="13" t="n">
-        <v>25.5</v>
-      </c>
+      <c r="C23" s="3" t="inlineStr"/>
+      <c r="D23" s="9" t="inlineStr"/>
+      <c r="E23" s="9" t="inlineStr"/>
+      <c r="F23" s="9" t="inlineStr"/>
       <c r="G23" s="3" t="n">
-        <v>11.9</v>
+        <v>59.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>17.6</v>
+        <v>88.2</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 2
-</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>65.09999999999999</v>
-      </c>
+        <v>10.4</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="K23" s="3" t="inlineStr"/>
       <c r="L23" s="3" t="n">
-        <v>198.5</v>
-      </c>
-      <c r="M23" s="3" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="N23" s="3" t="n">
-        <v>22.7</v>
-      </c>
+        <v>198.4</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr"/>
+      <c r="N23" s="3" t="inlineStr"/>
       <c r="O23" s="3" t="n">
-        <v>98.8</v>
-      </c>
-      <c r="P23" s="3" t="n">
-        <v>0.3</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="P23" s="3" t="inlineStr"/>
       <c r="Q23" s="3" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="R23" s="3" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="S23" s="3" t="n">
-        <v>8.800000000000001</v>
-      </c>
+        <v>1252.9</v>
+      </c>
+      <c r="R23" s="3" t="inlineStr"/>
+      <c r="S23" s="3" t="inlineStr"/>
       <c r="T23" s="3" t="n">
-        <v>64</v>
+        <v>1320</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="V23" s="3" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="W23" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X23" s="3" t="n">
-        <v>28.1</v>
-      </c>
+        <v>179.6</v>
+      </c>
+      <c r="V23" s="3" t="inlineStr"/>
+      <c r="W23" s="3" t="inlineStr"/>
+      <c r="X23" s="3" t="inlineStr"/>
       <c r="Y23" s="3" t="n">
-        <v>84.40000000000001</v>
+        <v>422</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>2.2</v>
+        <v>26.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2482,81 +2386,72 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F24" s="10" t="n">
+        <v>322</v>
+      </c>
+      <c r="D24" s="12" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="inlineStr"/>
+      <c r="L24" s="8" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>988.1</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="R24" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G24" s="10" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="H24" s="3" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="I24" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3 2
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>351.6</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74
-15156
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="O24" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P24" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="Q24" s="3" t="n"/>
-      <c r="R24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="S24" s="3" t="n">
-        <v>0.1</v>
+      <c r="S24" s="8" t="n">
+        <v>27.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>0.1</v>
+        <v>164</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>0.4</v>
+        <v>15.9</v>
       </c>
       <c r="V24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="W24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X24" s="3" t="n">
-        <v>0.1</v>
+        <v>25.9</v>
+      </c>
+      <c r="W24" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X24" s="8" t="n">
+        <v>28.1</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>0.1</v>
+        <v>184.4</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>1.1</v>
+        <v>55.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2572,76 +2467,74 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F25" s="10" t="n">
-        <v>26.1</v>
-      </c>
-      <c r="G25" s="10" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H25" s="3" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H25" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="I25" s="3" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="I25" s="3" t="inlineStr"/>
       <c r="J25" s="3" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>14.4</v>
+        <v>17.6</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M25" s="12" t="n">
-        <v>39.8</v>
-      </c>
-      <c r="N25" s="12" t="n">
+      <c r="M25" s="3" t="n">
+        <v>194.4</v>
+      </c>
+      <c r="N25" s="8" t="n">
         <v>22.9</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>0.4</v>
+        <v>10.4</v>
       </c>
       <c r="Q25" s="3" t="n">
-        <v>6.9</v>
+        <v>22.9</v>
       </c>
       <c r="R25" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="S25" s="3" t="n">
+      <c r="S25" s="8" t="n">
         <v>26.1</v>
       </c>
       <c r="T25" s="3" t="n">
-        <v>23.6</v>
+        <v>93.2</v>
       </c>
       <c r="U25" s="3" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="W25" s="8" t="n">
+        <v>21</v>
+      </c>
+      <c r="X25" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="Z25" s="3" t="n">
         <v>1.8</v>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="W25" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="X25" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="Y25" s="3" t="n">
-        <v>952.6</v>
-      </c>
-      <c r="Z25" s="3" t="n">
-        <v>0.1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2657,43 +2550,41 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>345</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="F26" s="11" t="n">
-        <v>68.61</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>3.1</v>
-      </c>
+        <v>2345</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr"/>
       <c r="J26" s="3" t="n">
-        <v>4.4</v>
+        <v>14.4</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>26.6</v>
+        <v>20.6</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>26.4</v>
+        <v>20.4</v>
       </c>
       <c r="N26" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>98</v>
+        <v>198</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0.4</v>
@@ -2701,7 +2592,7 @@
       <c r="Q26" s="3" t="n">
         <v>31.4</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2710,23 +2601,23 @@
       <c r="T26" s="3" t="n">
         <v>55.2</v>
       </c>
-      <c r="U26" s="12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="V26" s="3" t="n">
-        <v>22.2</v>
-      </c>
-      <c r="W26" s="3" t="n">
+      <c r="U26" s="3" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="W26" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>26.8</v>
+        <v>62.1</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>4.3</v>
+        <v>174.3</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>4.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2742,31 +2633,29 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>32.6</v>
+        <v>2418.2</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>32.9</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>26.8</v>
+        <v>5.4</v>
+      </c>
+      <c r="F27" s="8" t="n">
+        <v>86.09999999999999</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>12.8</v>
+        <v>13.7</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="I27" s="3" t="n">
-        <v>1.9</v>
-      </c>
+        <v>17.6</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr"/>
       <c r="J27" s="3" t="n">
-        <v>52.4</v>
+        <v>5.9</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>19.6</v>
@@ -2774,26 +2663,26 @@
       <c r="M27" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N27" s="3" t="n">
+      <c r="N27" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>994</v>
+        <v>199</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>32.9</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="S27" s="3" t="n">
+      <c r="S27" s="8" t="n">
         <v>26.4</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>23.4</v>
@@ -2801,17 +2690,17 @@
       <c r="V27" s="3" t="n">
         <v>29.3</v>
       </c>
-      <c r="W27" s="3" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="X27" s="3" t="n">
+      <c r="W27" s="8" t="n">
+        <v>95.5</v>
+      </c>
+      <c r="X27" s="8" t="n">
         <v>30.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>0.2</v>
+        <v>174.2</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>4.3</v>
+        <v>110.5</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2829,74 +2718,74 @@
       <c r="C28" s="3" t="n">
         <v>282.3</v>
       </c>
-      <c r="D28" s="11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E28" s="3" t="n">
+      <c r="D28" s="12" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="E28" s="12" t="n">
         <v>19.8</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H28" s="3" t="n">
-        <v>190.8</v>
+      <c r="F28" s="12" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>18.4</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>1.1</v>
+        <v>11.9</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>18.1</v>
+        <v>12.6</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M28" s="12" t="n">
-        <v>29.9</v>
+      <c r="M28" s="3" t="n">
+        <v>49.9</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>23.1</v>
+        <v>33.4</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>38</v>
+        <v>198</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q28" s="3" t="n">
-        <v>29.2</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q28" s="8" t="n">
+        <v>29.7</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="S28" s="3" t="n">
+      <c r="S28" s="8" t="n">
         <v>28.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>69.40000000000001</v>
+        <v>169.4</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="V28" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="W28" s="3" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v>224.4</v>
+      </c>
+      <c r="W28" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="X28" s="3" t="n">
-        <v>26.3</v>
+      <c r="X28" s="8" t="n">
+        <v>260.3</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>5.8</v>
+        <v>14.3</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2912,76 +2801,76 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>140.2</v>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>80.3</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>24.7</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>5.2</v>
+        <v>120.2</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>8.9</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2.2</v>
+        <v>19</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>93.90000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>23.7</v>
+        <v>18.1</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="N29" s="3" t="n">
+      <c r="N29" s="8" t="n">
         <v>25.4</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>96.5</v>
+        <v>196.5</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="Q29" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="Q29" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="S29" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>3.7</v>
+        <v>173.7</v>
       </c>
       <c r="U29" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="V29" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="W29" s="3" t="n">
+      <c r="V29" s="8" t="n">
+        <v>35</v>
+      </c>
+      <c r="W29" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="X29" s="3" t="n">
+      <c r="X29" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>21.6</v>
+        <v>181.8</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>30.2</v>
+        <v>5.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2996,81 +2885,51 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>1363.5</v>
-      </c>
-      <c r="D30" s="13" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="E30" s="13" t="n">
-        <v>996.1</v>
-      </c>
-      <c r="F30" s="13" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>1.4</v>
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="9" t="inlineStr"/>
+      <c r="E30" s="9" t="inlineStr"/>
+      <c r="F30" s="9" t="inlineStr"/>
+      <c r="G30" s="10" t="n">
+        <v>50.7</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.4</v>
+        <v>192.2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>2</v>
+        <v>9.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>172.1</v>
+        <v>16.7</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="M30" s="3" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="N30" s="3" t="n">
-        <v>172.8</v>
-      </c>
+        <v>123.7</v>
+      </c>
+      <c r="L30" s="3" t="inlineStr"/>
+      <c r="M30" s="3" t="inlineStr"/>
+      <c r="N30" s="3" t="inlineStr"/>
       <c r="O30" s="3" t="n">
-        <v>429.5</v>
+        <v>1489.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Q30" s="3" t="n">
-        <v>145.5</v>
-      </c>
-      <c r="R30" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="S30" s="3" t="n">
-        <v>3.3</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr"/>
+      <c r="S30" s="3" t="inlineStr"/>
       <c r="T30" s="3" t="n">
-        <v>344.5</v>
+        <v>1344.5</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>68.8</v>
-      </c>
-      <c r="V30" s="3" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="W30" s="3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="X30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-4
-</t>
-        </is>
-      </c>
+        <v>168.8</v>
+      </c>
+      <c r="V30" s="3" t="inlineStr"/>
+      <c r="W30" s="3" t="inlineStr"/>
+      <c r="X30" s="3" t="inlineStr"/>
       <c r="Y30" s="3" t="n">
-        <v>11.5</v>
+        <v>1411.5</v>
       </c>
       <c r="Z30" s="3" t="n">
-        <v>0.4</v>
+        <v>30.9</v>
       </c>
       <c r="AA30" s="3" t="inlineStr">
         <is>
@@ -3088,82 +2947,72 @@
       <c r="C31" s="3" t="n">
         <v>272.7</v>
       </c>
-      <c r="D31" s="13" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="E31" s="13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="F31" s="13" t="n">
-        <v>16</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H31" s="3" t="n">
-        <v>19.4</v>
+      <c r="D31" s="12" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G31" s="8" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>88.40000000000001</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>1.3</v>
+        <v>20.1</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="K31" s="3" t="n">
-        <v>34.1</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="M31" s="3" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="N31" s="3" t="n">
+      <c r="K31" s="3" t="inlineStr"/>
+      <c r="L31" s="8" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="M31" s="8" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="N31" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>978.9</v>
+        <v>197.9</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q31" s="12" t="n">
-        <v>39.1</v>
-      </c>
-      <c r="R31" s="12" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="S31" s="3" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="T31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6 89
-</t>
-        </is>
+        <v>10.2</v>
+      </c>
+      <c r="Q31" s="8" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="R31" s="8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S31" s="8" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>168.9</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>13.8</v>
+        <v>63.8</v>
       </c>
       <c r="V31" s="3" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="W31" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="X31" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1141
-22
-171971191 7
-</t>
-        </is>
+        <v>255.1</v>
+      </c>
+      <c r="W31" s="8" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="X31" s="8" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>181.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>6.1</v>
+        <v>16.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3179,81 +3028,74 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>263.5</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="E32" s="3" t="n">
+        <v>1263.5</v>
+      </c>
+      <c r="D32" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="E32" s="12" t="n">
         <v>20.4</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="12" t="n">
         <v>24.7</v>
       </c>
-      <c r="G32" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>19</v>
+      <c r="G32" s="12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>2.4</v>
-      </c>
+        <v>16.3</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr"/>
       <c r="K32" s="3" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="M32" s="3" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="M32" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="N32" s="3" t="n">
+      <c r="N32" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>99</v>
+        <v>990.1</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="Q32" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="S32" s="3" t="n">
-        <v>22.9</v>
+      <c r="S32" s="8" t="n">
+        <v>27.9</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>69.8</v>
+        <v>169.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="V32" s="12" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="W32" s="3" t="n">
+      <c r="V32" s="8" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="W32" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="X32" s="3" t="n">
-        <v>25.8</v>
+      <c r="X32" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1717177
-23
-83
-</t>
-        </is>
+        <v>181.1</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>16.7</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3269,76 +3111,72 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>44.1</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F33" s="10" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="G33" s="10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="H33" s="3" t="n">
-        <v>17.8</v>
+        <v>144.1</v>
+      </c>
+      <c r="D33" s="12" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F33" s="12" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>129</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>1.3</v>
-      </c>
+        <v>10.5</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr"/>
       <c r="K33" s="3" t="n">
-        <v>5.9</v>
+        <v>14.5</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>2.1</v>
+        <v>20.8</v>
       </c>
       <c r="M33" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="N33" s="3" t="n">
+      <c r="N33" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="O33" s="3" t="n">
-        <v>980.8</v>
-      </c>
-      <c r="P33" s="3" t="n">
-        <v>20.4</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="P33" s="3" t="inlineStr"/>
       <c r="Q33" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="S33" s="3" t="n">
-        <v>1.5</v>
+      <c r="S33" s="8" t="n">
+        <v>25.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>183.4</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="V33" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="V33" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="W33" s="3" t="n">
+      <c r="W33" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="X33" s="3" t="n">
-        <v>21.4</v>
+      <c r="X33" s="8" t="n">
+        <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>28.7</v>
+        <v>191.8</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>12.8</v>
+        <v>2.3</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3354,79 +3192,74 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="D34" s="11" t="n">
-        <v>92.5</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="F34" s="11" t="n">
-        <v>43.9</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>13.6</v>
+        <v>1117.8</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F34" s="12" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>167.8</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v>0.2</v>
-      </c>
+        <v>11.9</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr"/>
       <c r="K34" s="3" t="n">
-        <v>2.8</v>
+        <v>5.9</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="M34" s="12" t="n">
-        <v>61.2</v>
+        <v>20.1</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>980.8</v>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 20
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="3" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="R34" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q34" s="8" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="R34" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>76.2</v>
+        <v>70.2</v>
       </c>
       <c r="U34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V34" s="12" t="n">
-        <v>63.5</v>
-      </c>
-      <c r="W34" s="3" t="n">
+      <c r="V34" s="8" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="W34" s="8" t="n">
         <v>21</v>
       </c>
       <c r="X34" s="3" t="n">
-        <v>29.3</v>
+        <v>21.4</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>62.5</v>
+        <v>162.5</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>4.9</v>
+        <v>12.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3442,64 +3275,56 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>284.4</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>28.6</v>
-      </c>
-      <c r="E35" s="3" t="n">
+        <v>1284.4</v>
+      </c>
+      <c r="D35" s="12" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E35" s="12" t="n">
         <v>18.8</v>
       </c>
-      <c r="F35" s="3" t="n">
+      <c r="F35" s="12" t="n">
         <v>24.1</v>
       </c>
-      <c r="G35" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>19</v>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 6
-</t>
-        </is>
+      <c r="G35" s="12" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13 72
-</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>21.9</v>
-      </c>
-      <c r="M35" s="3" t="n">
-        <v>0.4</v>
-      </c>
+        <v>16.8</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L35" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr"/>
       <c r="N35" s="3" t="n">
-        <v>25.8</v>
+        <v>243.1</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>100</v>
+        <v>1100</v>
       </c>
       <c r="P35" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q35" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="8" t="n">
         <v>24.8</v>
       </c>
-      <c r="S35" s="3" t="n">
+      <c r="S35" s="8" t="n">
         <v>29</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>275.4</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>9.4</v>
@@ -3511,13 +3336,13 @@
         <v>24.4</v>
       </c>
       <c r="X35" s="3" t="n">
-        <v>24.2</v>
+        <v>29.3</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>1.3</v>
+        <v>14.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3533,41 +3358,31 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>117.2</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F36" s="11" t="n">
-        <v>43.9</v>
+        <v>1117.2</v>
+      </c>
+      <c r="D36" s="12" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <v>24.9</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222725
-1142811042
-</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0 6
-</t>
-        </is>
+        <v>72.5</v>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>0.6</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13 72
-</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>16.3</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>21.9</v>
@@ -3575,14 +3390,14 @@
       <c r="M36" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="N36" s="3" t="n">
-        <v>20.9</v>
+      <c r="N36" s="8" t="n">
+        <v>25.8</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>28</v>
+        <v>198</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>6.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>21.5</v>
@@ -3594,25 +3409,25 @@
         <v>24.3</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>94.8</v>
+        <v>194.8</v>
       </c>
       <c r="U36" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="V36" s="12" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="W36" s="3" t="n">
+      <c r="V36" s="8" t="n">
+        <v>21.4</v>
+      </c>
+      <c r="W36" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="X36" s="3" t="n">
+      <c r="X36" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>4.8</v>
+        <v>94.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3628,79 +3443,52 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="D37" s="13" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="E37" s="13" t="n">
-        <v>60</v>
-      </c>
-      <c r="F37" s="13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>42.9</v>
+        <v>826.4</v>
+      </c>
+      <c r="D37" s="9" t="inlineStr"/>
+      <c r="E37" s="9" t="inlineStr"/>
+      <c r="F37" s="9" t="inlineStr"/>
+      <c r="G37" s="10" t="n">
+        <v>14.3</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>92.40000000000001</v>
-      </c>
+        <v>15.8</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr"/>
       <c r="K37" s="3" t="n">
-        <v>17.3</v>
+        <v>117.9</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>1034.4</v>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">777
-22
-7
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="O37" s="3" t="n">
-        <v>425</v>
-      </c>
+        <v>103.4</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr"/>
+      <c r="N37" s="3" t="inlineStr"/>
+      <c r="O37" s="3" t="inlineStr"/>
       <c r="P37" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>1334.1</v>
-      </c>
-      <c r="R37" s="3" t="n">
-        <v>117.9</v>
-      </c>
-      <c r="S37" s="3" t="n">
-        <v>86.3</v>
-      </c>
+        <v>133.1</v>
+      </c>
+      <c r="R37" s="3" t="inlineStr"/>
+      <c r="S37" s="3" t="inlineStr"/>
       <c r="T37" s="3" t="n">
         <v>393.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>40.4</v>
-      </c>
-      <c r="V37" s="3" t="n">
-        <v>124.1</v>
-      </c>
-      <c r="W37" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="X37" s="3" t="n"/>
+        <v>140.4</v>
+      </c>
+      <c r="V37" s="3" t="inlineStr"/>
+      <c r="W37" s="3" t="inlineStr"/>
+      <c r="X37" s="3" t="inlineStr"/>
       <c r="Y37" s="3" t="n">
-        <v>416</v>
+        <v>1416</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>0.7</v>
+        <v>128</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3716,71 +3504,69 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>165.3</v>
-      </c>
-      <c r="D38" s="10" t="n">
+        <v>163.3</v>
+      </c>
+      <c r="D38" s="12" t="n">
         <v>28.6</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E38" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F38" s="10" t="n">
+      <c r="F38" s="12" t="n">
         <v>24.3</v>
       </c>
-      <c r="G38" s="10" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H38" s="3" t="n">
-        <v>18.6</v>
+      <c r="G38" s="12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>68.59999999999999</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K38" s="3" t="n"/>
+        <v>12.2</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr"/>
+      <c r="K38" s="3" t="inlineStr"/>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>61.3</v>
+        <v>20</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P38" s="3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Q38" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q38" s="8" t="n">
         <v>26.6</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="S38" s="3" t="n">
-        <v>73.5</v>
+      <c r="S38" s="8" t="n">
+        <v>927.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="U38" s="3" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="V38" s="3" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="W38" s="3" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="X38" s="3" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v>811.1</v>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="W38" s="8" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X38" s="8" t="n">
         <v>26</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>8324.799999999999</v>
+        <v>1839.2</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>5.6</v>
@@ -3799,78 +3585,76 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="D39" s="10" t="n">
-        <v>40.7</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="F39" s="10" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="D39" s="8" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="F39" s="3" t="n">
         <v>25</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="H39" s="3" t="n">
-        <v>18</v>
+      <c r="H39" s="8" t="n">
+        <v>8</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="K39" s="3" t="n"/>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7 29
-15
-</t>
-        </is>
+        <v>93.5</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>19.5</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>10.6</v>
+        <v>19.2</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>72.59999999999999</v>
+        <v>22.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>99</v>
+        <v>1100</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q39" s="3" t="n">
-        <v>10.1</v>
+        <v>10</v>
+      </c>
+      <c r="Q39" s="8" t="n">
+        <v>130.7</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="S39" s="3" t="n">
-        <v>89.3</v>
+        <v>29.3</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>666.1</v>
-      </c>
-      <c r="U39" s="12" t="n">
-        <v>42.7</v>
-      </c>
-      <c r="V39" s="3" t="n">
-        <v>61.2</v>
+        <v>166.5</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v>27.8</v>
       </c>
       <c r="W39" s="3" t="n">
-        <v>83.09999999999999</v>
-      </c>
-      <c r="X39" s="3" t="n">
-        <v>22.6</v>
+        <v>23.9</v>
+      </c>
+      <c r="X39" s="8" t="n">
+        <v>27.2</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>2.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>6.1</v>
+        <v>106.1</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3886,71 +3670,73 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>28.1</v>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>44.8</v>
+        <v>278.1</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <v>30.8</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="F40" s="10" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>25.7</v>
       </c>
-      <c r="G40" s="3" t="n">
+      <c r="G40" s="12" t="n">
         <v>10.2</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K40" s="3" t="n"/>
+        <v>3.1</v>
+      </c>
+      <c r="K40" s="8" t="n">
+        <v>0.4</v>
+      </c>
       <c r="L40" s="3" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="N40" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="N40" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>990.6</v>
+        <v>99</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q40" s="3" t="n">
-        <v>36.7</v>
-      </c>
-      <c r="R40" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q40" s="8" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="R40" s="8" t="n">
         <v>25.3</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>65.40000000000001</v>
+        <v>165.4</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="8" t="n">
         <v>28</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X40" s="3" t="n">
+      <c r="X40" s="8" t="n">
         <v>27.3</v>
       </c>
       <c r="Y40" s="3" t="n">
-        <v>0.1</v>
+        <v>72.2</v>
       </c>
       <c r="Z40" s="3" t="n">
         <v>10.4</v>
@@ -3971,78 +3757,74 @@
       <c r="C41" s="3" t="n">
         <v>242.6</v>
       </c>
-      <c r="D41" s="11" t="n">
-        <v>99.59999999999999</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="F41" s="10" t="n">
+      <c r="D41" s="12" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="E41" s="12" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F41" s="12" t="n">
         <v>25.2</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>18.8</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="I41" s="3" t="n">
-        <v>1.5</v>
+      <c r="I41" s="8" t="n">
+        <v>18.5</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>21</v>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">442
-111
-</t>
-        </is>
+        <v>16.9</v>
+      </c>
+      <c r="L41" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="M41" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>98.8</v>
+        <v>193.8</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q41" s="3" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="R41" s="3" t="n">
+      <c r="Q41" s="8" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="R41" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="S41" s="3" t="n">
+      <c r="S41" s="8" t="n">
         <v>28.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="U41" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="V41" s="3" t="n">
-        <v>22.1</v>
+        <v>720.5</v>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v>27.1</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="X41" s="3" t="n">
-        <v>22.1</v>
+        <v>645.1</v>
+      </c>
+      <c r="X41" s="8" t="n">
+        <v>29.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>24.4</v>
+        <v>1841.1</v>
       </c>
       <c r="Z41" s="3" t="n">
-        <v>6.7</v>
+        <v>16.7</v>
       </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
@@ -4060,74 +3842,74 @@
       <c r="C42" s="3" t="n">
         <v>288.6</v>
       </c>
-      <c r="D42" s="10" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="F42" s="10" t="n">
+      <c r="D42" s="12" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="E42" s="12" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F42" s="12" t="n">
         <v>25.6</v>
       </c>
-      <c r="G42" s="3" t="n">
+      <c r="G42" s="12" t="n">
         <v>10.5</v>
       </c>
-      <c r="H42" s="3" t="n">
-        <v>18.6</v>
+      <c r="H42" s="8" t="n">
+        <v>188.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>1.5</v>
+        <v>16.6</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
+      </c>
+      <c r="K42" s="8" t="n">
+        <v>0.4</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>24.4</v>
-      </c>
-      <c r="N42" s="12" t="n">
-        <v>52.8</v>
+        <v>21.2</v>
+      </c>
+      <c r="M42" s="8" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="N42" s="3" t="n">
+        <v>25.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>10618.2</v>
+        <v>1600</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q42" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="S42" s="3" t="n">
+      <c r="S42" s="8" t="n">
         <v>27.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>68</v>
-      </c>
-      <c r="U42" s="3" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="V42" s="3" t="n">
-        <v>0.4</v>
+        <v>162</v>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v>207.1</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X42" s="3" t="n">
-        <v>29.3</v>
+      <c r="X42" s="8" t="n">
+        <v>239.3</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>0.2</v>
+        <v>181.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>6.5</v>
+        <v>16.5</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4143,74 +3925,74 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>311.6</v>
-      </c>
-      <c r="D43" s="10" t="n">
+        <v>2311.6</v>
+      </c>
+      <c r="D43" s="12" t="n">
         <v>30.8</v>
       </c>
-      <c r="E43" s="10" t="n">
-        <v>21.6</v>
-      </c>
-      <c r="F43" s="10" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G43" s="3" t="n">
+      <c r="E43" s="12" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F43" s="12" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G43" s="12" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H43" s="3" t="n">
+      <c r="H43" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="I43" s="3" t="n">
-        <v>1.6</v>
-      </c>
+      <c r="I43" s="3" t="inlineStr"/>
       <c r="J43" s="3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.2</v>
+        <v>3.9</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M43" s="3" t="n"/>
-      <c r="N43" s="3" t="n">
+      <c r="M43" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="N43" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q43" s="3" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="Q43" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="S43" s="3" t="n">
+      <c r="R43" s="8" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="S43" s="8" t="n">
         <v>24</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>726</v>
+        <v>17</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>24</v>
+        <v>24.8</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>2.9</v>
+        <v>22</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>95.09999999999999</v>
+        <v>35.4</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>84.3</v>
+        <v>184.3</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>4.6</v>
+        <v>14.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4225,80 +4007,30 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n">
-        <v>311.6</v>
-      </c>
-      <c r="D44" s="11" t="n">
-        <v>71.5</v>
-      </c>
-      <c r="E44" s="11" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="F44" s="10" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="G44" s="11" t="n">
-        <v>546.5</v>
-      </c>
-      <c r="H44" s="12" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42424
-211
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="n"/>
-      <c r="K44" s="3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-111562
-</t>
-        </is>
-      </c>
-      <c r="N44" s="12" t="n">
-        <v>81.09999999999999</v>
-      </c>
-      <c r="O44" s="3" t="n"/>
-      <c r="P44" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q44" s="12" t="n">
-        <v>46.3</v>
-      </c>
-      <c r="R44" s="12" t="n">
-        <v>373.3</v>
-      </c>
-      <c r="S44" s="3" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="T44" s="3" t="n">
-        <v>726</v>
-      </c>
-      <c r="U44" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V44" s="3" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="W44" s="3" t="n">
-        <v>79.7</v>
-      </c>
-      <c r="X44" s="12" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="Y44" s="3" t="n">
-        <v>3242.3</v>
-      </c>
-      <c r="Z44" s="3" t="n"/>
+      <c r="C44" s="3" t="inlineStr"/>
+      <c r="D44" s="3" t="inlineStr"/>
+      <c r="E44" s="3" t="inlineStr"/>
+      <c r="F44" s="3" t="inlineStr"/>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr"/>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -4313,72 +4045,54 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1453.4</v>
-      </c>
-      <c r="D45" s="13" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="E45" s="13" t="n">
-        <v>779.7</v>
-      </c>
-      <c r="F45" s="13" t="n">
-        <v>127.4</v>
-      </c>
+        <v>1722.7</v>
+      </c>
+      <c r="D45" s="9" t="inlineStr"/>
+      <c r="E45" s="9" t="inlineStr"/>
+      <c r="F45" s="9" t="inlineStr"/>
       <c r="G45" s="3" t="n">
-        <v>50.6</v>
+        <v>6.1</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>93.59999999999999</v>
+        <v>293.6</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>45.9</v>
-      </c>
-      <c r="K45" s="3" t="n"/>
-      <c r="L45" s="3" t="n">
-        <v>113.8</v>
-      </c>
-      <c r="M45" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N45" s="3" t="n">
-        <v>4.4</v>
-      </c>
+        <v>164.9</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="L45" s="3" t="inlineStr"/>
+      <c r="M45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr"/>
       <c r="O45" s="3" t="n">
-        <v>494.2</v>
-      </c>
-      <c r="P45" s="3" t="n"/>
+        <v>191.8</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>16.9</v>
+      </c>
       <c r="Q45" s="3" t="n">
-        <v>146.3</v>
-      </c>
-      <c r="R45" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v>78.09999999999999</v>
-      </c>
+        <v>146.2</v>
+      </c>
+      <c r="R45" s="3" t="inlineStr"/>
+      <c r="S45" s="3" t="inlineStr"/>
       <c r="T45" s="3" t="n">
         <v>341.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="V45" s="3" t="n">
-        <v>71.7</v>
-      </c>
-      <c r="W45" s="3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X45" s="3" t="n">
-        <v>27.6</v>
-      </c>
+        <v>1668</v>
+      </c>
+      <c r="V45" s="3" t="inlineStr"/>
+      <c r="W45" s="3" t="inlineStr"/>
+      <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>3242.3</v>
+        <v>992.3</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>38.3</v>
+        <v>198.5</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4396,74 +4110,72 @@
       <c r="C46" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D46" s="10" t="n">
-        <v>30.6</v>
-      </c>
-      <c r="E46" s="10" t="n">
+      <c r="D46" s="12" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E46" s="12" t="n">
         <v>20.5</v>
       </c>
-      <c r="F46" s="10" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="G46" s="10" t="n">
+      <c r="F46" s="12" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="G46" s="12" t="n">
         <v>10.1</v>
       </c>
-      <c r="H46" s="3" t="n">
+      <c r="H46" s="8" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="I46" s="3" t="n">
         <v>18.7</v>
-      </c>
-      <c r="I46" s="3" t="n">
-        <v>1.7</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K46" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="L46" s="12" t="n">
-        <v>68.40000000000001</v>
-      </c>
-      <c r="M46" s="3" t="n">
-        <v>10.5</v>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="M46" s="8" t="n">
+        <v>20.6</v>
       </c>
       <c r="N46" s="3" t="n">
-        <v>4.4</v>
+        <v>24.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>98.40000000000001</v>
+        <v>198.4</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Q46" s="3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="Q46" s="8" t="n">
         <v>29.3</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="S46" s="12" t="n">
-        <v>77.2</v>
+        <v>645.1</v>
+      </c>
+      <c r="S46" s="8" t="n">
+        <v>27.7</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="U46" s="12" t="n">
-        <v>32.4</v>
+        <v>168.3</v>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v>292.2</v>
       </c>
       <c r="V46" s="3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="W46" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="X46" s="3" t="n">
-        <v>0.1</v>
+        <v>26.8</v>
+      </c>
+      <c r="W46" s="8" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="X46" s="8" t="n">
+        <v>22.6</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>8.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>2.7</v>
+        <v>7.8</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -41,12 +41,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC0CB"/>
-        <bgColor rgb="00FFC0CB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00CC3300"/>
         <bgColor rgb="00CC3300"/>
       </patternFill>
@@ -61,6 +55,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF6DCD57"/>
         <bgColor rgb="FF6DCD57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -149,7 +149,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -158,7 +158,16 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -774,75 +783,73 @@
       <c r="C4" s="3" t="n">
         <v>351.3</v>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="11" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="11" t="n">
         <v>22.7</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="11" t="n">
         <v>28.1</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="11" t="n">
         <v>10.8</v>
       </c>
-      <c r="H4" s="8" t="n">
+      <c r="H4" s="3" t="n">
         <v>21</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>21.6</v>
+        <v>2.6</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>14.4</v>
+        <v>22.1</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="N4" s="3" t="n">
-        <v>27.4</v>
+      <c r="N4" s="8" t="n">
+        <v>76.40000000000001</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>97.5</v>
       </c>
-      <c r="P4" s="8" t="n">
-        <v>1.7</v>
+      <c r="P4" s="3" t="n">
+        <v>10.7</v>
       </c>
       <c r="Q4" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="R4" s="8" t="n">
+      <c r="R4" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="S4" s="8" t="n">
-        <v>1281.1</v>
+      <c r="S4" s="3" t="n">
+        <v>28.1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>156.1</v>
-      </c>
-      <c r="U4" s="8" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="U4" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="V4" s="8" t="n">
+      <c r="V4" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="X4" s="8" t="n">
+      <c r="X4" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>174.3</v>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v>110</v>
-      </c>
+        <v>1754.3</v>
+      </c>
+      <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
           <t>1</t>
@@ -859,61 +866,61 @@
       <c r="C5" s="3" t="n">
         <v>278.1</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="E5" s="12" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F5" s="12" t="n">
+      <c r="E5" s="11" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F5" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="11" t="n">
         <v>10.3</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>1.6</v>
+        <v>11.6</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>3.1</v>
+        <v>31.1</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="L5" s="8" t="n">
+      <c r="L5" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0.5</v>
+        <v>25.4</v>
       </c>
       <c r="O5" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q5" s="8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q5" s="3" t="n">
         <v>26</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="S5" s="8" t="n">
+      <c r="S5" s="3" t="n">
         <v>26.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>118</v>
+        <v>18</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="V5" s="8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="V5" s="3" t="n">
         <v>22</v>
       </c>
       <c r="W5" s="3" t="n">
@@ -923,7 +930,7 @@
         <v>24.4</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>192</v>
+        <v>92</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>2.1</v>
@@ -942,74 +949,76 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>12368</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="E6" s="3" t="n">
+        <v>268.1</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E6" s="11" t="n">
         <v>21.1</v>
       </c>
-      <c r="F6" s="8" t="n">
-        <v>206.3</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>41</v>
+      <c r="F6" s="11" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>10.3</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L6" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="N6" s="8" t="n">
+      <c r="N6" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>197</v>
+        <v>92</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>10.7</v>
+        <v>0.2</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="R6" s="8" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="R6" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="S6" s="3" t="n">
-        <v>41.3</v>
+        <v>27.3</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>99.59999999999999</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>18.6</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="W6" s="8" t="n">
+      <c r="W6" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="X6" s="8" t="n">
+      <c r="X6" s="3" t="n">
         <v>29</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>85.40000000000001</v>
+        <v>45.4</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>9.4</v>
+        <v>19.8</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1027,29 +1036,29 @@
       <c r="C7" s="3" t="n">
         <v>418.2</v>
       </c>
-      <c r="D7" s="12" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="G7" s="12" t="n">
+      <c r="D7" s="11" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="G7" s="3" t="n">
         <v>11.4</v>
       </c>
-      <c r="H7" s="8" t="n">
-        <v>944.4</v>
+      <c r="H7" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>20.3</v>
+        <v>2.9</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="K7" s="8" t="n">
-        <v>11.3</v>
+        <v>21.8</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1.1</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>21.1</v>
@@ -1058,33 +1067,33 @@
         <v>20.9</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>46.1</v>
+        <v>24.6</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>1980.8</v>
+        <v>98</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>311.9</v>
-      </c>
-      <c r="R7" s="8" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="R7" s="3" t="n">
         <v>25.3</v>
       </c>
       <c r="S7" s="3" t="n">
         <v>28</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>159.5</v>
+        <v>59.5</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>19.1</v>
+        <v>29.1</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>28.7</v>
       </c>
-      <c r="W7" s="8" t="n">
+      <c r="W7" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="X7" s="8" t="n">
@@ -1110,19 +1119,19 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>19368</v>
-      </c>
-      <c r="D8" s="12" t="n">
+        <v>9681.1</v>
+      </c>
+      <c r="D8" s="11" t="n">
         <v>33.2</v>
       </c>
-      <c r="E8" s="12" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>11.5</v>
+      <c r="E8" s="11" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>12.5</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>20.6</v>
@@ -1131,39 +1140,39 @@
         <v>3.5</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>15.8</v>
+        <v>5.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L8" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L8" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="M8" s="8" t="n">
-        <v>41.7</v>
+      <c r="M8" s="3" t="n">
+        <v>21.7</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>196.5</v>
-      </c>
-      <c r="P8" s="8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q8" s="8" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="Q8" s="3" t="n">
         <v>33.3</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="S8" s="8" t="n">
+      <c r="S8" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>194.8</v>
-      </c>
-      <c r="U8" s="8" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="U8" s="3" t="n">
         <v>23</v>
       </c>
       <c r="V8" s="3" t="n">
@@ -1172,7 +1181,7 @@
       <c r="W8" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="X8" s="3" t="n">
+      <c r="X8" s="8" t="n">
         <v>28.2</v>
       </c>
       <c r="Y8" s="3" t="n">
@@ -1195,49 +1204,73 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>17183.6</v>
-      </c>
-      <c r="D9" s="9" t="inlineStr"/>
-      <c r="E9" s="9" t="inlineStr"/>
-      <c r="F9" s="9" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
+        <v>1185</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>161.7</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>1354.9</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>12100.8</v>
+      </c>
       <c r="I9" s="3" t="n">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>120.9</v>
+        <v>20.9</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr"/>
-      <c r="N9" s="3" t="inlineStr"/>
+      <c r="L9" s="3" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>1108</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>128.2</v>
+      </c>
       <c r="O9" s="3" t="n">
         <v>487</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q9" s="3" t="inlineStr"/>
-      <c r="R9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="n">
+        <v>156.6</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>124.4</v>
+      </c>
       <c r="S9" s="3" t="n">
-        <v>1371.5</v>
+        <v>153790.5</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>908</v>
+        <v>308</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>190.1</v>
-      </c>
-      <c r="V9" s="3" t="inlineStr"/>
-      <c r="W9" s="3" t="inlineStr"/>
+        <v>90.09999999999999</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>122</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>1420</v>
+      </c>
       <c r="X9" s="3" t="n">
-        <v>1032.5</v>
+        <v>1139.5</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>1389.1</v>
+        <v>589.1</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>41.8</v>
@@ -1256,30 +1289,30 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2356.7</v>
-      </c>
-      <c r="D10" s="12" t="n">
+        <v>356.7</v>
+      </c>
+      <c r="D10" s="11" t="n">
         <v>32.3</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="11" t="n">
         <v>21.5</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="11" t="n">
         <v>26.9</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="G10" s="11" t="n">
         <v>10.8</v>
       </c>
-      <c r="H10" s="8" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>2.4</v>
-      </c>
+      <c r="H10" s="3" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="K10" s="3" t="inlineStr"/>
+      <c r="K10" s="8" t="n">
+        <v>17.5</v>
+      </c>
       <c r="L10" s="3" t="n">
         <v>21.9</v>
       </c>
@@ -1290,37 +1323,37 @@
         <v>25.6</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>197.4</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q10" s="8" t="n">
+      <c r="Q10" s="3" t="n">
         <v>31.1</v>
       </c>
-      <c r="R10" s="8" t="n">
+      <c r="R10" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S10" s="8" t="n">
+      <c r="S10" s="3" t="n">
         <v>27.5</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>161.6</v>
       </c>
-      <c r="U10" s="3" t="n">
+      <c r="U10" s="8" t="n">
         <v>18</v>
       </c>
       <c r="V10" s="3" t="n">
         <v>27.1</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="8" t="n">
         <v>24</v>
       </c>
       <c r="X10" s="8" t="n">
         <v>27.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>177.8</v>
+        <v>1417.8</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>18.4</v>
@@ -1339,34 +1372,34 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>453.1</v>
-      </c>
-      <c r="D11" s="8" t="n">
-        <v>93.3</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>89.8</v>
-      </c>
-      <c r="F11" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F11" s="11" t="n">
         <v>26.6</v>
       </c>
-      <c r="G11" s="3" t="n">
-        <v>13.8</v>
+      <c r="G11" s="11" t="n">
+        <v>13.4</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>18.7</v>
+        <v>88.7</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="J11" s="8" t="n">
-        <v>71.09999999999999</v>
+      <c r="J11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>20.6</v>
+        <v>10.4</v>
+      </c>
+      <c r="L11" s="8" t="n">
+        <v>1.6</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>20.5</v>
@@ -1375,10 +1408,10 @@
         <v>24</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q11" s="3" t="n">
         <v>33.2</v>
@@ -1386,26 +1419,26 @@
       <c r="R11" s="3" t="n">
         <v>25.8</v>
       </c>
-      <c r="S11" s="8" t="n">
+      <c r="S11" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>156.3</v>
       </c>
-      <c r="U11" s="8" t="n">
+      <c r="U11" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="V11" s="8" t="n">
+      <c r="V11" s="3" t="n">
         <v>29.5</v>
       </c>
-      <c r="W11" s="8" t="n">
-        <v>655.1</v>
+      <c r="W11" s="3" t="n">
+        <v>25.1</v>
       </c>
       <c r="X11" s="3" t="n">
         <v>29</v>
       </c>
       <c r="Y11" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="Z11" s="3" t="n">
         <v>12.2</v>
@@ -1424,43 +1457,43 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>141824</v>
-      </c>
-      <c r="D12" s="12" t="n">
+        <v>1218.2</v>
+      </c>
+      <c r="D12" s="11" t="n">
         <v>32.8</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="11" t="n">
         <v>20.2</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="11" t="n">
         <v>26.5</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="G12" s="11" t="n">
         <v>12.6</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="L12" s="8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L12" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="M12" s="8" t="n">
+      <c r="M12" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="N12" s="8" t="n">
-        <v>220.3</v>
+      <c r="N12" s="3" t="n">
+        <v>22.5</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0.7</v>
@@ -1475,12 +1508,12 @@
         <v>28.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>1958</v>
-      </c>
-      <c r="U12" s="8" t="n">
+        <v>98</v>
+      </c>
+      <c r="U12" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="V12" s="8" t="n">
+      <c r="V12" s="3" t="n">
         <v>29.6</v>
       </c>
       <c r="W12" s="3" t="n">
@@ -1490,10 +1523,10 @@
         <v>30.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>713.2</v>
+        <v>13.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>11.1</v>
+        <v>111.1</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1509,61 +1542,63 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1230.1</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="E13" s="12" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E13" s="11" t="n">
         <v>20.8</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="F13" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="G13" s="11" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="H13" s="8" t="n">
+      <c r="H13" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>11.2</v>
       </c>
-      <c r="J13" s="8" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="K13" s="8" t="n">
+      <c r="J13" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K13" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="L13" s="8" t="n">
+      <c r="L13" s="3" t="n">
         <v>21.3</v>
       </c>
-      <c r="M13" s="8" t="n">
+      <c r="M13" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="N13" s="8" t="n">
+      <c r="N13" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="O13" s="3" t="n">
-        <v>197</v>
-      </c>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="8" t="n">
-        <v>229.1</v>
-      </c>
-      <c r="R13" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="R13" s="3" t="n">
         <v>24.3</v>
       </c>
-      <c r="S13" s="8" t="n">
+      <c r="S13" s="3" t="n">
         <v>27.3</v>
       </c>
       <c r="T13" s="3" t="n">
-        <v>167.9</v>
-      </c>
-      <c r="U13" s="8" t="n">
+        <v>67.90000000000001</v>
+      </c>
+      <c r="U13" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="V13" s="8" t="n">
+      <c r="V13" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="W13" s="3" t="n">
@@ -1573,10 +1608,10 @@
         <v>27.8</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>80.8</v>
+        <v>800.8</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1592,52 +1627,52 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>1821.4</v>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="E14" s="12" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="G14" s="8" t="n">
-        <v>80.09999999999999</v>
+        <v>821.4</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="G14" s="11" t="n">
+        <v>8.1</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>17.8</v>
+        <v>87.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>18.6</v>
+        <v>11.6</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="L14" s="8" t="n">
-        <v>41.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>21.1</v>
       </c>
       <c r="M14" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="N14" s="8" t="n">
+      <c r="N14" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="O14" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q14" s="8" t="n">
+      <c r="Q14" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="R14" s="8" t="n">
-        <v>24.8</v>
+      <c r="R14" s="3" t="n">
+        <v>24.2</v>
       </c>
       <c r="S14" s="3" t="n">
         <v>28.2</v>
@@ -1646,7 +1681,7 @@
         <v>77.8</v>
       </c>
       <c r="U14" s="3" t="n">
-        <v>18.1</v>
+        <v>8.1</v>
       </c>
       <c r="V14" s="3" t="n">
         <v>26</v>
@@ -1654,14 +1689,14 @@
       <c r="W14" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X14" s="8" t="n">
+      <c r="X14" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>185.1</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>5</v>
+        <v>0.1</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1679,74 +1714,74 @@
       <c r="C15" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D15" s="12" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E15" s="12" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F15" s="12" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>12.1</v>
+      <c r="D15" s="11" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>82.09999999999999</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>17.4</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" s="8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J15" s="8" t="n">
         <v>8</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>10.8</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="M15" s="8" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="N15" s="8" t="n">
+      <c r="M15" s="3" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="N15" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="O15" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="8" t="n">
+      <c r="Q15" s="3" t="n">
         <v>30</v>
       </c>
       <c r="R15" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="S15" s="8" t="n">
+      <c r="S15" s="3" t="n">
         <v>30</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="U15" s="3" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="V15" s="8" t="n">
+      <c r="U15" s="8" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="V15" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="W15" s="8" t="n">
+      <c r="W15" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="X15" s="8" t="n">
+      <c r="X15" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>16.6</v>
+        <v>716.6</v>
       </c>
       <c r="Z15" s="3" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="AA15" s="3" t="inlineStr">
         <is>
@@ -1761,57 +1796,77 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="9" t="inlineStr"/>
-      <c r="E16" s="11" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="F16" s="12" t="n">
+      <c r="C16" s="3" t="n">
+        <v>15308.1</v>
+      </c>
+      <c r="D16" s="10" t="n">
+        <v>1524.2</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="F16" s="10" t="n">
         <v>126.8</v>
       </c>
-      <c r="G16" s="10" t="n">
-        <v>15.4</v>
+      <c r="G16" s="15" t="n">
+        <v>52.5</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>192.1</v>
+        <v>19.2</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>186.4</v>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
-      <c r="N16" s="3" t="inlineStr"/>
+        <v>162.4</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>1129</v>
+      </c>
       <c r="O16" s="3" t="n">
-        <v>1490</v>
+        <v>490</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>21.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>152.4</v>
       </c>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>142.7</v>
+      </c>
       <c r="T16" s="3" t="n">
-        <v>1331</v>
+        <v>331</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>176.3</v>
-      </c>
-      <c r="V16" s="3" t="inlineStr"/>
-      <c r="W16" s="3" t="inlineStr"/>
-      <c r="X16" s="3" t="inlineStr"/>
+        <v>17.6</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v>412.6</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>251.2</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>140</v>
+      </c>
       <c r="Y16" s="3" t="n">
-        <v>1386.1</v>
+        <v>13861.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>42.3</v>
+        <v>14.2</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1829,70 +1884,74 @@
       <c r="C17" s="3" t="n">
         <v>306.2</v>
       </c>
-      <c r="D17" s="12" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E17" s="12" t="n">
+      <c r="D17" s="11" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E17" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="F17" s="12" t="n">
-        <v>25.4</v>
-      </c>
-      <c r="G17" s="12" t="n">
+      <c r="F17" s="11" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G17" s="3" t="n">
         <v>10.9</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>23.5</v>
+        <v>2.3</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="K17" s="3" t="inlineStr"/>
+      <c r="K17" s="3" t="n">
+        <v>0.1</v>
+      </c>
       <c r="L17" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="M17" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="N17" s="3" t="n">
-        <v>23.8</v>
+      <c r="N17" s="8" t="n">
+        <v>888.6</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>198</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q17" s="3" t="n">
-        <v>90.5</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q17" s="8" t="n">
+        <v>30.5</v>
       </c>
       <c r="R17" s="3" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="S17" s="8" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="S17" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>166.2</v>
       </c>
-      <c r="U17" s="3" t="n">
+      <c r="U17" s="8" t="n">
         <v>15.3</v>
       </c>
-      <c r="V17" s="8" t="n">
+      <c r="V17" s="3" t="n">
         <v>27.3</v>
       </c>
-      <c r="W17" s="3" t="inlineStr"/>
-      <c r="X17" s="3" t="n">
+      <c r="W17" s="3" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="X17" s="8" t="n">
         <v>28</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>1717.2</v>
+        <v>141.2</v>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>85.09999999999999</v>
+        <v>18.5</v>
       </c>
       <c r="AA17" s="3" t="inlineStr">
         <is>
@@ -1908,76 +1967,76 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="D18" s="12" t="n">
+        <v>3341.1</v>
+      </c>
+      <c r="D18" s="11" t="n">
         <v>32.2</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="E18" s="11" t="n">
         <v>19.2</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="F18" s="11" t="n">
         <v>25.7</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="G18" s="11" t="n">
         <v>13</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>67.2</v>
+        <v>171.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>20.4</v>
+        <v>0.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K18" s="8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>19.7</v>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>69.7</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>89.40000000000001</v>
+        <v>29.4</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="O18" s="3" t="n">
-        <v>197</v>
+        <v>97</v>
       </c>
       <c r="P18" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q18" s="8" t="n">
+      <c r="Q18" s="3" t="n">
         <v>32.2</v>
       </c>
-      <c r="R18" s="8" t="n">
+      <c r="R18" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="S18" s="8" t="n">
+      <c r="S18" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>158</v>
       </c>
-      <c r="U18" s="8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="V18" s="8" t="n">
+      <c r="U18" s="3" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="V18" s="3" t="n">
         <v>28.3</v>
       </c>
       <c r="W18" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>229.8</v>
+        <v>29.8</v>
       </c>
       <c r="Y18" s="3" t="n">
-        <v>177.6</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>8.6</v>
+        <v>18.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -1993,43 +2052,43 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1326.2</v>
-      </c>
-      <c r="D19" s="12" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="E19" s="12" t="n">
+        <v>326.2</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E19" s="11" t="n">
         <v>20.5</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="F19" s="11" t="n">
         <v>26.3</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="G19" s="11" t="n">
         <v>11.7</v>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="H19" s="8" t="n">
         <v>18.8</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>13.6</v>
+        <v>3.6</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="L19" s="8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L19" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="3" t="n">
         <v>20.7</v>
       </c>
-      <c r="N19" s="8" t="n">
-        <v>24.3</v>
+      <c r="N19" s="3" t="n">
+        <v>24.5</v>
       </c>
       <c r="O19" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P19" s="3" t="n">
         <v>0.4</v>
@@ -2038,15 +2097,15 @@
         <v>31.7</v>
       </c>
       <c r="R19" s="8" t="n">
-        <v>25.3</v>
-      </c>
-      <c r="S19" s="8" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="S19" s="3" t="n">
         <v>28.2</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>160.5</v>
-      </c>
-      <c r="U19" s="3" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="U19" s="8" t="n">
         <v>18.4</v>
       </c>
       <c r="V19" s="8" t="n">
@@ -2055,11 +2114,11 @@
       <c r="W19" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="X19" s="8" t="n">
+      <c r="X19" s="3" t="n">
         <v>29.2</v>
       </c>
       <c r="Y19" s="3" t="n">
-        <v>188.5</v>
+        <v>88.5</v>
       </c>
       <c r="Z19" s="3" t="n">
         <v>3.8</v>
@@ -2078,56 +2137,58 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1299</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v>91.09999999999999</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>89.7</v>
-      </c>
-      <c r="F20" s="8" t="n">
+        <v>2899</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F20" s="11" t="n">
         <v>24.7</v>
       </c>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="11" t="n">
         <v>10</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>18.4</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>1.8</v>
+        <v>11.8</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>31.5</v>
+        <v>3.5</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="L20" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="M20" s="8" t="n">
+      <c r="M20" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="O20" s="3" t="inlineStr"/>
+        <v>22.8</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>99</v>
+      </c>
       <c r="P20" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="Q20" s="8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q20" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="R20" s="8" t="n">
-        <v>238.4</v>
+      <c r="R20" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>171.6</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="U20" s="3" t="n">
         <v>10.6</v>
@@ -2138,11 +2199,11 @@
       <c r="W20" s="8" t="n">
         <v>22.8</v>
       </c>
-      <c r="X20" s="8" t="n">
+      <c r="X20" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="Y20" s="3" t="n">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="Z20" s="3" t="n">
         <v>5.4</v>
@@ -2161,56 +2222,58 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>1357.5</v>
-      </c>
-      <c r="D21" s="12" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="D21" s="11" t="n">
         <v>30.1</v>
       </c>
-      <c r="E21" s="12" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="F21" s="12" t="n">
+      <c r="E21" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="F21" s="11" t="n">
         <v>24.1</v>
       </c>
-      <c r="G21" s="12" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="H21" s="3" t="inlineStr"/>
+      <c r="G21" s="15" t="n">
+        <v>82.8</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>16.4</v>
+      </c>
       <c r="I21" s="3" t="n">
-        <v>2.2</v>
+        <v>12.2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>3.8</v>
+        <v>12.8</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L21" s="8" t="n">
         <v>18.9</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="N21" s="8" t="n">
-        <v>12.8</v>
+        <v>88.90000000000001</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>21.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1001</v>
-      </c>
-      <c r="P21" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="8" t="n">
+        <v>100</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="R21" s="8" t="n">
+      <c r="R21" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="S21" s="3" t="n">
         <v>26.9</v>
       </c>
       <c r="T21" s="3" t="n">
-        <v>163.1</v>
+        <v>63.1</v>
       </c>
       <c r="U21" s="3" t="n">
         <v>15.7</v>
@@ -2218,17 +2281,17 @@
       <c r="V21" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="W21" s="8" t="n">
+      <c r="W21" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="X21" s="8" t="n">
         <v>28.8</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>184.1</v>
+        <v>18484.1</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>5.4</v>
+        <v>1.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2244,32 +2307,34 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1294.9</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>531.2</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="F22" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="G22" s="3" t="n">
+        <v>992.9</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G22" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>17.4</v>
+        <v>11.4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr"/>
+        <v>11.9</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>13.5</v>
+      </c>
       <c r="K22" s="3" t="n">
-        <v>10.1</v>
+        <v>0.1</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>69.09999999999999</v>
+        <v>19.1</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>19.1</v>
@@ -2278,12 +2343,12 @@
         <v>22.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>100</v>
-      </c>
-      <c r="P22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="8" t="n">
+        <v>10800</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="3" t="n">
         <v>31</v>
       </c>
       <c r="R22" s="3" t="n">
@@ -2293,19 +2358,19 @@
         <v>29.9</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>166.8</v>
+        <v>66.8</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="V22" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="W22" s="8" t="n">
+      <c r="W22" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X22" s="8" t="n">
-        <v>216.5</v>
+      <c r="X22" s="3" t="n">
+        <v>26.5</v>
       </c>
       <c r="Y22" s="3" t="n">
         <v>88.8</v>
@@ -2326,15 +2391,23 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="9" t="inlineStr"/>
-      <c r="E23" s="9" t="inlineStr"/>
-      <c r="F23" s="9" t="inlineStr"/>
+      <c r="C23" s="3" t="n">
+        <v>1610.1</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>155.4</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>125.8</v>
+      </c>
       <c r="G23" s="3" t="n">
-        <v>59.2</v>
+        <v>59</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>88.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>10.4</v>
@@ -2342,35 +2415,53 @@
       <c r="J23" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="K23" s="3" t="inlineStr"/>
+      <c r="K23" s="3" t="n">
+        <v>16.5</v>
+      </c>
       <c r="L23" s="3" t="n">
-        <v>198.4</v>
-      </c>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="inlineStr"/>
+        <v>98.40000000000001</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>97.8</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>1613.3</v>
+      </c>
       <c r="O23" s="3" t="n">
         <v>494</v>
       </c>
-      <c r="P23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="n">
+        <v>1.3</v>
+      </c>
       <c r="Q23" s="3" t="n">
-        <v>1252.9</v>
-      </c>
-      <c r="R23" s="3" t="inlineStr"/>
-      <c r="S23" s="3" t="inlineStr"/>
+        <v>152.9</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>1240.6</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>115394.7</v>
+      </c>
       <c r="T23" s="3" t="n">
-        <v>1320</v>
+        <v>320</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>179.6</v>
-      </c>
-      <c r="V23" s="3" t="inlineStr"/>
-      <c r="W23" s="3" t="inlineStr"/>
-      <c r="X23" s="3" t="inlineStr"/>
+        <v>796.1</v>
+      </c>
+      <c r="V23" s="3" t="n">
+        <v>122.3</v>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>140.6</v>
+      </c>
       <c r="Y23" s="3" t="n">
         <v>422</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>26.5</v>
+        <v>126.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2386,54 +2477,56 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>322</v>
-      </c>
-      <c r="D24" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="D24" s="11" t="n">
         <v>31.1</v>
       </c>
-      <c r="E24" s="12" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="F24" s="12" t="n">
+      <c r="E24" s="11" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F24" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="G24" s="11" t="n">
         <v>11.9</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr"/>
+        <v>21.1</v>
+      </c>
+      <c r="J24" s="8" t="n">
+        <v>1.9</v>
+      </c>
       <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="8" t="n">
-        <v>29.7</v>
+      <c r="L24" s="3" t="n">
+        <v>19.7</v>
       </c>
       <c r="M24" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>0.8</v>
+        <v>22.7</v>
       </c>
       <c r="O24" s="3" t="n">
-        <v>988.1</v>
+        <v>0.4</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>10.3</v>
+        <v>5.3</v>
       </c>
       <c r="Q24" s="3" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="R24" s="8" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="R24" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S24" s="8" t="n">
+      <c r="S24" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>164</v>
+        <v>64</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>15.9</v>
@@ -2441,17 +2534,17 @@
       <c r="V24" s="3" t="n">
         <v>25.9</v>
       </c>
-      <c r="W24" s="8" t="n">
+      <c r="W24" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X24" s="8" t="n">
+      <c r="X24" s="3" t="n">
         <v>28.1</v>
       </c>
       <c r="Y24" s="3" t="n">
-        <v>184.4</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>55.3</v>
+        <v>5.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2467,44 +2560,46 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>177.8</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>4.4</v>
+        <v>171.8</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>24.9</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H25" s="8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H25" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
+      <c r="I25" s="3" t="n">
+        <v>11.4</v>
+      </c>
       <c r="J25" s="3" t="n">
         <v>2.3</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>17.6</v>
+        <v>5.6</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>20</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>194.4</v>
-      </c>
-      <c r="N25" s="8" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="N25" s="3" t="n">
         <v>22.9</v>
       </c>
       <c r="O25" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>10.4</v>
+        <v>0.4</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>22.9</v>
@@ -2512,29 +2607,29 @@
       <c r="R25" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="S25" s="8" t="n">
+      <c r="S25" s="3" t="n">
         <v>26.1</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>93.2</v>
       </c>
       <c r="U25" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="V25" s="8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V25" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="W25" s="8" t="n">
+      <c r="W25" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="Y25" s="3" t="n">
         <v>95.2</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2550,29 +2645,31 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2345</v>
-      </c>
-      <c r="D26" s="12" t="n">
+        <v>845</v>
+      </c>
+      <c r="D26" s="11" t="n">
         <v>31.7</v>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="11" t="n">
         <v>20.5</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="F26" s="11" t="n">
         <v>26.1</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="G26" s="11" t="n">
         <v>11.2</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="I26" s="3" t="inlineStr"/>
+        <v>886.8</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="J26" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>20.6</v>
@@ -2584,19 +2681,19 @@
         <v>23.8</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P26" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q26" s="3" t="n">
-        <v>31.4</v>
-      </c>
-      <c r="R26" s="8" t="n">
+      <c r="Q26" s="8" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="R26" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>25.3</v>
+        <v>2.5</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>55.2</v>
@@ -2604,17 +2701,17 @@
       <c r="U26" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="V26" s="8" t="n">
+      <c r="V26" s="3" t="n">
         <v>27.2</v>
       </c>
-      <c r="W26" s="8" t="n">
+      <c r="W26" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="X26" s="3" t="n">
-        <v>62.1</v>
+        <v>26.8</v>
       </c>
       <c r="Y26" s="3" t="n">
-        <v>174.3</v>
+        <v>74.3</v>
       </c>
       <c r="Z26" s="3" t="n">
         <v>9.199999999999999</v>
@@ -2633,29 +2730,31 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2418.2</v>
-      </c>
-      <c r="D27" s="8" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="H27" s="3" t="n">
+        <v>1418.2</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>37</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="G27" s="8" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="H27" s="8" t="n">
         <v>17.6</v>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
+      <c r="I27" s="3" t="n">
+        <v>13.1</v>
+      </c>
       <c r="J27" s="3" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>19.6</v>
@@ -2663,26 +2762,26 @@
       <c r="M27" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N27" s="8" t="n">
+      <c r="N27" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>4.2</v>
+        <v>0.2</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>32.9</v>
       </c>
-      <c r="R27" s="8" t="n">
+      <c r="R27" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S27" s="8" t="n">
+      <c r="S27" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>153</v>
+        <v>53</v>
       </c>
       <c r="U27" s="3" t="n">
         <v>23.4</v>
@@ -2691,16 +2790,16 @@
         <v>29.3</v>
       </c>
       <c r="W27" s="8" t="n">
-        <v>95.5</v>
-      </c>
-      <c r="X27" s="8" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="X27" s="3" t="n">
         <v>30.2</v>
       </c>
       <c r="Y27" s="3" t="n">
-        <v>174.2</v>
+        <v>74.2</v>
       </c>
       <c r="Z27" s="3" t="n">
-        <v>110.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -2718,74 +2817,74 @@
       <c r="C28" s="3" t="n">
         <v>282.3</v>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="D28" s="11" t="n">
         <v>32.6</v>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="E28" s="11" t="n">
         <v>19.8</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="F28" s="11" t="n">
         <v>26.2</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="G28" s="11" t="n">
         <v>12.8</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>18.4</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J28" s="3" t="n">
         <v>3.2</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>12.6</v>
+        <v>80</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>20.1</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>49.9</v>
+        <v>29.9</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>33.4</v>
+        <v>23.1</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0.4</v>
       </c>
       <c r="Q28" s="8" t="n">
-        <v>29.7</v>
+        <v>979.8</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="S28" s="8" t="n">
+      <c r="S28" s="3" t="n">
         <v>28.9</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>169.4</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v>224.4</v>
-      </c>
-      <c r="W28" s="8" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>24.4</v>
+      </c>
+      <c r="W28" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="X28" s="8" t="n">
-        <v>260.3</v>
+        <v>659.5</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>186</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>14.3</v>
+        <v>0.2</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2801,48 +2900,46 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>120.2</v>
-      </c>
-      <c r="D29" s="12" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E29" s="12" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="F29" s="12" t="n">
+        <v>122112.1</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="F29" s="11" t="n">
         <v>24.8</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="G29" s="11" t="n">
         <v>8.9</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>11.1</v>
+        <v>1.1</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="K29" s="3" t="n">
-        <v>18.1</v>
-      </c>
+      <c r="K29" s="3" t="inlineStr"/>
       <c r="L29" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="M29" s="8" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="N29" s="8" t="n">
+      <c r="M29" s="3" t="n">
+        <v>241.9</v>
+      </c>
+      <c r="N29" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>196.5</v>
+        <v>96.5</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q29" s="8" t="n">
+      <c r="Q29" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="R29" s="8" t="n">
@@ -2852,25 +2949,25 @@
         <v>28.8</v>
       </c>
       <c r="T29" s="3" t="n">
-        <v>173.7</v>
-      </c>
-      <c r="U29" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v>35</v>
-      </c>
-      <c r="W29" s="8" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="W29" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="X29" s="8" t="n">
         <v>25.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>181.8</v>
+        <v>181.9</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>5.8</v>
+        <v>15.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2885,48 +2982,74 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
-      <c r="D30" s="9" t="inlineStr"/>
-      <c r="E30" s="9" t="inlineStr"/>
-      <c r="F30" s="9" t="inlineStr"/>
-      <c r="G30" s="10" t="n">
-        <v>50.7</v>
+      <c r="C30" s="3" t="n">
+        <v>625.1</v>
+      </c>
+      <c r="D30" s="10" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G30" s="15" t="n">
+        <v>57</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>192.2</v>
+        <v>92.2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>9.9</v>
+        <v>19.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>16.7</v>
+        <v>114.8</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>123.7</v>
       </c>
-      <c r="L30" s="3" t="inlineStr"/>
-      <c r="M30" s="3" t="inlineStr"/>
-      <c r="N30" s="3" t="inlineStr"/>
+      <c r="L30" s="3" t="n">
+        <v>180.2</v>
+      </c>
+      <c r="M30" s="3" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>122.8</v>
+      </c>
       <c r="O30" s="3" t="n">
-        <v>1489.5</v>
+        <v>489.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>121</v>
-      </c>
-      <c r="Q30" s="3" t="inlineStr"/>
-      <c r="R30" s="3" t="inlineStr"/>
-      <c r="S30" s="3" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="Q30" s="3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>312.1</v>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>13.5</v>
+      </c>
       <c r="T30" s="3" t="n">
-        <v>1344.5</v>
+        <v>344.5</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>168.8</v>
-      </c>
-      <c r="V30" s="3" t="inlineStr"/>
-      <c r="W30" s="3" t="inlineStr"/>
-      <c r="X30" s="3" t="inlineStr"/>
+        <v>68.8</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>127.4</v>
+      </c>
+      <c r="W30" s="3" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v>13.3</v>
+      </c>
       <c r="Y30" s="3" t="n">
-        <v>1411.5</v>
+        <v>411.5</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>30.9</v>
@@ -2947,72 +3070,72 @@
       <c r="C31" s="3" t="n">
         <v>272.7</v>
       </c>
-      <c r="D31" s="12" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E31" s="12" t="n">
+      <c r="D31" s="15" t="n">
+        <v>1246.1</v>
+      </c>
+      <c r="E31" s="11" t="n">
         <v>19.9</v>
       </c>
-      <c r="F31" s="12" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="G31" s="8" t="n">
-        <v>11.9</v>
+      <c r="F31" s="15" t="n">
+        <v>95.59999999999999</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>11.4</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>88.40000000000001</v>
+        <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>20.1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="8" t="n">
+      <c r="L31" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="M31" s="8" t="n">
+      <c r="M31" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="N31" s="8" t="n">
+      <c r="N31" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>197.9</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q31" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q31" s="3" t="n">
         <v>29.1</v>
       </c>
-      <c r="R31" s="8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="S31" s="8" t="n">
+      <c r="R31" s="3" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="S31" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>168.9</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="U31" s="3" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="V31" s="3" t="n">
-        <v>255.1</v>
-      </c>
-      <c r="W31" s="8" t="n">
-        <v>23.1</v>
+        <v>13.8</v>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>25.1</v>
       </c>
       <c r="X31" s="8" t="n">
-        <v>206.7</v>
+        <v>26.7</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>181.3</v>
+        <v>182.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>16.2</v>
+        <v>1682.8</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3028,41 +3151,43 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1263.5</v>
-      </c>
-      <c r="D32" s="12" t="n">
+        <v>263.5</v>
+      </c>
+      <c r="D32" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="11" t="n">
         <v>20.4</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="F32" s="11" t="n">
         <v>24.7</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="G32" s="11" t="n">
         <v>8.6</v>
       </c>
       <c r="H32" s="8" t="n">
         <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="J32" s="3" t="inlineStr"/>
+        <v>1.3</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>12.4</v>
+      </c>
       <c r="K32" s="3" t="n">
         <v>3.4</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M32" s="8" t="n">
+      <c r="M32" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="N32" s="8" t="n">
+      <c r="N32" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="O32" s="3" t="n">
-        <v>990.1</v>
+        <v>99</v>
       </c>
       <c r="P32" s="3" t="n">
         <v>0.2</v>
@@ -3070,32 +3195,32 @@
       <c r="Q32" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="R32" s="8" t="n">
+      <c r="R32" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="S32" s="8" t="n">
+      <c r="S32" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T32" s="3" t="n">
-        <v>169.8</v>
+        <v>69.8</v>
       </c>
       <c r="U32" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="V32" s="8" t="n">
+      <c r="V32" s="3" t="n">
         <v>27.1</v>
       </c>
-      <c r="W32" s="8" t="n">
+      <c r="W32" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="X32" s="8" t="n">
-        <v>29.1</v>
+      <c r="X32" s="3" t="n">
+        <v>99.09999999999999</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>181.1</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>16.7</v>
+        <v>16.4</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3111,29 +3236,31 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>144.1</v>
-      </c>
-      <c r="D33" s="12" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="D33" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="E33" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="F33" s="11" t="n">
         <v>22.9</v>
       </c>
-      <c r="G33" s="3" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H33" s="8" t="n">
-        <v>129</v>
+      <c r="G33" s="11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I33" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="J33" s="3" t="inlineStr"/>
-      <c r="K33" s="3" t="n">
-        <v>14.5</v>
+      <c r="J33" s="3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K33" s="8" t="n">
+        <v>26.5</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>20.8</v>
@@ -3141,42 +3268,44 @@
       <c r="M33" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="N33" s="8" t="n">
+      <c r="N33" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="O33" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="Q33" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="R33" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="S33" s="8" t="n">
+      <c r="S33" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>183.4</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
-        <v>15</v>
-      </c>
-      <c r="V33" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="V33" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="W33" s="8" t="n">
+      <c r="W33" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="X33" s="8" t="n">
+      <c r="X33" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="Y33" s="3" t="n">
-        <v>191.8</v>
+        <v>91.8</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>2.3</v>
+        <v>12.3</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3192,22 +3321,22 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1117.8</v>
-      </c>
-      <c r="D34" s="12" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="E34" s="12" t="n">
-        <v>19.2</v>
-      </c>
-      <c r="F34" s="12" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="F34" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="G34" s="11" t="n">
         <v>11.5</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>167.8</v>
+        <v>17.8</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>11.9</v>
@@ -3226,40 +3355,40 @@
         <v>23.5</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q34" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Q34" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="R34" s="8" t="n">
+      <c r="R34" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="S34" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>70.2</v>
-      </c>
-      <c r="U34" s="3" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="V34" s="8" t="n">
+        <v>80.2</v>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="V34" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="W34" s="8" t="n">
+      <c r="W34" s="3" t="n">
         <v>21</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>162.5</v>
+        <v>62.6</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>12.8</v>
+        <v>182.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3275,41 +3404,43 @@
         </is>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1284.4</v>
-      </c>
-      <c r="D35" s="12" t="n">
-        <v>29.4</v>
-      </c>
-      <c r="E35" s="12" t="n">
+        <v>284.4</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="E35" s="11" t="n">
         <v>18.8</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F35" s="11" t="n">
         <v>24.1</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="G35" s="11" t="n">
         <v>10.7</v>
       </c>
       <c r="H35" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>16.8</v>
+        <v>1.8</v>
       </c>
       <c r="K35" s="3" t="n">
         <v>2.8</v>
       </c>
       <c r="L35" s="8" t="n">
-        <v>69</v>
-      </c>
-      <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="3" t="n">
-        <v>243.1</v>
+        <v>19</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="N35" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P35" s="3" t="n">
         <v>10</v>
@@ -3317,14 +3448,14 @@
       <c r="Q35" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R35" s="8" t="n">
+      <c r="R35" s="3" t="n">
         <v>24.8</v>
       </c>
-      <c r="S35" s="8" t="n">
+      <c r="S35" s="3" t="n">
         <v>29</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>275.4</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>9.4</v>
@@ -3335,14 +3466,14 @@
       <c r="W35" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="X35" s="3" t="n">
-        <v>29.3</v>
+      <c r="X35" s="8" t="n">
+        <v>2959.3</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>14.9</v>
+        <v>164.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3360,20 +3491,20 @@
       <c r="C36" s="3" t="n">
         <v>1117.2</v>
       </c>
-      <c r="D36" s="12" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="E36" s="12" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="F36" s="12" t="n">
+      <c r="D36" s="11" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F36" s="11" t="n">
         <v>24.9</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>72.5</v>
+      <c r="G36" s="11" t="n">
+        <v>7.5</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.6</v>
@@ -3382,7 +3513,7 @@
         <v>11</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>16.3</v>
+        <v>11.3</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>21.9</v>
@@ -3390,14 +3521,14 @@
       <c r="M36" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="N36" s="8" t="n">
+      <c r="N36" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>21.5</v>
@@ -3409,25 +3540,25 @@
         <v>24.3</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>194.8</v>
+        <v>94.8</v>
       </c>
       <c r="U36" s="3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V36" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V36" s="3" t="n">
         <v>21.4</v>
       </c>
-      <c r="W36" s="8" t="n">
+      <c r="W36" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="X36" s="8" t="n">
+      <c r="X36" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="Y36" s="3" t="n">
         <v>94.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>1.3</v>
+        <v>15.3</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3445,47 +3576,71 @@
       <c r="C37" s="3" t="n">
         <v>826.4</v>
       </c>
-      <c r="D37" s="9" t="inlineStr"/>
-      <c r="E37" s="9" t="inlineStr"/>
-      <c r="F37" s="9" t="inlineStr"/>
-      <c r="G37" s="10" t="n">
-        <v>14.3</v>
+      <c r="D37" s="11" t="n">
+        <v>142.9</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="G37" s="11" t="n">
+        <v>42.9</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.8</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr"/>
+        <v>5.8</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>12.2</v>
+      </c>
       <c r="K37" s="3" t="n">
         <v>117.9</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>103.4</v>
       </c>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
-      <c r="O37" s="3" t="inlineStr"/>
+      <c r="M37" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="N37" s="3" t="n">
+        <v>92</v>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>0.8</v>
+      </c>
       <c r="P37" s="3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>133.1</v>
-      </c>
-      <c r="R37" s="3" t="inlineStr"/>
-      <c r="S37" s="3" t="inlineStr"/>
+        <v>233.1</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>136.3</v>
+      </c>
       <c r="T37" s="3" t="n">
         <v>393.6</v>
       </c>
       <c r="U37" s="3" t="n">
-        <v>140.4</v>
-      </c>
-      <c r="V37" s="3" t="inlineStr"/>
-      <c r="W37" s="3" t="inlineStr"/>
-      <c r="X37" s="3" t="inlineStr"/>
+        <v>40.4</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="W37" s="3" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v>129.8</v>
+      </c>
       <c r="Y37" s="3" t="n">
-        <v>1416</v>
+        <v>12466</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>128</v>
@@ -3504,69 +3659,73 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>163.3</v>
-      </c>
-      <c r="D38" s="12" t="n">
+        <v>155.3</v>
+      </c>
+      <c r="D38" s="11" t="n">
         <v>28.6</v>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F38" s="11" t="n">
         <v>24.3</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="G38" s="11" t="n">
         <v>8.6</v>
       </c>
-      <c r="H38" s="8" t="n">
-        <v>68.59999999999999</v>
+      <c r="H38" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr"/>
-      <c r="K38" s="3" t="inlineStr"/>
+        <v>1.2</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>1.1</v>
+      </c>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>20</v>
+        <v>20.8</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P38" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="8" t="n">
+      <c r="Q38" s="3" t="n">
         <v>26.6</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>23.6</v>
       </c>
-      <c r="S38" s="8" t="n">
-        <v>927.3</v>
+      <c r="S38" s="3" t="n">
+        <v>27.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>78.7</v>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v>811.1</v>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v>24.8</v>
-      </c>
-      <c r="W38" s="8" t="n">
+        <v>828.7</v>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>81.09999999999999</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="W38" s="3" t="n">
         <v>22.5</v>
       </c>
       <c r="X38" s="8" t="n">
         <v>26</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>1839.2</v>
+        <v>183.2</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>5.6</v>
@@ -3585,31 +3744,31 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332.5</v>
-      </c>
-      <c r="D39" s="8" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>69.3</v>
-      </c>
-      <c r="F39" s="3" t="n">
+        <v>332</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F39" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="G39" s="3" t="n">
+      <c r="G39" s="11" t="n">
         <v>11.4</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>93.5</v>
+        <v>9.5</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>19.5</v>
@@ -3621,13 +3780,13 @@
         <v>22.6</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q39" s="8" t="n">
-        <v>130.7</v>
+        <v>0.1</v>
+      </c>
+      <c r="Q39" s="3" t="n">
+        <v>30.7</v>
       </c>
       <c r="R39" s="3" t="n">
         <v>25.5</v>
@@ -3636,25 +3795,25 @@
         <v>29.3</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>166.5</v>
+        <v>6685.3</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="V39" s="8" t="n">
+      <c r="V39" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="W39" s="3" t="n">
         <v>23.9</v>
       </c>
       <c r="X39" s="8" t="n">
-        <v>27.2</v>
+        <v>17.8</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>72.90000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
-        <v>106.1</v>
+        <v>10.1</v>
       </c>
       <c r="AA39" s="3" t="inlineStr">
         <is>
@@ -3670,76 +3829,76 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>278.1</v>
-      </c>
-      <c r="D40" s="12" t="n">
+        <v>278.8</v>
+      </c>
+      <c r="D40" s="11" t="n">
         <v>30.8</v>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="E40" s="11" t="n">
         <v>20.6</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="F40" s="11" t="n">
         <v>25.7</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="G40" s="11" t="n">
         <v>10.2</v>
       </c>
-      <c r="H40" s="3" t="n">
-        <v>19</v>
+      <c r="H40" s="8" t="n">
+        <v>29</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K40" s="8" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>21</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="N40" s="8" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="N40" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q40" s="8" t="n">
-        <v>30.7</v>
-      </c>
-      <c r="R40" s="8" t="n">
-        <v>25.3</v>
+        <v>0.2</v>
+      </c>
+      <c r="Q40" s="3" t="n">
+        <v>80.7</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>25.8</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>165.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="V40" s="8" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="V40" s="3" t="n">
         <v>28</v>
       </c>
       <c r="W40" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X40" s="8" t="n">
+      <c r="X40" s="3" t="n">
         <v>27.3</v>
       </c>
       <c r="Y40" s="3" t="n">
         <v>72.2</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>10.4</v>
+        <v>1811.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3755,77 +3914,75 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>242.6</v>
-      </c>
-      <c r="D41" s="12" t="n">
+        <v>248.6</v>
+      </c>
+      <c r="D41" s="11" t="n">
         <v>29.6</v>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="E41" s="11" t="n">
         <v>20.8</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="F41" s="11" t="n">
         <v>25.2</v>
       </c>
-      <c r="G41" s="3" t="n">
-        <v>18.8</v>
+      <c r="G41" s="11" t="n">
+        <v>8.800000000000001</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>19.4</v>
       </c>
-      <c r="I41" s="8" t="n">
-        <v>18.5</v>
+      <c r="I41" s="3" t="n">
+        <v>11.5</v>
       </c>
       <c r="J41" s="3" t="n">
         <v>2.4</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="L41" s="8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L41" s="3" t="n">
         <v>20.9</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>20.2</v>
+        <v>26.2</v>
       </c>
       <c r="N41" s="3" t="n">
         <v>23.2</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>193.8</v>
+        <v>93.8</v>
       </c>
       <c r="P41" s="3" t="n">
         <v>1.5</v>
       </c>
       <c r="Q41" s="8" t="n">
-        <v>9.300000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="R41" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="S41" s="8" t="n">
+      <c r="S41" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>720.5</v>
-      </c>
-      <c r="U41" s="8" t="n">
+        <v>80.5</v>
+      </c>
+      <c r="U41" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V41" s="8" t="n">
+      <c r="V41" s="3" t="n">
         <v>27.1</v>
       </c>
       <c r="W41" s="3" t="n">
-        <v>645.1</v>
-      </c>
-      <c r="X41" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="X41" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>1841.1</v>
-      </c>
-      <c r="Z41" s="3" t="n">
-        <v>16.7</v>
-      </c>
+        <v>181.1</v>
+      </c>
+      <c r="Z41" s="3" t="inlineStr"/>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3842,68 +3999,68 @@
       <c r="C42" s="3" t="n">
         <v>288.6</v>
       </c>
-      <c r="D42" s="12" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E42" s="12" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F42" s="12" t="n">
+      <c r="D42" s="11" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F42" s="11" t="n">
         <v>25.6</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="G42" s="11" t="n">
         <v>10.5</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>188.6</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>16.6</v>
+        <v>11.6</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K42" s="8" t="n">
-        <v>0.4</v>
+        <v>10.9</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M42" s="8" t="n">
-        <v>91.2</v>
+      <c r="M42" s="3" t="n">
+        <v>21.2</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="O42" s="3" t="n">
-        <v>1600</v>
+        <v>100</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q42" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q42" s="3" t="n">
         <v>30.9</v>
       </c>
-      <c r="R42" s="8" t="n">
+      <c r="R42" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="S42" s="8" t="n">
+      <c r="S42" s="3" t="n">
         <v>27.6</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>162</v>
-      </c>
-      <c r="U42" s="8" t="n">
+        <v>62</v>
+      </c>
+      <c r="U42" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V42" s="8" t="n">
-        <v>207.1</v>
+      <c r="V42" s="3" t="n">
+        <v>27.1</v>
       </c>
       <c r="W42" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="X42" s="8" t="n">
-        <v>239.3</v>
+        <v>8953.5</v>
       </c>
       <c r="Y42" s="3" t="n">
         <v>181.8</v>
@@ -3925,24 +4082,26 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>2311.6</v>
-      </c>
-      <c r="D43" s="12" t="n">
-        <v>30.8</v>
-      </c>
-      <c r="E43" s="12" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="F43" s="12" t="n">
+        <v>312.6</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="F43" s="11" t="n">
         <v>25.9</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="G43" s="11" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="H43" s="8" t="n">
         <v>18.6</v>
       </c>
-      <c r="I43" s="3" t="inlineStr"/>
+      <c r="I43" s="8" t="n">
+        <v>41.6</v>
+      </c>
       <c r="J43" s="3" t="n">
         <v>3</v>
       </c>
@@ -3952,47 +4111,47 @@
       <c r="L43" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M43" s="8" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="N43" s="8" t="n">
+      <c r="M43" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="N43" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>199</v>
+        <v>99</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q43" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="8" t="n">
+      <c r="R43" s="3" t="n">
         <v>21.7</v>
       </c>
-      <c r="S43" s="8" t="n">
+      <c r="S43" s="3" t="n">
         <v>24</v>
       </c>
       <c r="T43" s="3" t="n">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="U43" s="3" t="n">
         <v>2.1</v>
       </c>
       <c r="V43" s="3" t="n">
-        <v>24.8</v>
+        <v>24</v>
       </c>
       <c r="W43" s="3" t="n">
         <v>22</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>35.4</v>
+        <v>95.8</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>184.3</v>
+        <v>1849.5</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>14.6</v>
+        <v>0.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4007,10 +4166,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr"/>
-      <c r="D44" s="3" t="inlineStr"/>
-      <c r="E44" s="3" t="inlineStr"/>
-      <c r="F44" s="3" t="inlineStr"/>
+      <c r="C44" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D44" s="11" t="inlineStr"/>
+      <c r="E44" s="11" t="inlineStr"/>
+      <c r="F44" s="11" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
@@ -4045,54 +4206,74 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1722.7</v>
-      </c>
-      <c r="D45" s="9" t="inlineStr"/>
-      <c r="E45" s="9" t="inlineStr"/>
-      <c r="F45" s="9" t="inlineStr"/>
-      <c r="G45" s="3" t="n">
-        <v>6.1</v>
+        <v>1423.4</v>
+      </c>
+      <c r="D45" s="10" t="n">
+        <v>922.7</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>10101.1</v>
+      </c>
+      <c r="G45" s="15" t="n">
+        <v>1210.1</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>293.6</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>164.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>51</v>
-      </c>
-      <c r="L45" s="3" t="inlineStr"/>
+        <v>2.1</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>100900160.4</v>
+      </c>
       <c r="M45" s="3" t="inlineStr"/>
-      <c r="N45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="n">
+        <v>16128.5</v>
+      </c>
       <c r="O45" s="3" t="n">
-        <v>191.8</v>
+        <v>4916</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>16.9</v>
+        <v>11.9</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>146.2</v>
-      </c>
-      <c r="R45" s="3" t="inlineStr"/>
-      <c r="S45" s="3" t="inlineStr"/>
+        <v>1246.3</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>122.2</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>13.8</v>
+      </c>
       <c r="T45" s="3" t="n">
         <v>341.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>1668</v>
-      </c>
-      <c r="V45" s="3" t="inlineStr"/>
-      <c r="W45" s="3" t="inlineStr"/>
-      <c r="X45" s="3" t="inlineStr"/>
+        <v>66.8</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>1412.4</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>122.5</v>
+      </c>
       <c r="Y45" s="3" t="n">
-        <v>992.3</v>
+        <v>3983.1</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>198.5</v>
+        <v>10820.9</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4110,72 +4291,74 @@
       <c r="C46" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D46" s="12" t="n">
+      <c r="D46" s="11" t="n">
         <v>30.5</v>
       </c>
-      <c r="E46" s="12" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="F46" s="12" t="n">
+      <c r="E46" s="11" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="F46" s="11" t="n">
         <v>25.5</v>
       </c>
-      <c r="G46" s="12" t="n">
+      <c r="G46" s="11" t="n">
         <v>10.1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>88.7</v>
+        <v>18.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>18.7</v>
+        <v>11.7</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="n">
+        <v>1.5</v>
+      </c>
       <c r="L46" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="M46" s="8" t="n">
-        <v>20.6</v>
+      <c r="M46" s="3" t="n">
+        <v>20</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>198.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="Q46" s="8" t="n">
-        <v>29.3</v>
+        <v>0.4</v>
+      </c>
+      <c r="Q46" s="3" t="n">
+        <v>29.9</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>645.1</v>
+        <v>24.5</v>
       </c>
       <c r="S46" s="8" t="n">
-        <v>27.7</v>
+        <v>71.7</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>168.3</v>
+        <v>68.3</v>
       </c>
       <c r="U46" s="8" t="n">
-        <v>292.2</v>
-      </c>
-      <c r="V46" s="3" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="V46" s="8" t="n">
         <v>26.8</v>
       </c>
       <c r="W46" s="8" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="X46" s="8" t="n">
-        <v>22.6</v>
+        <v>73.8</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>27.8</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>18.5</v>
+        <v>128.5</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>7.8</v>
+        <v>18.7</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -41,8 +41,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="FF6DCD57"/>
+        <bgColor rgb="FF6DCD57"/>
       </patternFill>
     </fill>
     <fill>
@@ -53,8 +53,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF6DCD57"/>
-        <bgColor rgb="FF6DCD57"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -149,25 +149,28 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -783,16 +786,16 @@
       <c r="C4" s="3" t="n">
         <v>351.3</v>
       </c>
-      <c r="D4" s="11" t="n">
-        <v>33.5</v>
-      </c>
-      <c r="E4" s="11" t="n">
+      <c r="D4" s="9" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="E4" s="9" t="n">
         <v>22.7</v>
       </c>
-      <c r="F4" s="11" t="n">
+      <c r="F4" s="9" t="n">
         <v>28.1</v>
       </c>
-      <c r="G4" s="11" t="n">
+      <c r="G4" s="9" t="n">
         <v>10.8</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -802,7 +805,7 @@
         <v>2.6</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>22.1</v>
+        <v>14.4</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>0</v>
@@ -813,14 +816,14 @@
       <c r="M4" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="N4" s="8" t="n">
-        <v>76.40000000000001</v>
+      <c r="N4" s="3" t="n">
+        <v>28.4</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>97.5</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>10.7</v>
+        <v>6.1</v>
       </c>
       <c r="Q4" s="8" t="n">
         <v>33</v>
@@ -828,7 +831,7 @@
       <c r="R4" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="S4" s="3" t="n">
+      <c r="S4" s="8" t="n">
         <v>28.1</v>
       </c>
       <c r="T4" s="3" t="n">
@@ -843,11 +846,11 @@
       <c r="W4" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="X4" s="3" t="n">
-        <v>29.1</v>
+      <c r="X4" s="8" t="n">
+        <v>92.09999999999999</v>
       </c>
       <c r="Y4" s="3" t="n">
-        <v>1754.3</v>
+        <v>74.3</v>
       </c>
       <c r="Z4" s="3" t="inlineStr"/>
       <c r="AA4" s="3" t="inlineStr">
@@ -866,26 +869,26 @@
       <c r="C5" s="3" t="n">
         <v>278.1</v>
       </c>
-      <c r="D5" s="11" t="n">
-        <v>31</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="F5" s="11" t="n">
+      <c r="D5" s="9" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="F5" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="9" t="n">
         <v>10.3</v>
       </c>
       <c r="H5" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>31.1</v>
+        <v>3.1</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>1.9</v>
@@ -893,8 +896,8 @@
       <c r="L5" s="3" t="n">
         <v>21.6</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>21.4</v>
+      <c r="M5" s="8" t="n">
+        <v>22.4</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>25.4</v>
@@ -915,7 +918,7 @@
         <v>26.2</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="U5" s="3" t="n">
         <v>8.4</v>
@@ -926,7 +929,7 @@
       <c r="W5" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X5" s="8" t="n">
+      <c r="X5" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="Y5" s="3" t="n">
@@ -949,19 +952,19 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>268.1</v>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E6" s="11" t="n">
+        <v>368</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="E6" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="F6" s="11" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="G6" s="11" t="n">
-        <v>10.3</v>
+      <c r="F6" s="9" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>20.3</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>20.2</v>
@@ -970,7 +973,7 @@
         <v>2</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>9.199999999999999</v>
+        <v>3.2</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>0</v>
@@ -985,13 +988,13 @@
         <v>25.1</v>
       </c>
       <c r="O6" s="3" t="n">
-        <v>92</v>
+        <v>972</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="8" t="n">
-        <v>12.4</v>
+      <c r="Q6" s="3" t="n">
+        <v>31.4</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>24.9</v>
@@ -1003,7 +1006,7 @@
         <v>99.59999999999999</v>
       </c>
       <c r="U6" s="3" t="n">
-        <v>88.59999999999999</v>
+        <v>18.6</v>
       </c>
       <c r="V6" s="3" t="n">
         <v>28.3</v>
@@ -1015,10 +1018,10 @@
         <v>29</v>
       </c>
       <c r="Y6" s="3" t="n">
-        <v>45.4</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="AA6" s="3" t="inlineStr">
         <is>
@@ -1034,31 +1037,31 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>418.2</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>36.4</v>
-      </c>
-      <c r="E7" s="11" t="n">
+        <v>8218.200000000001</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E7" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="F7" s="11" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="G7" s="3" t="n">
+      <c r="F7" s="9" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="G7" s="9" t="n">
         <v>11.4</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>19.4</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>21.8</v>
+        <v>2.8</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>21.1</v>
@@ -1087,8 +1090,8 @@
       <c r="T7" s="3" t="n">
         <v>59.5</v>
       </c>
-      <c r="U7" s="8" t="n">
-        <v>29.1</v>
+      <c r="U7" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="V7" s="3" t="n">
         <v>28.7</v>
@@ -1119,31 +1122,31 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>9681.1</v>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F8" s="11" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="G8" s="3" t="n">
-        <v>12.5</v>
+        <v>368</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>11.5</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>20.6</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>5.8</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
         <v>22.1</v>
@@ -1155,7 +1158,7 @@
         <v>25.7</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>96.5</v>
+        <v>98.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>10.9</v>
@@ -1170,7 +1173,7 @@
         <v>27.9</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>94.8</v>
+        <v>4.8</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>23</v>
@@ -1188,7 +1191,7 @@
         <v>74.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>19.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1204,22 +1207,22 @@
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1185</v>
-      </c>
-      <c r="D9" s="10" t="n">
+        <v>1783</v>
+      </c>
+      <c r="D9" s="9" t="n">
         <v>161.7</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="9" t="n">
         <v>107.4</v>
       </c>
-      <c r="F9" s="10" t="n">
-        <v>1354.9</v>
+      <c r="F9" s="9" t="n">
+        <v>134.5</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>5.4</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>12100.8</v>
+        <v>100.8</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>12</v>
@@ -1234,10 +1237,10 @@
         <v>109.4</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>1108</v>
+        <v>108</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>128.2</v>
+        <v>12.8</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>487</v>
@@ -1246,13 +1249,13 @@
         <v>13.1</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>156.6</v>
+        <v>8556.6</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>124.4</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>153790.5</v>
+        <v>127.5</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>308</v>
@@ -1261,16 +1264,16 @@
         <v>90.09999999999999</v>
       </c>
       <c r="V9" s="3" t="n">
-        <v>122</v>
+        <v>32.7</v>
       </c>
       <c r="W9" s="3" t="n">
-        <v>1420</v>
+        <v>120</v>
       </c>
       <c r="X9" s="3" t="n">
-        <v>1139.5</v>
+        <v>13.9</v>
       </c>
       <c r="Y9" s="3" t="n">
-        <v>589.1</v>
+        <v>389.1</v>
       </c>
       <c r="Z9" s="3" t="n">
         <v>41.8</v>
@@ -1289,32 +1292,34 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>356.7</v>
-      </c>
-      <c r="D10" s="11" t="n">
+        <v>256.7</v>
+      </c>
+      <c r="D10" s="9" t="n">
         <v>32.3</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="9" t="n">
         <v>21.5</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="9" t="n">
         <v>26.9</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="9" t="n">
         <v>10.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>2.2</v>
+      </c>
       <c r="J10" s="3" t="n">
         <v>4.2</v>
       </c>
-      <c r="K10" s="8" t="n">
-        <v>17.5</v>
+      <c r="K10" s="3" t="n">
+        <v>1.7</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>21.9</v>
+        <v>22.9</v>
       </c>
       <c r="M10" s="3" t="n">
         <v>21.6</v>
@@ -1338,7 +1343,7 @@
         <v>27.5</v>
       </c>
       <c r="T10" s="3" t="n">
-        <v>161.6</v>
+        <v>61.6</v>
       </c>
       <c r="U10" s="8" t="n">
         <v>18</v>
@@ -1346,14 +1351,14 @@
       <c r="V10" s="3" t="n">
         <v>27.1</v>
       </c>
-      <c r="W10" s="8" t="n">
+      <c r="W10" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="X10" s="8" t="n">
+      <c r="X10" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="Y10" s="3" t="n">
-        <v>1417.8</v>
+        <v>877.8</v>
       </c>
       <c r="Z10" s="3" t="n">
         <v>18.4</v>
@@ -1374,32 +1379,32 @@
       <c r="C11" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="9" t="n">
         <v>33.3</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="9" t="n">
         <v>26.6</v>
       </c>
-      <c r="G11" s="11" t="n">
-        <v>13.4</v>
+      <c r="G11" s="3" t="n">
+        <v>13.8</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>88.7</v>
+        <v>18.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>14.1</v>
+        <v>18.1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="L11" s="8" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>20.6</v>
       </c>
       <c r="M11" s="3" t="n">
         <v>20.5</v>
@@ -1423,7 +1428,7 @@
         <v>28.5</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>156.3</v>
+        <v>256.3</v>
       </c>
       <c r="U11" s="3" t="n">
         <v>22.1</v>
@@ -1441,7 +1446,7 @@
         <v>10.4</v>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>12.2</v>
+        <v>112.2</v>
       </c>
       <c r="AA11" s="3" t="inlineStr">
         <is>
@@ -1459,26 +1464,26 @@
       <c r="C12" s="3" t="n">
         <v>1218.2</v>
       </c>
-      <c r="D12" s="11" t="n">
+      <c r="D12" s="9" t="n">
         <v>32.8</v>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="9" t="n">
         <v>20.2</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="9" t="n">
         <v>26.5</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="9" t="n">
         <v>12.6</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>4.8</v>
@@ -1490,7 +1495,7 @@
         <v>20.1</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>22.5</v>
+        <v>23.3</v>
       </c>
       <c r="O12" s="3" t="n">
         <v>97</v>
@@ -1508,7 +1513,7 @@
         <v>28.7</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="U12" s="3" t="n">
         <v>20.8</v>
@@ -1519,14 +1524,14 @@
       <c r="W12" s="3" t="n">
         <v>25.6</v>
       </c>
-      <c r="X12" s="8" t="n">
+      <c r="X12" s="3" t="n">
         <v>30.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>13.2</v>
+        <v>713.2</v>
       </c>
       <c r="Z12" s="3" t="n">
-        <v>111.1</v>
+        <v>11.1</v>
       </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
@@ -1542,25 +1547,25 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>230.1</v>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>29.1</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="F13" s="11" t="n">
+        <v>238.1</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F13" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="9" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.1</v>
@@ -1581,7 +1586,7 @@
         <v>97</v>
       </c>
       <c r="P13" s="3" t="n">
-        <v>18.7</v>
+        <v>10.7</v>
       </c>
       <c r="Q13" s="3" t="n">
         <v>29.1</v>
@@ -1604,11 +1609,11 @@
       <c r="W13" s="3" t="n">
         <v>23.8</v>
       </c>
-      <c r="X13" s="8" t="n">
+      <c r="X13" s="3" t="n">
         <v>27.8</v>
       </c>
       <c r="Y13" s="3" t="n">
-        <v>800.8</v>
+        <v>80.8</v>
       </c>
       <c r="Z13" s="3" t="n">
         <v>6.6</v>
@@ -1627,18 +1632,18 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>821.4</v>
-      </c>
-      <c r="D14" s="11" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="E14" s="11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F14" s="11" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="G14" s="11" t="n">
+        <v>1221.4</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="G14" s="9" t="n">
         <v>8.1</v>
       </c>
       <c r="H14" s="8" t="n">
@@ -1651,7 +1656,7 @@
         <v>11.6</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>21.1</v>
@@ -1693,10 +1698,10 @@
         <v>28.6</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>185.1</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1714,17 +1719,17 @@
       <c r="C15" s="3" t="n">
         <v>340.8</v>
       </c>
-      <c r="D15" s="11" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="G15" s="3" t="n">
-        <v>82.09999999999999</v>
+      <c r="D15" s="9" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <v>12.1</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>17.4</v>
@@ -1732,11 +1737,11 @@
       <c r="I15" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="J15" s="8" t="n">
-        <v>8</v>
+      <c r="J15" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>10.8</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>19.5</v>
@@ -1753,7 +1758,7 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="3" t="n">
+      <c r="Q15" s="8" t="n">
         <v>30</v>
       </c>
       <c r="R15" s="3" t="n">
@@ -1765,10 +1770,10 @@
       <c r="T15" s="3" t="n">
         <v>71</v>
       </c>
-      <c r="U15" s="8" t="n">
-        <v>29.3</v>
-      </c>
-      <c r="V15" s="3" t="n">
+      <c r="U15" s="3" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="V15" s="8" t="n">
         <v>25</v>
       </c>
       <c r="W15" s="3" t="n">
@@ -1778,7 +1783,7 @@
         <v>24.3</v>
       </c>
       <c r="Y15" s="3" t="n">
-        <v>716.6</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="Z15" s="3" t="n">
         <v>7.4</v>
@@ -1799,38 +1804,38 @@
       <c r="C16" s="3" t="n">
         <v>15308.1</v>
       </c>
-      <c r="D16" s="10" t="n">
-        <v>1524.2</v>
-      </c>
-      <c r="E16" s="10" t="n">
+      <c r="D16" s="9" t="n">
+        <v>154.2</v>
+      </c>
+      <c r="E16" s="15" t="n">
         <v>99.2</v>
       </c>
-      <c r="F16" s="10" t="n">
-        <v>126.8</v>
-      </c>
-      <c r="G16" s="15" t="n">
-        <v>52.5</v>
+      <c r="F16" s="15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>54.5</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>19.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>19.7</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>162.4</v>
+        <v>16.4</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>102.2</v>
+        <v>2.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>110.1</v>
+        <v>10.1</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1129</v>
+        <v>111.9</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>490</v>
@@ -1842,31 +1847,31 @@
         <v>152.4</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>125.7</v>
+        <v>25.7</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>142.7</v>
+        <v>14.2</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>331</v>
       </c>
       <c r="U16" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="V16" s="3" t="n">
-        <v>412.6</v>
+        <v>12.6</v>
       </c>
       <c r="W16" s="3" t="n">
-        <v>251.2</v>
+        <v>212</v>
       </c>
       <c r="X16" s="3" t="n">
         <v>140</v>
       </c>
       <c r="Y16" s="3" t="n">
-        <v>13861.1</v>
+        <v>386.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>14.2</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1884,14 +1889,14 @@
       <c r="C17" s="3" t="n">
         <v>306.2</v>
       </c>
-      <c r="D17" s="11" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="E17" s="11" t="n">
+      <c r="D17" s="9" t="n">
+        <v>30.4</v>
+      </c>
+      <c r="E17" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="F17" s="11" t="n">
-        <v>25.6</v>
+      <c r="F17" s="9" t="n">
+        <v>25.1</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>10.9</v>
@@ -1906,7 +1911,7 @@
         <v>3.9</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>20.6</v>
@@ -1914,16 +1919,16 @@
       <c r="M17" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="N17" s="8" t="n">
-        <v>888.6</v>
+      <c r="N17" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="O17" s="3" t="n">
-        <v>198</v>
+        <v>98</v>
       </c>
       <c r="P17" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q17" s="8" t="n">
+      <c r="Q17" s="3" t="n">
         <v>30.5</v>
       </c>
       <c r="R17" s="3" t="n">
@@ -1933,9 +1938,9 @@
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>166.2</v>
-      </c>
-      <c r="U17" s="8" t="n">
+        <v>1966.2</v>
+      </c>
+      <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
       <c r="V17" s="3" t="n">
@@ -1944,11 +1949,11 @@
       <c r="W17" s="3" t="n">
         <v>24.1</v>
       </c>
-      <c r="X17" s="8" t="n">
+      <c r="X17" s="3" t="n">
         <v>28</v>
       </c>
       <c r="Y17" s="3" t="n">
-        <v>141.2</v>
+        <v>772.2</v>
       </c>
       <c r="Z17" s="3" t="n">
         <v>18.5</v>
@@ -1969,23 +1974,23 @@
       <c r="C18" s="3" t="n">
         <v>3341.1</v>
       </c>
-      <c r="D18" s="11" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="E18" s="11" t="n">
+      <c r="D18" s="9" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="E18" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="9" t="n">
         <v>25.7</v>
       </c>
-      <c r="G18" s="11" t="n">
+      <c r="G18" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="H18" s="8" t="n">
-        <v>171.4</v>
+      <c r="H18" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.4</v>
+        <v>8.4</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>14</v>
@@ -1994,10 +1999,10 @@
         <v>0</v>
       </c>
       <c r="L18" s="8" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>29.4</v>
+        <v>19.7</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>19.4</v>
       </c>
       <c r="N18" s="3" t="n">
         <v>22.3</v>
@@ -2018,7 +2023,7 @@
         <v>27.8</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>158</v>
+        <v>58</v>
       </c>
       <c r="U18" s="3" t="n">
         <v>20.1</v>
@@ -2029,14 +2034,14 @@
       <c r="W18" s="3" t="n">
         <v>25.1</v>
       </c>
-      <c r="X18" s="8" t="n">
+      <c r="X18" s="3" t="n">
         <v>29.8</v>
       </c>
       <c r="Y18" s="3" t="n">
         <v>77.59999999999999</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>18.6</v>
+        <v>8.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2054,19 +2059,19 @@
       <c r="C19" s="3" t="n">
         <v>326.2</v>
       </c>
-      <c r="D19" s="11" t="n">
+      <c r="D19" s="9" t="n">
         <v>32.2</v>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="F19" s="11" t="n">
+      <c r="F19" s="9" t="n">
         <v>26.3</v>
       </c>
-      <c r="G19" s="11" t="n">
+      <c r="G19" s="9" t="n">
         <v>11.7</v>
       </c>
-      <c r="H19" s="8" t="n">
+      <c r="H19" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="I19" s="3" t="n">
@@ -2085,7 +2090,7 @@
         <v>20.7</v>
       </c>
       <c r="N19" s="3" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="O19" s="3" t="n">
         <v>98</v>
@@ -2093,11 +2098,11 @@
       <c r="P19" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q19" s="8" t="n">
+      <c r="Q19" s="3" t="n">
         <v>31.7</v>
       </c>
-      <c r="R19" s="8" t="n">
-        <v>55.3</v>
+      <c r="R19" s="3" t="n">
+        <v>25.3</v>
       </c>
       <c r="S19" s="3" t="n">
         <v>28.2</v>
@@ -2105,13 +2110,13 @@
       <c r="T19" s="3" t="n">
         <v>60.5</v>
       </c>
-      <c r="U19" s="8" t="n">
+      <c r="U19" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="V19" s="8" t="n">
+      <c r="V19" s="3" t="n">
         <v>25.7</v>
       </c>
-      <c r="W19" s="8" t="n">
+      <c r="W19" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2137,22 +2142,22 @@
         </is>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2899</v>
-      </c>
-      <c r="D20" s="11" t="n">
+        <v>299</v>
+      </c>
+      <c r="D20" s="9" t="n">
         <v>29.7</v>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="9" t="n">
         <v>19.7</v>
       </c>
-      <c r="F20" s="11" t="n">
+      <c r="F20" s="9" t="n">
         <v>24.7</v>
       </c>
-      <c r="G20" s="11" t="n">
+      <c r="G20" s="9" t="n">
         <v>10</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>88.40000000000001</v>
+        <v>18.4</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>11.8</v>
@@ -2193,10 +2198,10 @@
       <c r="U20" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V20" s="8" t="n">
+      <c r="V20" s="3" t="n">
         <v>25</v>
       </c>
-      <c r="W20" s="8" t="n">
+      <c r="W20" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2224,26 +2229,26 @@
       <c r="C21" s="3" t="n">
         <v>357.5</v>
       </c>
-      <c r="D21" s="11" t="n">
+      <c r="D21" s="9" t="n">
         <v>30.1</v>
       </c>
-      <c r="E21" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="F21" s="11" t="n">
+      <c r="E21" s="9" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="F21" s="9" t="n">
         <v>24.1</v>
       </c>
-      <c r="G21" s="15" t="n">
-        <v>82.8</v>
-      </c>
-      <c r="H21" s="8" t="n">
+      <c r="G21" s="9" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H21" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>12.8</v>
+        <v>3.8</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>0</v>
@@ -2258,7 +2263,7 @@
         <v>21.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0</v>
@@ -2284,14 +2289,14 @@
       <c r="W21" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="X21" s="8" t="n">
+      <c r="X21" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>18484.1</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>1.4</v>
+        <v>5.4</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2307,34 +2312,34 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>992.9</v>
-      </c>
-      <c r="D22" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="E22" s="11" t="n">
-        <v>18</v>
-      </c>
-      <c r="F22" s="11" t="n">
+        <v>1492.9</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="F22" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="G22" s="8" t="n">
+      <c r="G22" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>11.4</v>
+        <v>17.4</v>
       </c>
       <c r="I22" s="3" t="n">
         <v>11.9</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="L22" s="8" t="n">
-        <v>19.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="M22" s="3" t="n">
         <v>19.1</v>
@@ -2343,13 +2348,13 @@
         <v>22.1</v>
       </c>
       <c r="O22" s="3" t="n">
-        <v>10800</v>
+        <v>100</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="R22" s="3" t="n">
         <v>25.8</v>
@@ -2361,7 +2366,7 @@
         <v>66.8</v>
       </c>
       <c r="U22" s="3" t="n">
-        <v>14.8</v>
+        <v>4.8</v>
       </c>
       <c r="V22" s="3" t="n">
         <v>24</v>
@@ -2394,20 +2399,20 @@
       <c r="C23" s="3" t="n">
         <v>1610.1</v>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D23" s="9" t="n">
         <v>155.4</v>
       </c>
-      <c r="E23" s="10" t="n">
-        <v>95.2</v>
-      </c>
-      <c r="F23" s="11" t="n">
-        <v>125.8</v>
+      <c r="E23" s="15" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <v>225.8</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>59</v>
+        <v>59.2</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>10.4</v>
@@ -2416,7 +2421,7 @@
         <v>18.4</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>98.40000000000001</v>
@@ -2425,7 +2430,7 @@
         <v>97.8</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1613.3</v>
+        <v>12.2</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>494</v>
@@ -2437,31 +2442,31 @@
         <v>152.9</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>1240.6</v>
+        <v>124.6</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>115394.7</v>
+        <v>1139.7</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>320</v>
       </c>
       <c r="U23" s="3" t="n">
-        <v>796.1</v>
+        <v>795.1</v>
       </c>
       <c r="V23" s="3" t="n">
-        <v>122.3</v>
+        <v>29.2</v>
       </c>
       <c r="W23" s="3" t="n">
-        <v>12.8</v>
+        <v>118.2</v>
       </c>
       <c r="X23" s="3" t="n">
-        <v>140.6</v>
+        <v>141.5</v>
       </c>
       <c r="Y23" s="3" t="n">
         <v>422</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>126.5</v>
+        <v>26.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2477,34 +2482,34 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>32</v>
-      </c>
-      <c r="D24" s="11" t="n">
+        <v>380.3</v>
+      </c>
+      <c r="D24" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="E24" s="11" t="n">
+      <c r="E24" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="F24" s="11" t="n">
+      <c r="F24" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="G24" s="11" t="n">
+      <c r="G24" s="9" t="n">
         <v>11.9</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K24" s="3" t="inlineStr"/>
+        <v>2.1</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr"/>
+      <c r="K24" s="3" t="n">
+        <v>0.2</v>
+      </c>
       <c r="L24" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="M24" s="8" t="n">
+      <c r="M24" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2514,7 +2519,7 @@
         <v>0.4</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>5.3</v>
+        <v>0.3</v>
       </c>
       <c r="Q24" s="3" t="n">
         <v>30.6</v>
@@ -2560,25 +2565,25 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>171.8</v>
-      </c>
-      <c r="D25" s="11" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="D25" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="E25" s="11" t="n">
+      <c r="E25" s="9" t="n">
         <v>19.7</v>
       </c>
-      <c r="F25" s="11" t="n">
+      <c r="F25" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="G25" s="3" t="n">
-        <v>10.9</v>
+      <c r="G25" s="9" t="n">
+        <v>10.3</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>11.4</v>
+        <v>0.4</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>2.3</v>
@@ -2586,11 +2591,11 @@
       <c r="K25" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="L25" s="3" t="n">
-        <v>20</v>
+      <c r="L25" s="8" t="n">
+        <v>110.4</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>19.8</v>
+        <v>494.4</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>22.9</v>
@@ -2619,7 +2624,7 @@
       <c r="V25" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="W25" s="3" t="n">
+      <c r="W25" s="8" t="n">
         <v>21</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2645,31 +2650,31 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>845</v>
-      </c>
-      <c r="D26" s="11" t="n">
+        <v>2345</v>
+      </c>
+      <c r="D26" s="9" t="n">
         <v>31.7</v>
       </c>
-      <c r="E26" s="11" t="n">
+      <c r="E26" s="9" t="n">
         <v>20.5</v>
       </c>
-      <c r="F26" s="11" t="n">
+      <c r="F26" s="9" t="n">
         <v>26.1</v>
       </c>
-      <c r="G26" s="11" t="n">
+      <c r="G26" s="9" t="n">
         <v>11.2</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>886.8</v>
+        <v>18.6</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>14.4</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>20.6</v>
@@ -2678,16 +2683,14 @@
         <v>20.4</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>23.8</v>
+        <v>15.8</v>
       </c>
       <c r="O26" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="P26" s="3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q26" s="8" t="n">
-        <v>85.40000000000001</v>
+      <c r="P26" s="3" t="inlineStr"/>
+      <c r="Q26" s="3" t="n">
+        <v>88.40000000000001</v>
       </c>
       <c r="R26" s="3" t="n">
         <v>24.1</v>
@@ -2730,25 +2733,25 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1418.2</v>
-      </c>
-      <c r="D27" s="11" t="n">
+        <v>418.2</v>
+      </c>
+      <c r="D27" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="E27" s="11" t="n">
+      <c r="E27" s="9" t="n">
         <v>19.2</v>
       </c>
-      <c r="F27" s="11" t="n">
+      <c r="F27" s="9" t="n">
         <v>28.1</v>
       </c>
-      <c r="G27" s="8" t="n">
-        <v>38.7</v>
+      <c r="G27" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="H27" s="8" t="n">
         <v>17.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>13.1</v>
+        <v>3.1</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>5.2</v>
@@ -2762,7 +2765,7 @@
       <c r="M27" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N27" s="3" t="n">
+      <c r="N27" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="O27" s="3" t="n">
@@ -2789,11 +2792,11 @@
       <c r="V27" s="3" t="n">
         <v>29.3</v>
       </c>
-      <c r="W27" s="8" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="X27" s="3" t="n">
-        <v>30.2</v>
+      <c r="W27" s="3" t="n">
+        <v>655.1</v>
+      </c>
+      <c r="X27" s="8" t="n">
+        <v>8.199999999999999</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>74.2</v>
@@ -2817,20 +2820,20 @@
       <c r="C28" s="3" t="n">
         <v>282.3</v>
       </c>
-      <c r="D28" s="11" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="E28" s="11" t="n">
+      <c r="D28" s="9" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="E28" s="9" t="n">
         <v>19.8</v>
       </c>
-      <c r="F28" s="11" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="G28" s="11" t="n">
+      <c r="F28" s="9" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="G28" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>88.40000000000001</v>
+        <v>18.4</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>1.9</v>
@@ -2839,7 +2842,7 @@
         <v>3.2</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>20.1</v>
@@ -2856,8 +2859,8 @@
       <c r="P28" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q28" s="8" t="n">
-        <v>979.8</v>
+      <c r="Q28" s="3" t="n">
+        <v>29.7</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>25.1</v>
@@ -2869,7 +2872,7 @@
         <v>69.40000000000001</v>
       </c>
       <c r="U28" s="3" t="n">
-        <v>18.7</v>
+        <v>12.7</v>
       </c>
       <c r="V28" s="3" t="n">
         <v>24.4</v>
@@ -2877,11 +2880,11 @@
       <c r="W28" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X28" s="8" t="n">
-        <v>659.5</v>
+      <c r="X28" s="3" t="n">
+        <v>26.3</v>
       </c>
       <c r="Y28" s="3" t="n">
-        <v>186</v>
+        <v>86</v>
       </c>
       <c r="Z28" s="3" t="n">
         <v>0.2</v>
@@ -2900,18 +2903,18 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>122112.1</v>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="F29" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="F29" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="G29" s="11" t="n">
+      <c r="G29" s="9" t="n">
         <v>8.9</v>
       </c>
       <c r="H29" s="3" t="n">
@@ -2921,14 +2924,14 @@
         <v>1.1</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="n">
-        <v>21.9</v>
+      <c r="L29" s="8" t="n">
+        <v>18.9</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>241.9</v>
+        <v>21.5</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>25.4</v>
@@ -2942,7 +2945,7 @@
       <c r="Q29" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="8" t="n">
+      <c r="R29" s="3" t="n">
         <v>24.8</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2952,7 +2955,7 @@
         <v>73.7</v>
       </c>
       <c r="U29" s="8" t="n">
-        <v>51.5</v>
+        <v>7.3</v>
       </c>
       <c r="V29" s="3" t="n">
         <v>25</v>
@@ -2960,14 +2963,14 @@
       <c r="W29" s="3" t="n">
         <v>22.6</v>
       </c>
-      <c r="X29" s="8" t="n">
+      <c r="X29" s="3" t="n">
         <v>25.9</v>
       </c>
       <c r="Y29" s="3" t="n">
-        <v>181.9</v>
+        <v>81.8</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>15.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2982,56 +2985,54 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C30" s="3" t="n">
-        <v>625.1</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F30" s="10" t="n">
+      <c r="C30" s="3" t="inlineStr"/>
+      <c r="D30" s="15" t="n">
+        <v>351.5</v>
+      </c>
+      <c r="E30" s="9" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="F30" s="15" t="n">
         <v>1120</v>
       </c>
-      <c r="G30" s="15" t="n">
-        <v>57</v>
+      <c r="G30" s="16" t="n">
+        <v>56.8</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>92.2</v>
+        <v>922.8</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>19.9</v>
+        <v>9.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>114.8</v>
+        <v>11.7</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>123.7</v>
+        <v>23.7</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>180.2</v>
+        <v>2.2</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>110.2</v>
+        <v>10.1</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>122.8</v>
+        <v>111.3</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>489.5</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>14.5</v>
+        <v>75.5</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>312.1</v>
+        <v>122</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>13.5</v>
+        <v>183.5</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>344.5</v>
@@ -3070,19 +3071,17 @@
       <c r="C31" s="3" t="n">
         <v>272.7</v>
       </c>
-      <c r="D31" s="15" t="n">
-        <v>1246.1</v>
-      </c>
-      <c r="E31" s="11" t="n">
+      <c r="D31" s="9" t="n">
+        <v>31.3</v>
+      </c>
+      <c r="E31" s="9" t="n">
         <v>19.9</v>
       </c>
-      <c r="F31" s="15" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>11.4</v>
-      </c>
-      <c r="H31" s="8" t="n">
+      <c r="F31" s="9" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
@@ -3119,23 +3118,23 @@
       <c r="T31" s="3" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="U31" s="3" t="n">
+      <c r="U31" s="8" t="n">
         <v>13.8</v>
       </c>
-      <c r="V31" s="8" t="n">
+      <c r="V31" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="W31" s="3" t="n">
-        <v>25.1</v>
+        <v>23.1</v>
       </c>
       <c r="X31" s="8" t="n">
         <v>26.7</v>
       </c>
       <c r="Y31" s="3" t="n">
-        <v>182.3</v>
+        <v>82.3</v>
       </c>
       <c r="Z31" s="3" t="n">
-        <v>1682.8</v>
+        <v>16.2</v>
       </c>
       <c r="AA31" s="3" t="inlineStr">
         <is>
@@ -3153,26 +3152,26 @@
       <c r="C32" s="3" t="n">
         <v>263.5</v>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="D32" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="E32" s="11" t="n">
+      <c r="E32" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="F32" s="11" t="n">
+      <c r="F32" s="9" t="n">
         <v>24.7</v>
       </c>
-      <c r="G32" s="11" t="n">
+      <c r="G32" s="9" t="n">
         <v>8.6</v>
       </c>
-      <c r="H32" s="8" t="n">
+      <c r="H32" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>12.4</v>
+        <v>2.4</v>
       </c>
       <c r="K32" s="3" t="n">
         <v>3.4</v>
@@ -3214,13 +3213,13 @@
         <v>24.5</v>
       </c>
       <c r="X32" s="3" t="n">
-        <v>99.09999999999999</v>
+        <v>29.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>82.09999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>16.4</v>
+        <v>6.7</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3236,18 +3235,18 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="D33" s="11" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="D33" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="E33" s="11" t="n">
+      <c r="E33" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="F33" s="11" t="n">
+      <c r="F33" s="9" t="n">
         <v>22.9</v>
       </c>
-      <c r="G33" s="11" t="n">
+      <c r="G33" s="9" t="n">
         <v>4.6</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3257,10 +3256,10 @@
         <v>10.5</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>1.3</v>
+        <v>12.3</v>
       </c>
       <c r="K33" s="8" t="n">
-        <v>26.5</v>
+        <v>22.5</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>20.8</v>
@@ -3287,7 +3286,7 @@
         <v>25.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>89.40000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>5</v>
@@ -3305,7 +3304,7 @@
         <v>91.8</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>12.3</v>
+        <v>2.3</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3323,16 +3322,16 @@
       <c r="C34" s="3" t="n">
         <v>117.2</v>
       </c>
-      <c r="D34" s="11" t="n">
+      <c r="D34" s="9" t="n">
         <v>30.6</v>
       </c>
-      <c r="E34" s="11" t="n">
+      <c r="E34" s="9" t="n">
         <v>19.1</v>
       </c>
-      <c r="F34" s="11" t="n">
+      <c r="F34" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="G34" s="11" t="n">
+      <c r="G34" s="9" t="n">
         <v>11.5</v>
       </c>
       <c r="H34" s="8" t="n">
@@ -3341,7 +3340,9 @@
       <c r="I34" s="3" t="n">
         <v>11.9</v>
       </c>
-      <c r="J34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="K34" s="3" t="n">
         <v>5.9</v>
       </c>
@@ -3358,7 +3359,7 @@
         <v>100</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q34" s="3" t="n">
         <v>30.1</v>
@@ -3370,25 +3371,25 @@
         <v>29.9</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>80.2</v>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v>20.6</v>
+        <v>70.2</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>12.6</v>
       </c>
       <c r="V34" s="3" t="n">
         <v>26.3</v>
       </c>
-      <c r="W34" s="3" t="n">
+      <c r="W34" s="8" t="n">
         <v>21</v>
       </c>
       <c r="X34" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>62.6</v>
+        <v>62.5</v>
       </c>
       <c r="Z34" s="3" t="n">
-        <v>182.8</v>
+        <v>12.8</v>
       </c>
       <c r="AA34" s="3" t="inlineStr">
         <is>
@@ -3406,16 +3407,16 @@
       <c r="C35" s="3" t="n">
         <v>284.4</v>
       </c>
-      <c r="D35" s="11" t="n">
+      <c r="D35" s="9" t="n">
         <v>29.5</v>
       </c>
-      <c r="E35" s="11" t="n">
+      <c r="E35" s="9" t="n">
         <v>18.8</v>
       </c>
-      <c r="F35" s="11" t="n">
+      <c r="F35" s="9" t="n">
         <v>24.1</v>
       </c>
-      <c r="G35" s="11" t="n">
+      <c r="G35" s="9" t="n">
         <v>10.7</v>
       </c>
       <c r="H35" s="8" t="n">
@@ -3430,14 +3431,14 @@
       <c r="K35" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="L35" s="8" t="n">
+      <c r="L35" s="3" t="n">
         <v>19</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>19</v>
       </c>
       <c r="N35" s="8" t="n">
-        <v>18.9</v>
+        <v>14.9</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>100</v>
@@ -3455,7 +3456,7 @@
         <v>29</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>75.40000000000001</v>
+        <v>25.4</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>9.4</v>
@@ -3467,13 +3468,13 @@
         <v>24.4</v>
       </c>
       <c r="X35" s="8" t="n">
-        <v>2959.3</v>
+        <v>95.3</v>
       </c>
       <c r="Y35" s="3" t="n">
         <v>85.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>164.9</v>
+        <v>14.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3489,19 +3490,19 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1117.2</v>
-      </c>
-      <c r="D36" s="11" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="D36" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="11" t="n">
+      <c r="E36" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="F36" s="11" t="n">
+      <c r="F36" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="G36" s="11" t="n">
-        <v>7.5</v>
+      <c r="G36" s="3" t="n">
+        <v>1.5</v>
       </c>
       <c r="H36" s="8" t="n">
         <v>19</v>
@@ -3510,7 +3511,7 @@
         <v>0.6</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>11.3</v>
@@ -3528,7 +3529,7 @@
         <v>98</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="Q36" s="3" t="n">
         <v>21.5</v>
@@ -3542,14 +3543,12 @@
       <c r="T36" s="3" t="n">
         <v>94.8</v>
       </c>
-      <c r="U36" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="U36" s="3" t="inlineStr"/>
       <c r="V36" s="3" t="n">
         <v>21.4</v>
       </c>
       <c r="W36" s="3" t="n">
-        <v>20.8</v>
+        <v>61.8</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>24.2</v>
@@ -3558,7 +3557,7 @@
         <v>94.8</v>
       </c>
       <c r="Z36" s="3" t="n">
-        <v>15.3</v>
+        <v>19.3</v>
       </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
@@ -3576,16 +3575,16 @@
       <c r="C37" s="3" t="n">
         <v>826.4</v>
       </c>
-      <c r="D37" s="11" t="n">
+      <c r="D37" s="9" t="n">
         <v>142.9</v>
       </c>
-      <c r="E37" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="F37" s="11" t="n">
-        <v>121.5</v>
-      </c>
-      <c r="G37" s="11" t="n">
+      <c r="E37" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="15" t="n">
+        <v>182.1</v>
+      </c>
+      <c r="G37" s="3" t="n">
         <v>42.9</v>
       </c>
       <c r="H37" s="3" t="n">
@@ -3595,55 +3594,55 @@
         <v>5.8</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>12.2</v>
+        <v>2.2</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>117.9</v>
+        <v>1807.9</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>103.4</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>28.8</v>
+        <v>22.9</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>92</v>
+        <v>20.2</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>0.8</v>
+        <v>32.2</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q37" s="3" t="n">
-        <v>233.1</v>
+        <v>133.8</v>
       </c>
       <c r="R37" s="3" t="n">
-        <v>127.2</v>
+        <v>117.2</v>
       </c>
       <c r="S37" s="3" t="n">
-        <v>136.3</v>
+        <v>13.6</v>
       </c>
       <c r="T37" s="3" t="n">
-        <v>393.6</v>
+        <v>3923.6</v>
       </c>
       <c r="U37" s="3" t="n">
         <v>40.4</v>
       </c>
       <c r="V37" s="3" t="n">
-        <v>124.1</v>
+        <v>24.1</v>
       </c>
       <c r="W37" s="3" t="n">
-        <v>11.2</v>
+        <v>112.2</v>
       </c>
       <c r="X37" s="3" t="n">
-        <v>129.8</v>
+        <v>12.2</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>12466</v>
+        <v>416</v>
       </c>
       <c r="Z37" s="3" t="n">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="AA37" s="3" t="inlineStr">
         <is>
@@ -3659,18 +3658,18 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>155.3</v>
-      </c>
-      <c r="D38" s="11" t="n">
+        <v>165.3</v>
+      </c>
+      <c r="D38" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="E38" s="11" t="n">
+      <c r="E38" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="F38" s="11" t="n">
+      <c r="F38" s="9" t="n">
         <v>24.3</v>
       </c>
-      <c r="G38" s="11" t="n">
+      <c r="G38" s="9" t="n">
         <v>8.6</v>
       </c>
       <c r="H38" s="3" t="n">
@@ -3679,17 +3678,17 @@
       <c r="I38" s="3" t="n">
         <v>1.2</v>
       </c>
-      <c r="J38" s="8" t="n">
-        <v>11.8</v>
+      <c r="J38" s="3" t="n">
+        <v>2.8</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>20.8</v>
+        <v>20.2</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>24.2</v>
@@ -3700,32 +3699,32 @@
       <c r="P38" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="3" t="n">
-        <v>26.6</v>
+      <c r="Q38" s="8" t="n">
+        <v>56.6</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="S38" s="3" t="n">
-        <v>27.3</v>
+        <v>48.5</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>828.7</v>
+        <v>78.7</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="V38" s="3" t="n">
-        <v>28.8</v>
+        <v>24.8</v>
       </c>
       <c r="W38" s="3" t="n">
         <v>22.5</v>
       </c>
-      <c r="X38" s="8" t="n">
+      <c r="X38" s="3" t="n">
         <v>26</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>183.2</v>
+        <v>83.2</v>
       </c>
       <c r="Z38" s="3" t="n">
         <v>5.6</v>
@@ -3744,28 +3743,28 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332</v>
-      </c>
-      <c r="D39" s="11" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="D39" s="9" t="n">
         <v>30.7</v>
       </c>
-      <c r="E39" s="11" t="n">
+      <c r="E39" s="9" t="n">
         <v>19.3</v>
       </c>
-      <c r="F39" s="11" t="n">
+      <c r="F39" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="G39" s="11" t="n">
+      <c r="G39" s="9" t="n">
         <v>11.4</v>
       </c>
-      <c r="H39" s="8" t="n">
+      <c r="H39" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>9.5</v>
+        <v>3.5</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
@@ -3783,7 +3782,7 @@
         <v>100</v>
       </c>
       <c r="P39" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q39" s="3" t="n">
         <v>30.7</v>
@@ -3795,7 +3794,7 @@
         <v>29.3</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>6685.3</v>
+        <v>66.5</v>
       </c>
       <c r="U39" s="3" t="n">
         <v>14.7</v>
@@ -3806,8 +3805,8 @@
       <c r="W39" s="3" t="n">
         <v>23.9</v>
       </c>
-      <c r="X39" s="8" t="n">
-        <v>17.8</v>
+      <c r="X39" s="3" t="n">
+        <v>27.2</v>
       </c>
       <c r="Y39" s="3" t="n">
         <v>72.90000000000001</v>
@@ -3829,28 +3828,28 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>278.8</v>
-      </c>
-      <c r="D40" s="11" t="n">
+        <v>2728.1</v>
+      </c>
+      <c r="D40" s="9" t="n">
         <v>30.8</v>
       </c>
-      <c r="E40" s="11" t="n">
+      <c r="E40" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="9" t="n">
         <v>25.7</v>
       </c>
-      <c r="G40" s="11" t="n">
+      <c r="G40" s="9" t="n">
         <v>10.2</v>
       </c>
-      <c r="H40" s="8" t="n">
-        <v>29</v>
+      <c r="H40" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>11.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -3861,8 +3860,8 @@
       <c r="M40" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="N40" s="3" t="n">
-        <v>24.6</v>
+      <c r="N40" s="8" t="n">
+        <v>42.6</v>
       </c>
       <c r="O40" s="3" t="n">
         <v>99</v>
@@ -3871,10 +3870,10 @@
         <v>0.2</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>80.7</v>
+        <v>30.7</v>
       </c>
       <c r="R40" s="3" t="n">
-        <v>25.8</v>
+        <v>25.3</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>28.8</v>
@@ -3883,7 +3882,7 @@
         <v>65.40000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
-        <v>19.2</v>
+        <v>15.2</v>
       </c>
       <c r="V40" s="3" t="n">
         <v>28</v>
@@ -3898,7 +3897,7 @@
         <v>72.2</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>1811.4</v>
+        <v>10.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3914,18 +3913,18 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>248.6</v>
-      </c>
-      <c r="D41" s="11" t="n">
+        <v>242.6</v>
+      </c>
+      <c r="D41" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="E41" s="11" t="n">
+      <c r="E41" s="9" t="n">
         <v>20.8</v>
       </c>
-      <c r="F41" s="11" t="n">
+      <c r="F41" s="9" t="n">
         <v>25.2</v>
       </c>
-      <c r="G41" s="11" t="n">
+      <c r="G41" s="9" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H41" s="3" t="n">
@@ -3938,7 +3937,7 @@
         <v>2.4</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>20.9</v>
@@ -3955,17 +3954,17 @@
       <c r="P41" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q41" s="8" t="n">
-        <v>95.3</v>
-      </c>
-      <c r="R41" s="8" t="n">
+      <c r="Q41" s="3" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="R41" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>80.5</v>
+        <v>20.5</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>12</v>
@@ -3980,9 +3979,11 @@
         <v>29.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>181.1</v>
-      </c>
-      <c r="Z41" s="3" t="inlineStr"/>
+        <v>81.09999999999999</v>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v>16.7</v>
+      </c>
       <c r="AA41" s="3" t="inlineStr">
         <is>
           <t>28</t>
@@ -3999,26 +4000,26 @@
       <c r="C42" s="3" t="n">
         <v>288.6</v>
       </c>
-      <c r="D42" s="11" t="n">
+      <c r="D42" s="9" t="n">
         <v>30.9</v>
       </c>
-      <c r="E42" s="11" t="n">
+      <c r="E42" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="F42" s="11" t="n">
+      <c r="F42" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="G42" s="11" t="n">
+      <c r="G42" s="9" t="n">
         <v>10.5</v>
       </c>
-      <c r="H42" s="8" t="n">
-        <v>88.59999999999999</v>
+      <c r="H42" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>10.9</v>
+        <v>2.9</v>
       </c>
       <c r="K42" s="3" t="n">
         <v>0</v>
@@ -4026,8 +4027,8 @@
       <c r="L42" s="3" t="n">
         <v>21.2</v>
       </c>
-      <c r="M42" s="3" t="n">
-        <v>21.2</v>
+      <c r="M42" s="8" t="n">
+        <v>81.2</v>
       </c>
       <c r="N42" s="3" t="n">
         <v>25.2</v>
@@ -4036,7 +4037,7 @@
         <v>100</v>
       </c>
       <c r="P42" s="3" t="n">
-        <v>18</v>
+        <v>80.8</v>
       </c>
       <c r="Q42" s="3" t="n">
         <v>30.9</v>
@@ -4059,11 +4060,11 @@
       <c r="W42" s="3" t="n">
         <v>24.6</v>
       </c>
-      <c r="X42" s="8" t="n">
-        <v>8953.5</v>
+      <c r="X42" s="3" t="n">
+        <v>29.8</v>
       </c>
       <c r="Y42" s="3" t="n">
-        <v>181.8</v>
+        <v>81.8</v>
       </c>
       <c r="Z42" s="3" t="n">
         <v>16.5</v>
@@ -4082,25 +4083,25 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>312.6</v>
-      </c>
-      <c r="D43" s="11" t="n">
+        <v>311.6</v>
+      </c>
+      <c r="D43" s="9" t="n">
         <v>30.7</v>
       </c>
-      <c r="E43" s="11" t="n">
+      <c r="E43" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="F43" s="11" t="n">
+      <c r="F43" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="G43" s="11" t="n">
+      <c r="G43" s="9" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="H43" s="8" t="n">
+      <c r="H43" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="I43" s="8" t="n">
-        <v>41.6</v>
+      <c r="I43" s="3" t="n">
+        <v>21.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>3</v>
@@ -4121,7 +4122,7 @@
         <v>99</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>24.7</v>
@@ -4145,10 +4146,10 @@
         <v>22</v>
       </c>
       <c r="X43" s="3" t="n">
-        <v>95.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="Y43" s="3" t="n">
-        <v>1849.5</v>
+        <v>84.3</v>
       </c>
       <c r="Z43" s="3" t="n">
         <v>0.6</v>
@@ -4169,9 +4170,9 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="11" t="inlineStr"/>
-      <c r="E44" s="11" t="inlineStr"/>
-      <c r="F44" s="11" t="inlineStr"/>
+      <c r="D44" s="9" t="inlineStr"/>
+      <c r="E44" s="9" t="inlineStr"/>
+      <c r="F44" s="14" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
@@ -4208,48 +4209,48 @@
       <c r="C45" s="3" t="n">
         <v>1423.4</v>
       </c>
-      <c r="D45" s="10" t="n">
-        <v>922.7</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="F45" s="10" t="n">
-        <v>10101.1</v>
-      </c>
-      <c r="G45" s="15" t="n">
-        <v>1210.1</v>
+      <c r="D45" s="15" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="F45" s="15" t="n">
+        <v>124.5</v>
+      </c>
+      <c r="G45" s="16" t="n">
+        <v>19.1</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>93.59999999999999</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>2.5</v>
+        <v>82.5</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>164.9</v>
+        <v>1814.9</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>100900160.4</v>
+        <v>105081.6</v>
       </c>
       <c r="M45" s="3" t="inlineStr"/>
       <c r="N45" s="3" t="n">
-        <v>16128.5</v>
+        <v>1820.5</v>
       </c>
       <c r="O45" s="3" t="n">
-        <v>4916</v>
+        <v>491.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>11.9</v>
+        <v>16.9</v>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>1246.3</v>
+        <v>846.3</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>122.2</v>
+        <v>63.3</v>
       </c>
       <c r="S45" s="3" t="n">
         <v>13.8</v>
@@ -4261,19 +4262,19 @@
         <v>66.8</v>
       </c>
       <c r="V45" s="3" t="n">
-        <v>222</v>
+        <v>34</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>1412.4</v>
+        <v>112.8</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>122.5</v>
+        <v>12.2</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>3983.1</v>
+        <v>9929.5</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>10820.9</v>
+        <v>80.5</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4291,20 +4292,20 @@
       <c r="C46" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D46" s="11" t="n">
+      <c r="D46" s="9" t="n">
         <v>30.5</v>
       </c>
-      <c r="E46" s="11" t="n">
+      <c r="E46" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="F46" s="11" t="n">
+      <c r="F46" s="9" t="n">
         <v>25.5</v>
       </c>
-      <c r="G46" s="11" t="n">
-        <v>10.1</v>
+      <c r="G46" s="8" t="n">
+        <v>9.1</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>18.7</v>
+        <v>88.7</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>11.7</v>
@@ -4313,13 +4314,13 @@
         <v>3</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>1.5</v>
+        <v>0.1</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>20.8</v>
       </c>
       <c r="M46" s="3" t="n">
-        <v>20</v>
+        <v>20.5</v>
       </c>
       <c r="N46" s="3" t="n">
         <v>24.1</v>
@@ -4330,35 +4331,35 @@
       <c r="P46" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q46" s="3" t="n">
-        <v>29.9</v>
+      <c r="Q46" s="8" t="n">
+        <v>95.3</v>
       </c>
       <c r="R46" s="3" t="n">
         <v>24.5</v>
       </c>
-      <c r="S46" s="8" t="n">
-        <v>71.7</v>
+      <c r="S46" s="3" t="n">
+        <v>27.8</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>68.3</v>
       </c>
-      <c r="U46" s="8" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="V46" s="8" t="n">
+      <c r="U46" s="3" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="V46" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="W46" s="8" t="n">
-        <v>73.8</v>
+      <c r="W46" s="3" t="n">
+        <v>23.8</v>
       </c>
       <c r="X46" s="3" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>128.5</v>
+        <v>28.5</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>18.7</v>
+        <v>7.7</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -26,7 +26,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC0CB"/>
+        <bgColor rgb="00FFC0CB"/>
       </patternFill>
     </fill>
   </fills>
@@ -146,9 +152,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -158,13 +161,16 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -807,13 +813,13 @@
       <c r="J4" s="3" t="n">
         <v>14.4</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="9" t="n">
         <v>22.7</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -825,13 +831,13 @@
       <c r="P4" s="3" t="n">
         <v>6.1</v>
       </c>
-      <c r="Q4" s="8" t="n">
+      <c r="Q4" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="R4" s="3" t="n">
+      <c r="R4" s="9" t="n">
         <v>25.6</v>
       </c>
-      <c r="S4" s="8" t="n">
+      <c r="S4" s="11" t="n">
         <v>28.1</v>
       </c>
       <c r="T4" s="3" t="n">
@@ -840,13 +846,13 @@
       <c r="U4" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" s="9" t="n">
         <v>28.6</v>
       </c>
-      <c r="W4" s="3" t="n">
+      <c r="W4" s="9" t="n">
         <v>24.9</v>
       </c>
-      <c r="X4" s="8" t="n">
+      <c r="X4" s="11" t="n">
         <v>92.09999999999999</v>
       </c>
       <c r="Y4" s="3" t="n">
@@ -890,13 +896,13 @@
       <c r="J5" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="9" t="n">
         <v>1.9</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M5" s="8" t="n">
+      <c r="M5" s="9" t="n">
         <v>22.4</v>
       </c>
       <c r="N5" s="3" t="n">
@@ -908,10 +914,10 @@
       <c r="P5" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q5" s="3" t="n">
+      <c r="Q5" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="R5" s="3" t="n">
+      <c r="R5" s="9" t="n">
         <v>23</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -923,10 +929,10 @@
       <c r="U5" s="3" t="n">
         <v>8.4</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" s="9" t="n">
         <v>22</v>
       </c>
-      <c r="W5" s="3" t="n">
+      <c r="W5" s="9" t="n">
         <v>21.1</v>
       </c>
       <c r="X5" s="3" t="n">
@@ -975,13 +981,13 @@
       <c r="J6" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="3" t="n">
+      <c r="L6" s="9" t="n">
         <v>21.6</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="9" t="n">
         <v>21.3</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -993,10 +999,10 @@
       <c r="P6" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q6" s="3" t="n">
+      <c r="Q6" s="9" t="n">
         <v>31.4</v>
       </c>
-      <c r="R6" s="3" t="n">
+      <c r="R6" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -1008,10 +1014,10 @@
       <c r="U6" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="V6" s="3" t="n">
+      <c r="V6" s="9" t="n">
         <v>28.3</v>
       </c>
-      <c r="W6" s="3" t="n">
+      <c r="W6" s="9" t="n">
         <v>24.8</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1060,13 +1066,13 @@
       <c r="J7" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="L7" s="3" t="n">
+      <c r="L7" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="9" t="n">
         <v>20.9</v>
       </c>
       <c r="N7" s="3" t="n">
@@ -1078,10 +1084,10 @@
       <c r="P7" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q7" s="8" t="n">
+      <c r="Q7" s="9" t="n">
         <v>31.9</v>
       </c>
-      <c r="R7" s="3" t="n">
+      <c r="R7" s="9" t="n">
         <v>25.3</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1093,13 +1099,13 @@
       <c r="U7" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" s="9" t="n">
         <v>28.7</v>
       </c>
-      <c r="W7" s="3" t="n">
+      <c r="W7" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="X7" s="8" t="n">
+      <c r="X7" s="11" t="n">
         <v>28.8</v>
       </c>
       <c r="Y7" s="3" t="n">
@@ -1145,13 +1151,13 @@
       <c r="J8" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="9" t="n">
         <v>22.1</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="9" t="n">
         <v>21.7</v>
       </c>
       <c r="N8" s="3" t="n">
@@ -1163,10 +1169,10 @@
       <c r="P8" s="3" t="n">
         <v>10.9</v>
       </c>
-      <c r="Q8" s="3" t="n">
+      <c r="Q8" s="9" t="n">
         <v>33.3</v>
       </c>
-      <c r="R8" s="3" t="n">
+      <c r="R8" s="9" t="n">
         <v>25.6</v>
       </c>
       <c r="S8" s="3" t="n">
@@ -1178,13 +1184,13 @@
       <c r="U8" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="V8" s="9" t="n">
         <v>28.1</v>
       </c>
-      <c r="W8" s="3" t="n">
+      <c r="W8" s="9" t="n">
         <v>24.4</v>
       </c>
-      <c r="X8" s="8" t="n">
+      <c r="X8" s="11" t="n">
         <v>28.2</v>
       </c>
       <c r="Y8" s="3" t="n">
@@ -1230,13 +1236,13 @@
       <c r="J9" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="9" t="n">
         <v>109.4</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="15" t="n">
         <v>108</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1248,10 +1254,10 @@
       <c r="P9" s="3" t="n">
         <v>13.1</v>
       </c>
-      <c r="Q9" s="3" t="n">
+      <c r="Q9" s="15" t="n">
         <v>8556.6</v>
       </c>
-      <c r="R9" s="3" t="n">
+      <c r="R9" s="9" t="n">
         <v>124.4</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1263,10 +1269,10 @@
       <c r="U9" s="3" t="n">
         <v>90.09999999999999</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" s="15" t="n">
         <v>32.7</v>
       </c>
-      <c r="W9" s="3" t="n">
+      <c r="W9" s="9" t="n">
         <v>120</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1318,10 +1324,10 @@
       <c r="K10" s="3" t="n">
         <v>1.7</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="15" t="n">
         <v>22.9</v>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1333,10 +1339,10 @@
       <c r="P10" s="3" t="n">
         <v>0.6</v>
       </c>
-      <c r="Q10" s="3" t="n">
+      <c r="Q10" s="9" t="n">
         <v>31.1</v>
       </c>
-      <c r="R10" s="3" t="n">
+      <c r="R10" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1345,13 +1351,13 @@
       <c r="T10" s="3" t="n">
         <v>61.6</v>
       </c>
-      <c r="U10" s="8" t="n">
+      <c r="U10" s="11" t="n">
         <v>18</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="W10" s="3" t="n">
+      <c r="W10" s="9" t="n">
         <v>24</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1391,7 +1397,7 @@
       <c r="G11" s="3" t="n">
         <v>13.8</v>
       </c>
-      <c r="H11" s="8" t="n">
+      <c r="H11" s="11" t="n">
         <v>18.7</v>
       </c>
       <c r="I11" s="3" t="n">
@@ -1400,13 +1406,13 @@
       <c r="J11" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="K11" s="8" t="n">
+      <c r="K11" s="11" t="n">
         <v>0.4</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="9" t="n">
         <v>20.5</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1418,10 +1424,10 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="3" t="n">
+      <c r="Q11" s="9" t="n">
         <v>33.2</v>
       </c>
-      <c r="R11" s="3" t="n">
+      <c r="R11" s="9" t="n">
         <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
@@ -1433,10 +1439,10 @@
       <c r="U11" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="V11" s="9" t="n">
         <v>29.5</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="9" t="n">
         <v>25.1</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1488,10 +1494,10 @@
       <c r="K12" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="L12" s="9" t="n">
         <v>20.4</v>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="9" t="n">
         <v>20.1</v>
       </c>
       <c r="N12" s="3" t="n">
@@ -1503,10 +1509,10 @@
       <c r="P12" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q12" s="3" t="n">
+      <c r="Q12" s="9" t="n">
         <v>32.8</v>
       </c>
-      <c r="R12" s="3" t="n">
+      <c r="R12" s="9" t="n">
         <v>25.8</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1518,10 +1524,10 @@
       <c r="U12" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="V12" s="9" t="n">
         <v>29.6</v>
       </c>
-      <c r="W12" s="3" t="n">
+      <c r="W12" s="9" t="n">
         <v>25.6</v>
       </c>
       <c r="X12" s="3" t="n">
@@ -1573,10 +1579,10 @@
       <c r="K13" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="9" t="n">
         <v>21.3</v>
       </c>
-      <c r="M13" s="3" t="n">
+      <c r="M13" s="9" t="n">
         <v>21</v>
       </c>
       <c r="N13" s="3" t="n">
@@ -1588,10 +1594,10 @@
       <c r="P13" s="3" t="n">
         <v>10.7</v>
       </c>
-      <c r="Q13" s="3" t="n">
+      <c r="Q13" s="9" t="n">
         <v>29.1</v>
       </c>
-      <c r="R13" s="3" t="n">
+      <c r="R13" s="9" t="n">
         <v>24.3</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1603,10 +1609,10 @@
       <c r="U13" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="V13" s="9" t="n">
         <v>26.4</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="9" t="n">
         <v>23.8</v>
       </c>
       <c r="X13" s="3" t="n">
@@ -1646,7 +1652,7 @@
       <c r="G14" s="9" t="n">
         <v>8.1</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="11" t="n">
         <v>87.8</v>
       </c>
       <c r="I14" s="3" t="n">
@@ -1658,10 +1664,10 @@
       <c r="K14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="L14" s="9" t="n">
         <v>21.1</v>
       </c>
-      <c r="M14" s="3" t="n">
+      <c r="M14" s="9" t="n">
         <v>20.9</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1673,10 +1679,10 @@
       <c r="P14" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q14" s="3" t="n">
+      <c r="Q14" s="9" t="n">
         <v>27.3</v>
       </c>
-      <c r="R14" s="3" t="n">
+      <c r="R14" s="9" t="n">
         <v>24.2</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1688,10 +1694,10 @@
       <c r="U14" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="V14" s="9" t="n">
         <v>26</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="9" t="n">
         <v>24</v>
       </c>
       <c r="X14" s="3" t="n">
@@ -1743,10 +1749,10 @@
       <c r="K15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="3" t="n">
+      <c r="L15" s="9" t="n">
         <v>19.5</v>
       </c>
-      <c r="M15" s="3" t="n">
+      <c r="M15" s="9" t="n">
         <v>19.4</v>
       </c>
       <c r="N15" s="3" t="n">
@@ -1758,10 +1764,10 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="8" t="n">
+      <c r="Q15" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="R15" s="3" t="n">
+      <c r="R15" s="9" t="n">
         <v>25.6</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1773,10 +1779,10 @@
       <c r="U15" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="V15" s="8" t="n">
+      <c r="V15" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="W15" s="3" t="n">
+      <c r="W15" s="9" t="n">
         <v>21.9</v>
       </c>
       <c r="X15" s="3" t="n">
@@ -1825,13 +1831,13 @@
       <c r="J16" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="15" t="n">
         <v>16.4</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="15" t="n">
         <v>2.9</v>
       </c>
-      <c r="M16" s="3" t="n">
+      <c r="M16" s="15" t="n">
         <v>10.1</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1843,10 +1849,10 @@
       <c r="P16" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q16" s="3" t="n">
+      <c r="Q16" s="9" t="n">
         <v>152.4</v>
       </c>
-      <c r="R16" s="3" t="n">
+      <c r="R16" s="15" t="n">
         <v>25.7</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1858,10 +1864,10 @@
       <c r="U16" s="3" t="n">
         <v>7.6</v>
       </c>
-      <c r="V16" s="3" t="n">
+      <c r="V16" s="15" t="n">
         <v>12.6</v>
       </c>
-      <c r="W16" s="3" t="n">
+      <c r="W16" s="15" t="n">
         <v>212</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1913,10 +1919,10 @@
       <c r="K17" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="L17" s="3" t="n">
+      <c r="L17" s="9" t="n">
         <v>20.6</v>
       </c>
-      <c r="M17" s="3" t="n">
+      <c r="M17" s="9" t="n">
         <v>20.4</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1928,10 +1934,10 @@
       <c r="P17" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q17" s="3" t="n">
+      <c r="Q17" s="9" t="n">
         <v>30.5</v>
       </c>
-      <c r="R17" s="3" t="n">
+      <c r="R17" s="9" t="n">
         <v>25.1</v>
       </c>
       <c r="S17" s="3" t="n">
@@ -1943,10 +1949,10 @@
       <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="V17" s="3" t="n">
+      <c r="V17" s="9" t="n">
         <v>27.3</v>
       </c>
-      <c r="W17" s="3" t="n">
+      <c r="W17" s="9" t="n">
         <v>24.1</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1995,10 +2001,10 @@
       <c r="J18" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="8" t="n">
+      <c r="L18" s="11" t="n">
         <v>19.7</v>
       </c>
       <c r="M18" s="3" t="n">
@@ -2016,7 +2022,7 @@
       <c r="Q18" s="3" t="n">
         <v>32.2</v>
       </c>
-      <c r="R18" s="3" t="n">
+      <c r="R18" s="9" t="n">
         <v>25.3</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -2028,10 +2034,10 @@
       <c r="U18" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="V18" s="3" t="n">
+      <c r="V18" s="9" t="n">
         <v>28.3</v>
       </c>
-      <c r="W18" s="3" t="n">
+      <c r="W18" s="9" t="n">
         <v>25.1</v>
       </c>
       <c r="X18" s="3" t="n">
@@ -2080,7 +2086,7 @@
       <c r="J19" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="9" t="n">
         <v>4.2</v>
       </c>
       <c r="L19" s="3" t="n">
@@ -2101,7 +2107,7 @@
       <c r="Q19" s="3" t="n">
         <v>31.7</v>
       </c>
-      <c r="R19" s="3" t="n">
+      <c r="R19" s="9" t="n">
         <v>25.3</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2113,10 +2119,10 @@
       <c r="U19" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="V19" s="3" t="n">
+      <c r="V19" s="9" t="n">
         <v>25.7</v>
       </c>
-      <c r="W19" s="3" t="n">
+      <c r="W19" s="9" t="n">
         <v>24.2</v>
       </c>
       <c r="X19" s="3" t="n">
@@ -2156,7 +2162,7 @@
       <c r="G20" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="H20" s="8" t="n">
+      <c r="H20" s="11" t="n">
         <v>18.4</v>
       </c>
       <c r="I20" s="3" t="n">
@@ -2165,10 +2171,10 @@
       <c r="J20" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="9" t="n">
         <v>2.2</v>
       </c>
-      <c r="L20" s="8" t="n">
+      <c r="L20" s="11" t="n">
         <v>19.8</v>
       </c>
       <c r="M20" s="3" t="n">
@@ -2186,7 +2192,7 @@
       <c r="Q20" s="3" t="n">
         <v>27.9</v>
       </c>
-      <c r="R20" s="3" t="n">
+      <c r="R20" s="9" t="n">
         <v>23.8</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2198,10 +2204,10 @@
       <c r="U20" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V20" s="3" t="n">
+      <c r="V20" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="W20" s="3" t="n">
+      <c r="W20" s="9" t="n">
         <v>22.8</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2250,13 +2256,13 @@
       <c r="J21" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="8" t="n">
+      <c r="L21" s="11" t="n">
         <v>18.9</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="16" t="n">
         <v>88.90000000000001</v>
       </c>
       <c r="N21" s="3" t="n">
@@ -2271,7 +2277,7 @@
       <c r="Q21" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="R21" s="3" t="n">
+      <c r="R21" s="9" t="n">
         <v>24.4</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2283,10 +2289,10 @@
       <c r="U21" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="V21" s="3" t="n">
+      <c r="V21" s="9" t="n">
         <v>26.3</v>
       </c>
-      <c r="W21" s="3" t="n">
+      <c r="W21" s="9" t="n">
         <v>24.2</v>
       </c>
       <c r="X21" s="3" t="n">
@@ -2326,7 +2332,7 @@
       <c r="G22" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="H22" s="8" t="n">
+      <c r="H22" s="11" t="n">
         <v>17.4</v>
       </c>
       <c r="I22" s="3" t="n">
@@ -2335,10 +2341,10 @@
       <c r="J22" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="9" t="n">
         <v>0.1</v>
       </c>
-      <c r="L22" s="8" t="n">
+      <c r="L22" s="16" t="n">
         <v>89.09999999999999</v>
       </c>
       <c r="M22" s="3" t="n">
@@ -2356,7 +2362,7 @@
       <c r="Q22" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="R22" s="3" t="n">
+      <c r="R22" s="9" t="n">
         <v>25.8</v>
       </c>
       <c r="S22" s="3" t="n">
@@ -2368,10 +2374,10 @@
       <c r="U22" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="V22" s="3" t="n">
+      <c r="V22" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="W22" s="3" t="n">
+      <c r="W22" s="9" t="n">
         <v>22.6</v>
       </c>
       <c r="X22" s="3" t="n">
@@ -2420,13 +2426,13 @@
       <c r="J23" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="9" t="n">
         <v>6.5</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="15" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="M23" s="3" t="n">
+      <c r="M23" s="15" t="n">
         <v>97.8</v>
       </c>
       <c r="N23" s="3" t="n">
@@ -2438,10 +2444,10 @@
       <c r="P23" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q23" s="3" t="n">
+      <c r="Q23" s="15" t="n">
         <v>152.9</v>
       </c>
-      <c r="R23" s="3" t="n">
+      <c r="R23" s="9" t="n">
         <v>124.6</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2453,10 +2459,10 @@
       <c r="U23" s="3" t="n">
         <v>795.1</v>
       </c>
-      <c r="V23" s="3" t="n">
+      <c r="V23" s="15" t="n">
         <v>29.2</v>
       </c>
-      <c r="W23" s="3" t="n">
+      <c r="W23" s="15" t="n">
         <v>118.2</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2506,10 +2512,10 @@
       <c r="K24" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="15" t="n">
         <v>19.7</v>
       </c>
-      <c r="M24" s="3" t="n">
+      <c r="M24" s="15" t="n">
         <v>19.6</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2521,10 +2527,10 @@
       <c r="P24" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q24" s="3" t="n">
+      <c r="Q24" s="15" t="n">
         <v>30.6</v>
       </c>
-      <c r="R24" s="3" t="n">
+      <c r="R24" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="S24" s="3" t="n">
@@ -2536,10 +2542,10 @@
       <c r="U24" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="V24" s="3" t="n">
+      <c r="V24" s="9" t="n">
         <v>25.9</v>
       </c>
-      <c r="W24" s="3" t="n">
+      <c r="W24" s="9" t="n">
         <v>23.8</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2591,11 +2597,11 @@
       <c r="K25" s="3" t="n">
         <v>5.6</v>
       </c>
-      <c r="L25" s="8" t="n">
-        <v>110.4</v>
-      </c>
-      <c r="M25" s="3" t="n">
-        <v>494.4</v>
+      <c r="L25" s="16" t="n">
+        <v>11.04</v>
+      </c>
+      <c r="M25" s="16" t="n">
+        <v>49.44</v>
       </c>
       <c r="N25" s="3" t="n">
         <v>22.9</v>
@@ -2609,7 +2615,7 @@
       <c r="Q25" s="3" t="n">
         <v>22.9</v>
       </c>
-      <c r="R25" s="3" t="n">
+      <c r="R25" s="9" t="n">
         <v>22.1</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2621,10 +2627,10 @@
       <c r="U25" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="V25" s="3" t="n">
+      <c r="V25" s="9" t="n">
         <v>21.5</v>
       </c>
-      <c r="W25" s="8" t="n">
+      <c r="W25" s="11" t="n">
         <v>21</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2664,7 +2670,7 @@
       <c r="G26" s="9" t="n">
         <v>11.2</v>
       </c>
-      <c r="H26" s="8" t="n">
+      <c r="H26" s="11" t="n">
         <v>18.6</v>
       </c>
       <c r="I26" s="3" t="n">
@@ -2689,10 +2695,10 @@
         <v>98</v>
       </c>
       <c r="P26" s="3" t="inlineStr"/>
-      <c r="Q26" s="3" t="n">
+      <c r="Q26" s="16" t="n">
         <v>88.40000000000001</v>
       </c>
-      <c r="R26" s="3" t="n">
+      <c r="R26" s="9" t="n">
         <v>24.1</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2704,7 +2710,7 @@
       <c r="U26" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="V26" s="3" t="n">
+      <c r="V26" s="9" t="n">
         <v>27.2</v>
       </c>
       <c r="W26" s="3" t="n">
@@ -2747,7 +2753,7 @@
       <c r="G27" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="H27" s="8" t="n">
+      <c r="H27" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="I27" s="3" t="n">
@@ -2765,7 +2771,7 @@
       <c r="M27" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N27" s="8" t="n">
+      <c r="N27" s="11" t="n">
         <v>22.6</v>
       </c>
       <c r="O27" s="3" t="n">
@@ -2777,7 +2783,7 @@
       <c r="Q27" s="3" t="n">
         <v>32.9</v>
       </c>
-      <c r="R27" s="3" t="n">
+      <c r="R27" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2789,13 +2795,13 @@
       <c r="U27" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="V27" s="3" t="n">
+      <c r="V27" s="9" t="n">
         <v>29.3</v>
       </c>
-      <c r="W27" s="3" t="n">
-        <v>655.1</v>
-      </c>
-      <c r="X27" s="8" t="n">
+      <c r="W27" s="16" t="n">
+        <v>65.51000000000001</v>
+      </c>
+      <c r="X27" s="11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Y27" s="3" t="n">
@@ -2832,7 +2838,7 @@
       <c r="G28" s="3" t="n">
         <v>12.8</v>
       </c>
-      <c r="H28" s="8" t="n">
+      <c r="H28" s="11" t="n">
         <v>18.4</v>
       </c>
       <c r="I28" s="3" t="n">
@@ -2862,7 +2868,7 @@
       <c r="Q28" s="3" t="n">
         <v>29.7</v>
       </c>
-      <c r="R28" s="3" t="n">
+      <c r="R28" s="9" t="n">
         <v>25.1</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2874,7 +2880,7 @@
       <c r="U28" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="V28" s="3" t="n">
+      <c r="V28" s="9" t="n">
         <v>24.4</v>
       </c>
       <c r="W28" s="3" t="n">
@@ -2926,8 +2932,8 @@
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="8" t="n">
+      <c r="K29" s="13" t="inlineStr"/>
+      <c r="L29" s="11" t="n">
         <v>18.9</v>
       </c>
       <c r="M29" s="3" t="n">
@@ -2945,7 +2951,7 @@
       <c r="Q29" s="3" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="3" t="n">
+      <c r="R29" s="9" t="n">
         <v>24.8</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2954,10 +2960,10 @@
       <c r="T29" s="3" t="n">
         <v>73.7</v>
       </c>
-      <c r="U29" s="8" t="n">
+      <c r="U29" s="11" t="n">
         <v>7.3</v>
       </c>
-      <c r="V29" s="3" t="n">
+      <c r="V29" s="9" t="n">
         <v>25</v>
       </c>
       <c r="W29" s="3" t="n">
@@ -3007,13 +3013,13 @@
       <c r="J30" s="3" t="n">
         <v>11.7</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="15" t="n">
         <v>23.7</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="15" t="n">
         <v>2.2</v>
       </c>
-      <c r="M30" s="3" t="n">
+      <c r="M30" s="15" t="n">
         <v>10.1</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3025,10 +3031,10 @@
       <c r="P30" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q30" s="3" t="n">
+      <c r="Q30" s="15" t="n">
         <v>75.5</v>
       </c>
-      <c r="R30" s="3" t="n">
+      <c r="R30" s="15" t="n">
         <v>122</v>
       </c>
       <c r="S30" s="3" t="n">
@@ -3040,10 +3046,10 @@
       <c r="U30" s="3" t="n">
         <v>68.8</v>
       </c>
-      <c r="V30" s="3" t="n">
+      <c r="V30" s="9" t="n">
         <v>127.4</v>
       </c>
-      <c r="W30" s="3" t="n">
+      <c r="W30" s="15" t="n">
         <v>115.3</v>
       </c>
       <c r="X30" s="3" t="n">
@@ -3091,10 +3097,10 @@
         <v>3.4</v>
       </c>
       <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="n">
+      <c r="L31" s="15" t="n">
         <v>20.4</v>
       </c>
-      <c r="M31" s="3" t="n">
+      <c r="M31" s="15" t="n">
         <v>20.2</v>
       </c>
       <c r="N31" s="3" t="n">
@@ -3106,10 +3112,10 @@
       <c r="P31" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q31" s="3" t="n">
+      <c r="Q31" s="15" t="n">
         <v>29.1</v>
       </c>
-      <c r="R31" s="3" t="n">
+      <c r="R31" s="9" t="n">
         <v>24.2</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3118,16 +3124,16 @@
       <c r="T31" s="3" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="U31" s="8" t="n">
+      <c r="U31" s="11" t="n">
         <v>13.8</v>
       </c>
-      <c r="V31" s="3" t="n">
+      <c r="V31" s="9" t="n">
         <v>25.5</v>
       </c>
-      <c r="W31" s="3" t="n">
+      <c r="W31" s="15" t="n">
         <v>23.1</v>
       </c>
-      <c r="X31" s="8" t="n">
+      <c r="X31" s="11" t="n">
         <v>26.7</v>
       </c>
       <c r="Y31" s="3" t="n">
@@ -3176,7 +3182,7 @@
       <c r="K32" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="L32" s="9" t="n">
         <v>21.6</v>
       </c>
       <c r="M32" s="3" t="n">
@@ -3194,7 +3200,7 @@
       <c r="Q32" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="R32" s="3" t="n">
+      <c r="R32" s="9" t="n">
         <v>24.5</v>
       </c>
       <c r="S32" s="3" t="n">
@@ -3206,7 +3212,7 @@
       <c r="U32" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="V32" s="3" t="n">
+      <c r="V32" s="9" t="n">
         <v>27.1</v>
       </c>
       <c r="W32" s="3" t="n">
@@ -3258,10 +3264,10 @@
       <c r="J33" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="K33" s="8" t="n">
+      <c r="K33" s="11" t="n">
         <v>22.5</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="9" t="n">
         <v>20.8</v>
       </c>
       <c r="M33" s="3" t="n">
@@ -3279,7 +3285,7 @@
       <c r="Q33" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="R33" s="3" t="n">
+      <c r="R33" s="9" t="n">
         <v>22.1</v>
       </c>
       <c r="S33" s="3" t="n">
@@ -3291,7 +3297,7 @@
       <c r="U33" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="V33" s="3" t="n">
+      <c r="V33" s="9" t="n">
         <v>23</v>
       </c>
       <c r="W33" s="3" t="n">
@@ -3334,7 +3340,7 @@
       <c r="G34" s="9" t="n">
         <v>11.5</v>
       </c>
-      <c r="H34" s="8" t="n">
+      <c r="H34" s="11" t="n">
         <v>17.8</v>
       </c>
       <c r="I34" s="3" t="n">
@@ -3346,7 +3352,7 @@
       <c r="K34" s="3" t="n">
         <v>5.9</v>
       </c>
-      <c r="L34" s="3" t="n">
+      <c r="L34" s="9" t="n">
         <v>20.1</v>
       </c>
       <c r="M34" s="3" t="n">
@@ -3364,7 +3370,7 @@
       <c r="Q34" s="3" t="n">
         <v>30.1</v>
       </c>
-      <c r="R34" s="3" t="n">
+      <c r="R34" s="9" t="n">
         <v>25.6</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3376,10 +3382,10 @@
       <c r="U34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V34" s="3" t="n">
+      <c r="V34" s="9" t="n">
         <v>26.3</v>
       </c>
-      <c r="W34" s="8" t="n">
+      <c r="W34" s="11" t="n">
         <v>21</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3419,7 +3425,7 @@
       <c r="G35" s="9" t="n">
         <v>10.7</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="11" t="n">
         <v>17.6</v>
       </c>
       <c r="I35" s="3" t="n">
@@ -3431,13 +3437,13 @@
       <c r="K35" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="9" t="n">
         <v>19</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="N35" s="8" t="n">
+      <c r="N35" s="11" t="n">
         <v>14.9</v>
       </c>
       <c r="O35" s="3" t="n">
@@ -3449,7 +3455,7 @@
       <c r="Q35" s="3" t="n">
         <v>28.3</v>
       </c>
-      <c r="R35" s="3" t="n">
+      <c r="R35" s="9" t="n">
         <v>24.8</v>
       </c>
       <c r="S35" s="3" t="n">
@@ -3461,13 +3467,13 @@
       <c r="U35" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="V35" s="3" t="n">
+      <c r="V35" s="9" t="n">
         <v>26.3</v>
       </c>
       <c r="W35" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="X35" s="8" t="n">
+      <c r="X35" s="11" t="n">
         <v>95.3</v>
       </c>
       <c r="Y35" s="3" t="n">
@@ -3504,7 +3510,7 @@
       <c r="G36" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="H36" s="8" t="n">
+      <c r="H36" s="11" t="n">
         <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
@@ -3516,7 +3522,7 @@
       <c r="K36" s="3" t="n">
         <v>11.3</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="9" t="n">
         <v>21.9</v>
       </c>
       <c r="M36" s="3" t="n">
@@ -3534,7 +3540,7 @@
       <c r="Q36" s="3" t="n">
         <v>21.5</v>
       </c>
-      <c r="R36" s="3" t="n">
+      <c r="R36" s="9" t="n">
         <v>20.9</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3544,10 +3550,10 @@
         <v>94.8</v>
       </c>
       <c r="U36" s="3" t="inlineStr"/>
-      <c r="V36" s="3" t="n">
+      <c r="V36" s="9" t="n">
         <v>21.4</v>
       </c>
-      <c r="W36" s="3" t="n">
+      <c r="W36" s="16" t="n">
         <v>61.8</v>
       </c>
       <c r="X36" s="3" t="n">
@@ -3596,13 +3602,13 @@
       <c r="J37" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="15" t="n">
         <v>1807.9</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="9" t="n">
         <v>103.4</v>
       </c>
-      <c r="M37" s="3" t="n">
+      <c r="M37" s="15" t="n">
         <v>22.9</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3614,10 +3620,10 @@
       <c r="P37" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q37" s="3" t="n">
+      <c r="Q37" s="15" t="n">
         <v>133.8</v>
       </c>
-      <c r="R37" s="3" t="n">
+      <c r="R37" s="15" t="n">
         <v>117.2</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3629,10 +3635,10 @@
       <c r="U37" s="3" t="n">
         <v>40.4</v>
       </c>
-      <c r="V37" s="3" t="n">
+      <c r="V37" s="15" t="n">
         <v>24.1</v>
       </c>
-      <c r="W37" s="3" t="n">
+      <c r="W37" s="15" t="n">
         <v>112.2</v>
       </c>
       <c r="X37" s="3" t="n">
@@ -3684,10 +3690,10 @@
       <c r="K38" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L38" s="3" t="n">
+      <c r="L38" s="9" t="n">
         <v>20.7</v>
       </c>
-      <c r="M38" s="3" t="n">
+      <c r="M38" s="15" t="n">
         <v>20.2</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3699,10 +3705,10 @@
       <c r="P38" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="8" t="n">
+      <c r="Q38" s="15" t="n">
         <v>56.6</v>
       </c>
-      <c r="R38" s="3" t="n">
+      <c r="R38" s="9" t="n">
         <v>23.6</v>
       </c>
       <c r="S38" s="3" t="n">
@@ -3714,10 +3720,10 @@
       <c r="U38" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="V38" s="3" t="n">
+      <c r="V38" s="9" t="n">
         <v>24.8</v>
       </c>
-      <c r="W38" s="3" t="n">
+      <c r="W38" s="15" t="n">
         <v>22.5</v>
       </c>
       <c r="X38" s="3" t="n">
@@ -3769,7 +3775,7 @@
       <c r="K39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L39" s="3" t="n">
+      <c r="L39" s="9" t="n">
         <v>19.5</v>
       </c>
       <c r="M39" s="3" t="n">
@@ -3787,7 +3793,7 @@
       <c r="Q39" s="3" t="n">
         <v>30.7</v>
       </c>
-      <c r="R39" s="3" t="n">
+      <c r="R39" s="9" t="n">
         <v>25.5</v>
       </c>
       <c r="S39" s="3" t="n">
@@ -3799,10 +3805,10 @@
       <c r="U39" s="3" t="n">
         <v>14.7</v>
       </c>
-      <c r="V39" s="3" t="n">
+      <c r="V39" s="9" t="n">
         <v>27.8</v>
       </c>
-      <c r="W39" s="3" t="n">
+      <c r="W39" s="9" t="n">
         <v>23.9</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3854,13 +3860,13 @@
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L40" s="9" t="n">
         <v>21</v>
       </c>
       <c r="M40" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="N40" s="8" t="n">
+      <c r="N40" s="11" t="n">
         <v>42.6</v>
       </c>
       <c r="O40" s="3" t="n">
@@ -3872,7 +3878,7 @@
       <c r="Q40" s="3" t="n">
         <v>30.7</v>
       </c>
-      <c r="R40" s="3" t="n">
+      <c r="R40" s="9" t="n">
         <v>25.3</v>
       </c>
       <c r="S40" s="3" t="n">
@@ -3884,10 +3890,10 @@
       <c r="U40" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="V40" s="3" t="n">
+      <c r="V40" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="W40" s="3" t="n">
+      <c r="W40" s="9" t="n">
         <v>24</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3939,7 +3945,7 @@
       <c r="K41" s="3" t="n">
         <v>11.8</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="9" t="n">
         <v>20.9</v>
       </c>
       <c r="M41" s="3" t="n">
@@ -3957,7 +3963,7 @@
       <c r="Q41" s="3" t="n">
         <v>29.3</v>
       </c>
-      <c r="R41" s="3" t="n">
+      <c r="R41" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="S41" s="3" t="n">
@@ -3969,10 +3975,10 @@
       <c r="U41" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V41" s="3" t="n">
+      <c r="V41" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="W41" s="3" t="n">
+      <c r="W41" s="9" t="n">
         <v>24.5</v>
       </c>
       <c r="X41" s="3" t="n">
@@ -4024,10 +4030,10 @@
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="L42" s="9" t="n">
         <v>21.2</v>
       </c>
-      <c r="M42" s="8" t="n">
+      <c r="M42" s="11" t="n">
         <v>81.2</v>
       </c>
       <c r="N42" s="3" t="n">
@@ -4042,7 +4048,7 @@
       <c r="Q42" s="3" t="n">
         <v>30.9</v>
       </c>
-      <c r="R42" s="3" t="n">
+      <c r="R42" s="9" t="n">
         <v>24.9</v>
       </c>
       <c r="S42" s="3" t="n">
@@ -4054,10 +4060,10 @@
       <c r="U42" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V42" s="3" t="n">
+      <c r="V42" s="9" t="n">
         <v>27.1</v>
       </c>
-      <c r="W42" s="3" t="n">
+      <c r="W42" s="9" t="n">
         <v>24.6</v>
       </c>
       <c r="X42" s="3" t="n">
@@ -4109,7 +4115,7 @@
       <c r="K43" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="L43" s="9" t="n">
         <v>21.2</v>
       </c>
       <c r="M43" s="3" t="n">
@@ -4127,7 +4133,7 @@
       <c r="Q43" s="3" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="3" t="n">
+      <c r="R43" s="9" t="n">
         <v>21.7</v>
       </c>
       <c r="S43" s="3" t="n">
@@ -4139,10 +4145,10 @@
       <c r="U43" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="V43" s="3" t="n">
+      <c r="V43" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="W43" s="3" t="n">
+      <c r="W43" s="9" t="n">
         <v>22</v>
       </c>
       <c r="X43" s="3" t="n">
@@ -4172,24 +4178,24 @@
       </c>
       <c r="D44" s="9" t="inlineStr"/>
       <c r="E44" s="9" t="inlineStr"/>
-      <c r="F44" s="14" t="inlineStr"/>
+      <c r="F44" s="13" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="3" t="inlineStr"/>
-      <c r="L44" s="3" t="inlineStr"/>
+      <c r="K44" s="13" t="inlineStr"/>
+      <c r="L44" s="9" t="inlineStr"/>
       <c r="M44" s="3" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="3" t="inlineStr"/>
-      <c r="R44" s="3" t="inlineStr"/>
+      <c r="Q44" s="13" t="inlineStr"/>
+      <c r="R44" s="9" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="inlineStr"/>
-      <c r="W44" s="3" t="inlineStr"/>
+      <c r="V44" s="9" t="inlineStr"/>
+      <c r="W44" s="9" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4230,13 +4236,13 @@
       <c r="J45" s="3" t="n">
         <v>1814.9</v>
       </c>
-      <c r="K45" s="3" t="n">
+      <c r="K45" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="15" t="n">
         <v>105081.6</v>
       </c>
-      <c r="M45" s="3" t="inlineStr"/>
+      <c r="M45" s="14" t="inlineStr"/>
       <c r="N45" s="3" t="n">
         <v>1820.5</v>
       </c>
@@ -4246,10 +4252,10 @@
       <c r="P45" s="3" t="n">
         <v>16.9</v>
       </c>
-      <c r="Q45" s="3" t="n">
+      <c r="Q45" s="15" t="n">
         <v>846.3</v>
       </c>
-      <c r="R45" s="3" t="n">
+      <c r="R45" s="15" t="n">
         <v>63.3</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4261,10 +4267,10 @@
       <c r="U45" s="3" t="n">
         <v>66.8</v>
       </c>
-      <c r="V45" s="3" t="n">
+      <c r="V45" s="15" t="n">
         <v>34</v>
       </c>
-      <c r="W45" s="3" t="n">
+      <c r="W45" s="15" t="n">
         <v>112.8</v>
       </c>
       <c r="X45" s="3" t="n">
@@ -4301,10 +4307,10 @@
       <c r="F46" s="9" t="n">
         <v>25.5</v>
       </c>
-      <c r="G46" s="8" t="n">
+      <c r="G46" s="11" t="n">
         <v>9.1</v>
       </c>
-      <c r="H46" s="8" t="n">
+      <c r="H46" s="11" t="n">
         <v>88.7</v>
       </c>
       <c r="I46" s="3" t="n">
@@ -4316,7 +4322,7 @@
       <c r="K46" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L46" s="3" t="n">
+      <c r="L46" s="9" t="n">
         <v>20.8</v>
       </c>
       <c r="M46" s="3" t="n">
@@ -4331,10 +4337,10 @@
       <c r="P46" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q46" s="8" t="n">
+      <c r="Q46" s="15" t="n">
         <v>95.3</v>
       </c>
-      <c r="R46" s="3" t="n">
+      <c r="R46" s="9" t="n">
         <v>24.5</v>
       </c>
       <c r="S46" s="3" t="n">
@@ -4346,10 +4352,10 @@
       <c r="U46" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="V46" s="3" t="n">
+      <c r="V46" s="9" t="n">
         <v>26.8</v>
       </c>
-      <c r="W46" s="3" t="n">
+      <c r="W46" s="9" t="n">
         <v>23.8</v>
       </c>
       <c r="X46" s="3" t="n">

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -47,14 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -149,31 +143,25 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -789,16 +777,16 @@
       <c r="C4" s="3" t="n">
         <v>351.3</v>
       </c>
-      <c r="D4" s="9" t="n">
+      <c r="D4" s="8" t="n">
         <v>33.5</v>
       </c>
-      <c r="E4" s="9" t="n">
+      <c r="E4" s="8" t="n">
         <v>22.7</v>
       </c>
-      <c r="F4" s="9" t="n">
+      <c r="F4" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="G4" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="H4" s="3" t="n">
@@ -810,13 +798,13 @@
       <c r="J4" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="9" t="n">
+      <c r="L4" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="8" t="n">
         <v>22.7</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -828,10 +816,10 @@
       <c r="P4" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q4" s="9" t="n">
+      <c r="Q4" s="8" t="n">
         <v>33</v>
       </c>
-      <c r="R4" s="9" t="n">
+      <c r="R4" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="S4" s="3" t="n">
@@ -843,10 +831,10 @@
       <c r="U4" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="V4" s="9" t="n">
+      <c r="V4" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="W4" s="9" t="n">
+      <c r="W4" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="X4" s="3" t="n">
@@ -874,16 +862,16 @@
       <c r="C5" s="3" t="n">
         <v>278.1</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="H5" s="3" t="n">
@@ -895,14 +883,14 @@
       <c r="J5" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="8" t="n">
         <v>1.9</v>
       </c>
-      <c r="L5" s="9" t="n">
+      <c r="L5" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M5" s="3" t="n">
-        <v>20.4</v>
+      <c r="M5" s="8" t="n">
+        <v>21.4</v>
       </c>
       <c r="N5" s="3" t="n">
         <v>25.4</v>
@@ -913,10 +901,10 @@
       <c r="P5" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q5" s="9" t="n">
+      <c r="Q5" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="R5" s="9" t="n">
+      <c r="R5" s="8" t="n">
         <v>23</v>
       </c>
       <c r="S5" s="3" t="n">
@@ -926,19 +914,19 @@
         <v>78</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="V5" s="9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="V5" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="W5" s="9" t="n">
+      <c r="W5" s="8" t="n">
         <v>21.1</v>
       </c>
       <c r="X5" s="3" t="n">
         <v>24.4</v>
       </c>
       <c r="Y5" s="3" t="n">
-        <v>192</v>
+        <v>92</v>
       </c>
       <c r="Z5" s="3" t="n">
         <v>10</v>
@@ -957,18 +945,18 @@
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2368</v>
-      </c>
-      <c r="D6" s="9" t="n">
+        <v>368</v>
+      </c>
+      <c r="D6" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="E6" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="H6" s="3" t="n">
@@ -980,13 +968,13 @@
       <c r="J6" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="8" t="n">
         <v>21.3</v>
       </c>
       <c r="N6" s="3" t="n">
@@ -998,10 +986,10 @@
       <c r="P6" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q6" s="9" t="n">
+      <c r="Q6" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="R6" s="9" t="n">
+      <c r="R6" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S6" s="3" t="n">
@@ -1013,10 +1001,10 @@
       <c r="U6" s="3" t="n">
         <v>18.6</v>
       </c>
-      <c r="V6" s="9" t="n">
+      <c r="V6" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="W6" s="9" t="n">
+      <c r="W6" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="X6" s="3" t="n">
@@ -1042,18 +1030,18 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>418.2</v>
-      </c>
-      <c r="D7" s="9" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D7" s="8" t="n">
         <v>32.4</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="8" t="n">
         <v>26.7</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="H7" s="3" t="n">
@@ -1065,16 +1053,16 @@
       <c r="J7" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K7" s="3" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="L7" s="9" t="n">
+      <c r="K7" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L7" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="N7" s="8" t="n">
+      <c r="N7" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="O7" s="3" t="n">
@@ -1083,10 +1071,10 @@
       <c r="P7" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q7" s="9" t="n">
+      <c r="Q7" s="8" t="n">
         <v>31.9</v>
       </c>
-      <c r="R7" s="9" t="n">
+      <c r="R7" s="8" t="n">
         <v>25.3</v>
       </c>
       <c r="S7" s="3" t="n">
@@ -1098,10 +1086,10 @@
       <c r="U7" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="V7" s="9" t="n">
+      <c r="V7" s="8" t="n">
         <v>28.7</v>
       </c>
-      <c r="W7" s="9" t="n">
+      <c r="W7" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="X7" s="3" t="n">
@@ -1127,18 +1115,18 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>2368</v>
-      </c>
-      <c r="D8" s="9" t="n">
+        <v>368</v>
+      </c>
+      <c r="D8" s="8" t="n">
         <v>33.3</v>
       </c>
-      <c r="E8" s="9" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="F8" s="9" t="n">
+      <c r="E8" s="8" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="F8" s="8" t="n">
         <v>27.5</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="8" t="n">
         <v>11.5</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1150,43 +1138,43 @@
       <c r="J8" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="9" t="n">
+      <c r="L8" s="8" t="n">
         <v>22.1</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="8" t="n">
         <v>21.7</v>
       </c>
       <c r="N8" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>196.5</v>
+        <v>96.5</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q8" s="9" t="n">
+      <c r="Q8" s="8" t="n">
         <v>33.3</v>
       </c>
-      <c r="R8" s="9" t="n">
+      <c r="R8" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="S8" s="8" t="n">
+      <c r="S8" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>54.8</v>
       </c>
-      <c r="U8" s="8" t="n">
+      <c r="U8" s="3" t="n">
         <v>23</v>
       </c>
-      <c r="V8" s="9" t="n">
+      <c r="V8" s="8" t="n">
         <v>28.1</v>
       </c>
-      <c r="W8" s="9" t="n">
+      <c r="W8" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="X8" s="3" t="n">
@@ -1196,7 +1184,7 @@
         <v>74.2</v>
       </c>
       <c r="Z8" s="3" t="n">
-        <v>19.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA8" s="3" t="inlineStr">
         <is>
@@ -1214,16 +1202,16 @@
       <c r="C9" s="3" t="n">
         <v>1783.6</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="8" t="n">
         <v>161.7</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="8" t="n">
         <v>107.4</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="8" t="n">
         <v>134.5</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="8" t="n">
         <v>54.3</v>
       </c>
       <c r="H9" s="3" t="n">
@@ -1235,13 +1223,13 @@
       <c r="J9" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K9" s="16" t="n">
+      <c r="K9" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" s="8" t="n">
         <v>109.4</v>
       </c>
-      <c r="M9" s="16" t="n">
+      <c r="M9" s="8" t="n">
         <v>108</v>
       </c>
       <c r="N9" s="3" t="n">
@@ -1253,10 +1241,10 @@
       <c r="P9" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q9" s="16" t="n">
-        <v>255.6</v>
-      </c>
-      <c r="R9" s="9" t="n">
+      <c r="Q9" s="8" t="n">
+        <v>155.6</v>
+      </c>
+      <c r="R9" s="8" t="n">
         <v>124.4</v>
       </c>
       <c r="S9" s="3" t="n">
@@ -1268,10 +1256,10 @@
       <c r="U9" s="3" t="n">
         <v>90.09999999999999</v>
       </c>
-      <c r="V9" s="9" t="n">
+      <c r="V9" s="8" t="n">
         <v>135.7</v>
       </c>
-      <c r="W9" s="9" t="n">
+      <c r="W9" s="8" t="n">
         <v>120</v>
       </c>
       <c r="X9" s="3" t="n">
@@ -1281,7 +1269,7 @@
         <v>389.1</v>
       </c>
       <c r="Z9" s="3" t="n">
-        <v>141.8</v>
+        <v>41.8</v>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1299,20 +1287,20 @@
       <c r="C10" s="3" t="n">
         <v>356.7</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="8" t="n">
         <v>32.3</v>
       </c>
-      <c r="E10" s="9" t="n">
+      <c r="E10" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="8" t="n">
         <v>26.9</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>20.4</v>
+        <v>20</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>2.4</v>
@@ -1323,10 +1311,10 @@
       <c r="K10" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L10" s="9" t="n">
+      <c r="L10" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="M10" s="16" t="n">
+      <c r="M10" s="8" t="n">
         <v>21.6</v>
       </c>
       <c r="N10" s="3" t="n">
@@ -1336,12 +1324,12 @@
         <v>97.40000000000001</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="Q10" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q10" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="R10" s="9" t="n">
+      <c r="R10" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1353,10 +1341,10 @@
       <c r="U10" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="V10" s="9" t="n">
+      <c r="V10" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W10" s="9" t="n">
+      <c r="W10" s="8" t="n">
         <v>24</v>
       </c>
       <c r="X10" s="3" t="n">
@@ -1384,34 +1372,34 @@
       <c r="C11" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="8" t="n">
         <v>33.3</v>
       </c>
-      <c r="E11" s="9" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F11" s="9" t="n">
+      <c r="E11" s="8" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="F11" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="8" t="n">
         <v>13.4</v>
       </c>
-      <c r="H11" s="8" t="n">
-        <v>88.7</v>
+      <c r="H11" s="3" t="n">
+        <v>18.7</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>14.1</v>
+        <v>4.1</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K11" s="9" t="n">
+      <c r="K11" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="9" t="n">
+      <c r="L11" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="M11" s="9" t="n">
+      <c r="M11" s="8" t="n">
         <v>20.5</v>
       </c>
       <c r="N11" s="3" t="n">
@@ -1423,10 +1411,10 @@
       <c r="P11" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q11" s="9" t="n">
+      <c r="Q11" s="8" t="n">
         <v>33.2</v>
       </c>
-      <c r="R11" s="9" t="n">
+      <c r="R11" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
@@ -1438,10 +1426,10 @@
       <c r="U11" s="3" t="n">
         <v>22.1</v>
       </c>
-      <c r="V11" s="9" t="n">
+      <c r="V11" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="W11" s="3" t="n">
+      <c r="W11" s="8" t="n">
         <v>25.1</v>
       </c>
       <c r="X11" s="3" t="n">
@@ -1467,39 +1455,39 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2418.2</v>
-      </c>
-      <c r="D12" s="9" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D12" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="E12" s="9" t="n">
+      <c r="E12" s="8" t="n">
         <v>20.2</v>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="8" t="n">
         <v>26.5</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="8" t="n">
         <v>12.6</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K12" s="9" t="n">
+      <c r="K12" s="8" t="n">
         <v>4.8</v>
       </c>
-      <c r="L12" s="9" t="n">
+      <c r="L12" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="M12" s="9" t="n">
+      <c r="M12" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="N12" s="8" t="n">
+      <c r="N12" s="3" t="n">
         <v>23.3</v>
       </c>
       <c r="O12" s="3" t="n">
@@ -1508,10 +1496,10 @@
       <c r="P12" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q12" s="9" t="n">
+      <c r="Q12" s="8" t="n">
         <v>32.8</v>
       </c>
-      <c r="R12" s="9" t="n">
+      <c r="R12" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="S12" s="3" t="n">
@@ -1520,20 +1508,20 @@
       <c r="T12" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="U12" s="8" t="n">
+      <c r="U12" s="3" t="n">
         <v>20.8</v>
       </c>
-      <c r="V12" s="9" t="n">
+      <c r="V12" s="8" t="n">
         <v>29.6</v>
       </c>
-      <c r="W12" s="3" t="n">
+      <c r="W12" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="X12" s="8" t="n">
+      <c r="X12" s="3" t="n">
         <v>30.3</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>173.2</v>
+        <v>73.2</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>11.1</v>
@@ -1554,37 +1542,37 @@
       <c r="C13" s="3" t="n">
         <v>230.1</v>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="8" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>19.6</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>11.2</v>
+        <v>1.2</v>
       </c>
       <c r="J13" s="3" t="n">
         <v>2.1</v>
       </c>
-      <c r="K13" s="9" t="n">
+      <c r="K13" s="8" t="n">
         <v>11.6</v>
       </c>
-      <c r="L13" s="9" t="n">
+      <c r="L13" s="8" t="n">
         <v>21.3</v>
       </c>
-      <c r="M13" s="9" t="n">
+      <c r="M13" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="N13" s="8" t="n">
+      <c r="N13" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="O13" s="3" t="n">
@@ -1593,10 +1581,10 @@
       <c r="P13" s="3" t="n">
         <v>0.7</v>
       </c>
-      <c r="Q13" s="9" t="n">
+      <c r="Q13" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="R13" s="9" t="n">
+      <c r="R13" s="8" t="n">
         <v>24.3</v>
       </c>
       <c r="S13" s="3" t="n">
@@ -1608,10 +1596,10 @@
       <c r="U13" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="V13" s="9" t="n">
+      <c r="V13" s="8" t="n">
         <v>26.4</v>
       </c>
-      <c r="W13" s="3" t="n">
+      <c r="W13" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X13" s="3" t="n">
@@ -1621,7 +1609,7 @@
         <v>80.8</v>
       </c>
       <c r="Z13" s="3" t="n">
-        <v>16.6</v>
+        <v>6.6</v>
       </c>
       <c r="AA13" s="3" t="inlineStr">
         <is>
@@ -1639,37 +1627,37 @@
       <c r="C14" s="3" t="n">
         <v>121.4</v>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="D14" s="8" t="n">
         <v>27.6</v>
       </c>
-      <c r="E14" s="9" t="n">
+      <c r="E14" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="8" t="n">
         <v>23.5</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="8" t="n">
         <v>8.1</v>
       </c>
-      <c r="H14" s="8" t="n">
+      <c r="H14" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>0.8</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="K14" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K14" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L14" s="9" t="n">
+      <c r="L14" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="M14" s="9" t="n">
+      <c r="M14" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="N14" s="8" t="n">
+      <c r="N14" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="O14" s="3" t="n">
@@ -1678,10 +1666,10 @@
       <c r="P14" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q14" s="9" t="n">
+      <c r="Q14" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="R14" s="9" t="n">
+      <c r="R14" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="S14" s="3" t="n">
@@ -1693,20 +1681,20 @@
       <c r="U14" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V14" s="9" t="n">
+      <c r="V14" s="8" t="n">
         <v>26</v>
       </c>
-      <c r="W14" s="3" t="n">
+      <c r="W14" s="8" t="n">
         <v>24</v>
       </c>
       <c r="X14" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="Y14" s="3" t="n">
-        <v>185.1</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="Z14" s="3" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -1722,18 +1710,18 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2340.8</v>
-      </c>
-      <c r="D15" s="9" t="n">
+        <v>340.8</v>
+      </c>
+      <c r="D15" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="E15" s="9" t="n">
+      <c r="E15" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="8" t="n">
         <v>25.3</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="8" t="n">
         <v>12.1</v>
       </c>
       <c r="H15" s="3" t="n">
@@ -1743,18 +1731,18 @@
         <v>2.5</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="K15" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L15" s="9" t="n">
+      <c r="L15" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="M15" s="9" t="n">
+      <c r="M15" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="N15" s="8" t="n">
+      <c r="N15" s="3" t="n">
         <v>22.4</v>
       </c>
       <c r="O15" s="3" t="n">
@@ -1763,10 +1751,10 @@
       <c r="P15" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q15" s="9" t="n">
+      <c r="Q15" s="8" t="n">
         <v>30</v>
       </c>
-      <c r="R15" s="9" t="n">
+      <c r="R15" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="S15" s="3" t="n">
@@ -1778,11 +1766,11 @@
       <c r="U15" s="3" t="n">
         <v>12.3</v>
       </c>
-      <c r="V15" s="9" t="n">
+      <c r="V15" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W15" s="17" t="n">
-        <v>41.9</v>
+      <c r="W15" s="8" t="n">
+        <v>21.9</v>
       </c>
       <c r="X15" s="3" t="n">
         <v>24.3</v>
@@ -1809,20 +1797,20 @@
       <c r="C16" s="3" t="n">
         <v>1530.8</v>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="D16" s="8" t="n">
         <v>154.2</v>
       </c>
-      <c r="E16" s="9" t="n">
-        <v>99.7</v>
-      </c>
-      <c r="F16" s="9" t="n">
-        <v>126.9</v>
-      </c>
-      <c r="G16" s="9" t="n">
+      <c r="E16" s="8" t="n">
+        <v>99.40000000000001</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>126.8</v>
+      </c>
+      <c r="G16" s="3" t="n">
         <v>54.5</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1192.1</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>11.6</v>
@@ -1830,13 +1818,13 @@
       <c r="J16" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="K16" s="9" t="n">
+      <c r="K16" s="8" t="n">
         <v>16.4</v>
       </c>
-      <c r="L16" s="9" t="n">
+      <c r="L16" s="8" t="n">
         <v>102.9</v>
       </c>
-      <c r="M16" s="9" t="n">
+      <c r="M16" s="8" t="n">
         <v>101.9</v>
       </c>
       <c r="N16" s="3" t="n">
@@ -1848,10 +1836,10 @@
       <c r="P16" s="3" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q16" s="9" t="n">
+      <c r="Q16" s="8" t="n">
         <v>152.4</v>
       </c>
-      <c r="R16" s="9" t="n">
+      <c r="R16" s="8" t="n">
         <v>125.7</v>
       </c>
       <c r="S16" s="3" t="n">
@@ -1863,10 +1851,10 @@
       <c r="U16" s="3" t="n">
         <v>76.3</v>
       </c>
-      <c r="V16" s="9" t="n">
+      <c r="V16" s="8" t="n">
         <v>136.5</v>
       </c>
-      <c r="W16" s="16" t="n">
+      <c r="W16" s="8" t="n">
         <v>120.4</v>
       </c>
       <c r="X16" s="3" t="n">
@@ -1876,7 +1864,7 @@
         <v>386.1</v>
       </c>
       <c r="Z16" s="3" t="n">
-        <v>142.3</v>
+        <v>42.3</v>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -1892,18 +1880,18 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>230.6</v>
-      </c>
-      <c r="D17" s="9" t="n">
+        <v>306.2</v>
+      </c>
+      <c r="D17" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="E17" s="9" t="n">
+      <c r="E17" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="8" t="n">
         <v>25.4</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G17" s="8" t="n">
         <v>10.9</v>
       </c>
       <c r="H17" s="3" t="n">
@@ -1916,12 +1904,12 @@
         <v>3.9</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="M17" s="9" t="n">
+      <c r="M17" s="8" t="n">
         <v>20.4</v>
       </c>
       <c r="N17" s="3" t="n">
@@ -1933,25 +1921,25 @@
       <c r="P17" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q17" s="9" t="n">
+      <c r="Q17" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="R17" s="9" t="n">
+      <c r="R17" s="8" t="n">
         <v>25.1</v>
       </c>
       <c r="S17" s="3" t="n">
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>166.2</v>
+        <v>66.2</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>15.3</v>
       </c>
-      <c r="V17" s="9" t="n">
+      <c r="V17" s="8" t="n">
         <v>27.3</v>
       </c>
-      <c r="W17" s="16" t="n">
+      <c r="W17" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="X17" s="3" t="n">
@@ -1977,18 +1965,18 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="D18" s="9" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="D18" s="8" t="n">
         <v>32.2</v>
       </c>
-      <c r="E18" s="9" t="n">
+      <c r="E18" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="G18" s="8" t="n">
         <v>13</v>
       </c>
       <c r="H18" s="3" t="n">
@@ -2000,28 +1988,28 @@
       <c r="J18" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K18" s="9" t="n">
+      <c r="K18" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L18" s="9" t="n">
+      <c r="L18" s="8" t="n">
         <v>19.7</v>
       </c>
       <c r="M18" s="8" t="n">
         <v>19.4</v>
       </c>
-      <c r="N18" s="8" t="n">
+      <c r="N18" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>97</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="Q18" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q18" s="8" t="n">
         <v>32.2</v>
       </c>
-      <c r="R18" s="9" t="n">
+      <c r="R18" s="8" t="n">
         <v>25.3</v>
       </c>
       <c r="S18" s="3" t="n">
@@ -2030,13 +2018,13 @@
       <c r="T18" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="U18" s="8" t="n">
+      <c r="U18" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="V18" s="9" t="n">
+      <c r="V18" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="W18" s="9" t="n">
+      <c r="W18" s="8" t="n">
         <v>25.1</v>
       </c>
       <c r="X18" s="3" t="n">
@@ -2046,7 +2034,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>18.6</v>
+        <v>8.6</v>
       </c>
       <c r="AA18" s="3" t="inlineStr">
         <is>
@@ -2062,18 +2050,18 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>32.6</v>
-      </c>
-      <c r="D19" s="9" t="n">
+        <v>326.2</v>
+      </c>
+      <c r="D19" s="8" t="n">
         <v>32.2</v>
       </c>
-      <c r="E19" s="9" t="n">
+      <c r="E19" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="F19" s="9" t="n">
+      <c r="F19" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="8" t="n">
         <v>11.7</v>
       </c>
       <c r="H19" s="3" t="n">
@@ -2085,16 +2073,16 @@
       <c r="J19" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K19" s="9" t="n">
+      <c r="K19" s="8" t="n">
         <v>4.2</v>
       </c>
-      <c r="L19" s="9" t="n">
+      <c r="L19" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="M19" s="3" t="n">
+      <c r="M19" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="N19" s="8" t="n">
+      <c r="N19" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="O19" s="3" t="n">
@@ -2103,10 +2091,10 @@
       <c r="P19" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q19" s="9" t="n">
+      <c r="Q19" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="R19" s="9" t="n">
+      <c r="R19" s="8" t="n">
         <v>25.3</v>
       </c>
       <c r="S19" s="3" t="n">
@@ -2118,13 +2106,13 @@
       <c r="U19" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="V19" s="9" t="n">
+      <c r="V19" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="W19" s="9" t="n">
+      <c r="W19" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="X19" s="8" t="n">
+      <c r="X19" s="3" t="n">
         <v>29.2</v>
       </c>
       <c r="Y19" s="3" t="n">
@@ -2149,37 +2137,37 @@
       <c r="C20" s="3" t="n">
         <v>299</v>
       </c>
-      <c r="D20" s="9" t="n">
+      <c r="D20" s="8" t="n">
         <v>29.7</v>
       </c>
-      <c r="E20" s="9" t="n">
+      <c r="E20" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="F20" s="9" t="n">
+      <c r="F20" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="H20" s="8" t="n">
-        <v>118.4</v>
+      <c r="H20" s="3" t="n">
+        <v>18.4</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K20" s="9" t="n">
+      <c r="K20" s="8" t="n">
         <v>2.2</v>
       </c>
-      <c r="L20" s="9" t="n">
+      <c r="L20" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="M20" s="17" t="n">
-        <v>11.97</v>
-      </c>
-      <c r="N20" s="8" t="n">
+      <c r="M20" s="8" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="N20" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="O20" s="3" t="n">
@@ -2188,10 +2176,10 @@
       <c r="P20" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q20" s="9" t="n">
+      <c r="Q20" s="8" t="n">
         <v>27.9</v>
       </c>
-      <c r="R20" s="9" t="n">
+      <c r="R20" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="S20" s="3" t="n">
@@ -2203,10 +2191,10 @@
       <c r="U20" s="3" t="n">
         <v>10.6</v>
       </c>
-      <c r="V20" s="9" t="n">
+      <c r="V20" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W20" s="9" t="n">
+      <c r="W20" s="8" t="n">
         <v>22.8</v>
       </c>
       <c r="X20" s="3" t="n">
@@ -2232,21 +2220,21 @@
         </is>
       </c>
       <c r="C21" s="3" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="D21" s="9" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="D21" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="E21" s="9" t="n">
+      <c r="E21" s="8" t="n">
         <v>18</v>
       </c>
-      <c r="F21" s="9" t="n">
+      <c r="F21" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="8" t="n">
         <v>12.1</v>
       </c>
-      <c r="H21" s="8" t="n">
+      <c r="H21" s="3" t="n">
         <v>16.4</v>
       </c>
       <c r="I21" s="3" t="n">
@@ -2255,28 +2243,28 @@
       <c r="J21" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K21" s="9" t="n">
+      <c r="K21" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="9" t="n">
+      <c r="L21" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="M21" s="3" t="n">
+      <c r="M21" s="8" t="n">
         <v>18.9</v>
       </c>
-      <c r="N21" s="8" t="n">
+      <c r="N21" s="3" t="n">
         <v>21.8</v>
       </c>
       <c r="O21" s="3" t="n">
-        <v>1600</v>
+        <v>100</v>
       </c>
       <c r="P21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" s="9" t="n">
+      <c r="Q21" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="R21" s="9" t="n">
+      <c r="R21" s="8" t="n">
         <v>24.4</v>
       </c>
       <c r="S21" s="3" t="n">
@@ -2288,17 +2276,17 @@
       <c r="U21" s="3" t="n">
         <v>15.7</v>
       </c>
-      <c r="V21" s="9" t="n">
+      <c r="V21" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W21" s="9" t="n">
+      <c r="W21" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="X21" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="Y21" s="3" t="n">
-        <v>1844.1</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Z21" s="3" t="n">
         <v>5.4</v>
@@ -2319,37 +2307,37 @@
       <c r="C22" s="3" t="n">
         <v>294.9</v>
       </c>
-      <c r="D22" s="9" t="n">
+      <c r="D22" s="8" t="n">
         <v>31.2</v>
       </c>
-      <c r="E22" s="9" t="n">
+      <c r="E22" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="8" t="n">
         <v>25</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>167.4</v>
+        <v>12.9</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>17.4</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J22" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K22" s="9" t="n">
+      <c r="K22" s="8" t="n">
         <v>0.1</v>
       </c>
-      <c r="L22" s="9" t="n">
+      <c r="L22" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="M22" s="3" t="n">
+      <c r="M22" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="N22" s="8" t="n">
+      <c r="N22" s="3" t="n">
         <v>22.1</v>
       </c>
       <c r="O22" s="3" t="n">
@@ -2358,32 +2346,32 @@
       <c r="P22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" s="9" t="n">
+      <c r="Q22" s="8" t="n">
         <v>31</v>
       </c>
-      <c r="R22" s="9" t="n">
+      <c r="R22" s="8" t="n">
         <v>25.8</v>
       </c>
       <c r="S22" s="3" t="n">
         <v>29.9</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>166.8</v>
+        <v>66.8</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>14.8</v>
       </c>
-      <c r="V22" s="9" t="n">
+      <c r="V22" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="W22" s="9" t="n">
+      <c r="W22" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="X22" s="3" t="n">
         <v>26.5</v>
       </c>
       <c r="Y22" s="3" t="n">
-        <v>188.8</v>
+        <v>88.8</v>
       </c>
       <c r="Z22" s="3" t="n">
         <v>3.3</v>
@@ -2404,16 +2392,16 @@
       <c r="C23" s="3" t="n">
         <v>161</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="8" t="n">
         <v>155.4</v>
       </c>
-      <c r="E23" s="9" t="n">
+      <c r="E23" s="8" t="n">
         <v>96.2</v>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="8" t="n">
         <v>125.8</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="8" t="n">
         <v>59.2</v>
       </c>
       <c r="H23" s="3" t="n">
@@ -2425,28 +2413,28 @@
       <c r="J23" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="K23" s="9" t="n">
+      <c r="K23" s="8" t="n">
         <v>6.5</v>
       </c>
-      <c r="L23" s="9" t="n">
+      <c r="L23" s="8" t="n">
         <v>98.40000000000001</v>
       </c>
-      <c r="M23" s="16" t="n">
+      <c r="M23" s="8" t="n">
         <v>97.8</v>
       </c>
       <c r="N23" s="3" t="n">
         <v>113.3</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>494</v>
+        <v>94</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q23" s="9" t="n">
+      <c r="Q23" s="8" t="n">
         <v>152.9</v>
       </c>
-      <c r="R23" s="9" t="n">
+      <c r="R23" s="8" t="n">
         <v>124.6</v>
       </c>
       <c r="S23" s="3" t="n">
@@ -2458,10 +2446,10 @@
       <c r="U23" s="3" t="n">
         <v>79.59999999999999</v>
       </c>
-      <c r="V23" s="9" t="n">
+      <c r="V23" s="8" t="n">
         <v>129.3</v>
       </c>
-      <c r="W23" s="9" t="n">
+      <c r="W23" s="8" t="n">
         <v>118.9</v>
       </c>
       <c r="X23" s="3" t="n">
@@ -2471,7 +2459,7 @@
         <v>422</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>126.5</v>
+        <v>26.5</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2489,16 +2477,16 @@
       <c r="C24" s="3" t="n">
         <v>322</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="8" t="n">
         <v>31.1</v>
       </c>
-      <c r="E24" s="9" t="n">
+      <c r="E24" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="8" t="n">
         <v>11.9</v>
       </c>
       <c r="H24" s="3" t="n">
@@ -2511,12 +2499,12 @@
         <v>3.7</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="8" t="n">
         <v>19.7</v>
       </c>
-      <c r="M24" s="16" t="n">
+      <c r="M24" s="8" t="n">
         <v>19.6</v>
       </c>
       <c r="N24" s="3" t="n">
@@ -2528,25 +2516,25 @@
       <c r="P24" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="Q24" s="9" t="n">
+      <c r="Q24" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="R24" s="9" t="n">
+      <c r="R24" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S24" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>164</v>
+        <v>64</v>
       </c>
       <c r="U24" s="3" t="n">
         <v>15.9</v>
       </c>
-      <c r="V24" s="16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W24" s="9" t="n">
+      <c r="V24" s="8" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="W24" s="8" t="n">
         <v>23.8</v>
       </c>
       <c r="X24" s="3" t="n">
@@ -2556,7 +2544,7 @@
         <v>84.40000000000001</v>
       </c>
       <c r="Z24" s="3" t="n">
-        <v>5.3</v>
+        <v>25.3</v>
       </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
@@ -2574,34 +2562,34 @@
       <c r="C25" s="3" t="n">
         <v>177.8</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="E25" s="9" t="n">
+      <c r="E25" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>11.4</v>
+        <v>1.4</v>
       </c>
       <c r="J25" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="K25" s="9" t="n">
+      <c r="K25" s="8" t="n">
         <v>5.6</v>
       </c>
-      <c r="L25" s="17" t="n">
+      <c r="L25" s="10" t="n">
         <v>40.6</v>
       </c>
-      <c r="M25" s="3" t="n">
+      <c r="M25" s="8" t="n">
         <v>19.8</v>
       </c>
       <c r="N25" s="3" t="n">
@@ -2613,10 +2601,10 @@
       <c r="P25" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q25" s="9" t="n">
+      <c r="Q25" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="R25" s="9" t="n">
+      <c r="R25" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="S25" s="3" t="n">
@@ -2628,10 +2616,10 @@
       <c r="U25" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="V25" s="9" t="n">
+      <c r="V25" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="W25" s="9" t="n">
+      <c r="W25" s="8" t="n">
         <v>21</v>
       </c>
       <c r="X25" s="3" t="n">
@@ -2657,21 +2645,21 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>2345</v>
-      </c>
-      <c r="D26" s="9" t="n">
+        <v>345</v>
+      </c>
+      <c r="D26" s="8" t="n">
         <v>31.7</v>
       </c>
-      <c r="E26" s="9" t="n">
+      <c r="E26" s="8" t="n">
         <v>20.5</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="8" t="n">
         <v>26.1</v>
       </c>
-      <c r="G26" s="9" t="n">
+      <c r="G26" s="8" t="n">
         <v>11.2</v>
       </c>
-      <c r="H26" s="8" t="n">
+      <c r="H26" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I26" s="3" t="n">
@@ -2680,13 +2668,13 @@
       <c r="J26" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K26" s="9" t="n">
+      <c r="K26" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="M26" s="3" t="n">
+      <c r="M26" s="8" t="n">
         <v>20.4</v>
       </c>
       <c r="N26" s="3" t="n">
@@ -2698,10 +2686,10 @@
       <c r="P26" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q26" s="9" t="n">
+      <c r="Q26" s="8" t="n">
         <v>31.4</v>
       </c>
-      <c r="R26" s="9" t="n">
+      <c r="R26" s="8" t="n">
         <v>24.1</v>
       </c>
       <c r="S26" s="3" t="n">
@@ -2713,10 +2701,10 @@
       <c r="U26" s="3" t="n">
         <v>20.6</v>
       </c>
-      <c r="V26" s="9" t="n">
+      <c r="V26" s="8" t="n">
         <v>27.2</v>
       </c>
-      <c r="W26" s="9" t="n">
+      <c r="W26" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="X26" s="3" t="n">
@@ -2742,36 +2730,36 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>418.2</v>
-      </c>
-      <c r="D27" s="9" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="D27" s="8" t="n">
         <v>32.9</v>
       </c>
-      <c r="E27" s="9" t="n">
+      <c r="E27" s="8" t="n">
         <v>19.2</v>
       </c>
-      <c r="F27" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="G27" s="9" t="n">
+      <c r="F27" s="8" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="G27" s="8" t="n">
         <v>13.7</v>
       </c>
-      <c r="H27" s="8" t="n">
+      <c r="H27" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>13.1</v>
+        <v>3.1</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="K27" s="9" t="n">
+      <c r="K27" s="8" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M27" s="3" t="n">
+      <c r="M27" s="8" t="n">
         <v>19.5</v>
       </c>
       <c r="N27" s="3" t="n">
@@ -2783,10 +2771,10 @@
       <c r="P27" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q27" s="9" t="n">
+      <c r="Q27" s="8" t="n">
         <v>32.9</v>
       </c>
-      <c r="R27" s="9" t="n">
+      <c r="R27" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S27" s="3" t="n">
@@ -2798,14 +2786,14 @@
       <c r="U27" s="3" t="n">
         <v>23.4</v>
       </c>
-      <c r="V27" s="9" t="n">
+      <c r="V27" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="W27" s="9" t="n">
+      <c r="W27" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="X27" s="3" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="Y27" s="3" t="n">
         <v>74.2</v>
@@ -2827,18 +2815,18 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>282.4</v>
-      </c>
-      <c r="D28" s="9" t="n">
+        <v>28.2</v>
+      </c>
+      <c r="D28" s="8" t="n">
         <v>32.6</v>
       </c>
-      <c r="E28" s="9" t="n">
+      <c r="E28" s="8" t="n">
         <v>19.8</v>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="8" t="n">
         <v>26.2</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="8" t="n">
         <v>12.8</v>
       </c>
       <c r="H28" s="3" t="n">
@@ -2850,14 +2838,14 @@
       <c r="J28" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K28" s="9" t="n">
+      <c r="K28" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="L28" s="8" t="n">
+      <c r="L28" s="3" t="n">
         <v>20.1</v>
       </c>
-      <c r="M28" s="3" t="n">
-        <v>29.9</v>
+      <c r="M28" s="8" t="n">
+        <v>19.9</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>23.1</v>
@@ -2868,10 +2856,10 @@
       <c r="P28" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q28" s="9" t="n">
+      <c r="Q28" s="8" t="n">
         <v>29.7</v>
       </c>
-      <c r="R28" s="9" t="n">
+      <c r="R28" s="8" t="n">
         <v>25.1</v>
       </c>
       <c r="S28" s="3" t="n">
@@ -2883,20 +2871,20 @@
       <c r="U28" s="3" t="n">
         <v>12.7</v>
       </c>
-      <c r="V28" s="9" t="n">
+      <c r="V28" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="W28" s="9" t="n">
+      <c r="W28" s="8" t="n">
         <v>22.6</v>
       </c>
-      <c r="X28" s="8" t="n">
+      <c r="X28" s="3" t="n">
         <v>26.3</v>
       </c>
       <c r="Y28" s="3" t="n">
         <v>86</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>14.3</v>
+        <v>4.3</v>
       </c>
       <c r="AA28" s="3" t="inlineStr">
         <is>
@@ -2914,16 +2902,16 @@
       <c r="C29" s="3" t="n">
         <v>146.2</v>
       </c>
-      <c r="D29" s="9" t="n">
+      <c r="D29" s="8" t="n">
         <v>29.2</v>
       </c>
-      <c r="E29" s="9" t="n">
+      <c r="E29" s="8" t="n">
         <v>20.3</v>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="G29" s="9" t="n">
+      <c r="G29" s="8" t="n">
         <v>8.9</v>
       </c>
       <c r="H29" s="3" t="n">
@@ -2935,13 +2923,13 @@
       <c r="J29" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="K29" s="9" t="n">
+      <c r="K29" s="8" t="n">
         <v>18.1</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>21.9</v>
       </c>
-      <c r="M29" s="3" t="n">
+      <c r="M29" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="N29" s="3" t="n">
@@ -2953,10 +2941,10 @@
       <c r="P29" s="3" t="n">
         <v>0.9</v>
       </c>
-      <c r="Q29" s="9" t="n">
+      <c r="Q29" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="R29" s="9" t="n">
+      <c r="R29" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="S29" s="3" t="n">
@@ -2968,10 +2956,10 @@
       <c r="U29" s="3" t="n">
         <v>10.3</v>
       </c>
-      <c r="V29" s="9" t="n">
+      <c r="V29" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="W29" s="9" t="n">
+      <c r="W29" s="8" t="n">
         <v>22.6</v>
       </c>
       <c r="X29" s="3" t="n">
@@ -2981,7 +2969,7 @@
         <v>81.8</v>
       </c>
       <c r="Z29" s="3" t="n">
-        <v>15.8</v>
+        <v>5.8</v>
       </c>
       <c r="AA29" s="3" t="inlineStr">
         <is>
@@ -2997,36 +2985,36 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>136.3</v>
-      </c>
-      <c r="D30" s="16" t="n">
-        <v>1156.5</v>
-      </c>
-      <c r="E30" s="9" t="n">
+        <v>1363.5</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>156.5</v>
+      </c>
+      <c r="E30" s="8" t="n">
         <v>99.59999999999999</v>
       </c>
-      <c r="F30" s="16" t="n">
+      <c r="F30" s="8" t="n">
         <v>128</v>
       </c>
-      <c r="G30" s="17" t="n">
-        <v>25.7</v>
+      <c r="G30" s="8" t="n">
+        <v>56.9</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>92.2</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>19.9</v>
+        <v>9.9</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>1171.8</v>
-      </c>
-      <c r="K30" s="9" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="K30" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="L30" s="16" t="n">
+      <c r="L30" s="15" t="n">
         <v>102.2</v>
       </c>
-      <c r="M30" s="16" t="n">
+      <c r="M30" s="8" t="n">
         <v>101.1</v>
       </c>
       <c r="N30" s="3" t="n">
@@ -3038,14 +3026,14 @@
       <c r="P30" s="3" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q30" s="9" t="n">
+      <c r="Q30" s="8" t="n">
         <v>145.5</v>
       </c>
-      <c r="R30" s="9" t="n">
+      <c r="R30" s="8" t="n">
         <v>121</v>
       </c>
       <c r="S30" s="3" t="n">
-        <v>13.5</v>
+        <v>135.5</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>344.5</v>
@@ -3053,17 +3041,17 @@
       <c r="U30" s="3" t="n">
         <v>68.8</v>
       </c>
-      <c r="V30" s="9" t="n">
+      <c r="V30" s="8" t="n">
         <v>127.4</v>
       </c>
-      <c r="W30" s="9" t="n">
+      <c r="W30" s="8" t="n">
         <v>115.3</v>
       </c>
       <c r="X30" s="3" t="n">
         <v>133.7</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>2411.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>30.9</v>
@@ -3084,16 +3072,16 @@
       <c r="C31" s="3" t="n">
         <v>272.7</v>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="D31" s="8" t="n">
         <v>31.3</v>
       </c>
-      <c r="E31" s="9" t="n">
+      <c r="E31" s="8" t="n">
         <v>19.9</v>
       </c>
-      <c r="F31" s="9" t="n">
+      <c r="F31" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="G31" s="9" t="n">
+      <c r="G31" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="H31" s="3" t="n">
@@ -3103,30 +3091,30 @@
         <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>13.4</v>
+        <v>3.4</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="L31" s="16" t="n">
+      <c r="L31" s="15" t="n">
         <v>20.4</v>
       </c>
-      <c r="M31" s="16" t="n">
+      <c r="M31" s="8" t="n">
         <v>20.2</v>
       </c>
       <c r="N31" s="3" t="n">
         <v>23.6</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>9.699999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="P31" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="Q31" s="9" t="n">
+      <c r="Q31" s="8" t="n">
         <v>29.1</v>
       </c>
-      <c r="R31" s="9" t="n">
+      <c r="R31" s="8" t="n">
         <v>24.2</v>
       </c>
       <c r="S31" s="3" t="n">
@@ -3135,16 +3123,16 @@
       <c r="T31" s="3" t="n">
         <v>68.90000000000001</v>
       </c>
-      <c r="U31" s="8" t="n">
-        <v>113.8</v>
-      </c>
-      <c r="V31" s="16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="W31" s="9" t="n">
+      <c r="U31" s="3" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="W31" s="8" t="n">
         <v>23.1</v>
       </c>
-      <c r="X31" s="8" t="n">
+      <c r="X31" s="3" t="n">
         <v>26.7</v>
       </c>
       <c r="Y31" s="3" t="n">
@@ -3169,34 +3157,34 @@
       <c r="C32" s="3" t="n">
         <v>263.5</v>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="D32" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="E32" s="9" t="n">
+      <c r="E32" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="F32" s="9" t="n">
+      <c r="F32" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="G32" s="9" t="n">
+      <c r="G32" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="H32" s="8" t="n">
+      <c r="H32" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>1.3</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="K32" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K32" s="8" t="n">
         <v>3.4</v>
       </c>
-      <c r="L32" s="9" t="n">
+      <c r="L32" s="8" t="n">
         <v>21.6</v>
       </c>
-      <c r="M32" s="9" t="n">
+      <c r="M32" s="8" t="n">
         <v>21.5</v>
       </c>
       <c r="N32" s="3" t="n">
@@ -3208,13 +3196,13 @@
       <c r="P32" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q32" s="9" t="n">
+      <c r="Q32" s="8" t="n">
         <v>29</v>
       </c>
-      <c r="R32" s="9" t="n">
+      <c r="R32" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="S32" s="8" t="n">
+      <c r="S32" s="3" t="n">
         <v>27.9</v>
       </c>
       <c r="T32" s="3" t="n">
@@ -3223,20 +3211,20 @@
       <c r="U32" s="3" t="n">
         <v>12.1</v>
       </c>
-      <c r="V32" s="9" t="n">
+      <c r="V32" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W32" s="9" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="X32" s="8" t="n">
+      <c r="W32" s="8" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="X32" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>181.1</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z32" s="3" t="n">
-        <v>16.7</v>
+        <v>6.7</v>
       </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
@@ -3254,16 +3242,16 @@
       <c r="C33" s="3" t="n">
         <v>44.1</v>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="D33" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="E33" s="9" t="n">
+      <c r="E33" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="F33" s="9" t="n">
+      <c r="F33" s="8" t="n">
         <v>22.9</v>
       </c>
-      <c r="G33" s="9" t="n">
+      <c r="G33" s="8" t="n">
         <v>4.6</v>
       </c>
       <c r="H33" s="3" t="n">
@@ -3275,16 +3263,16 @@
       <c r="J33" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K33" s="3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="L33" s="9" t="n">
+      <c r="K33" s="8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L33" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="M33" s="9" t="n">
+      <c r="M33" s="8" t="n">
         <v>20.6</v>
       </c>
-      <c r="N33" s="8" t="n">
+      <c r="N33" s="3" t="n">
         <v>24.1</v>
       </c>
       <c r="O33" s="3" t="n">
@@ -3293,25 +3281,25 @@
       <c r="P33" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q33" s="9" t="n">
+      <c r="Q33" s="8" t="n">
         <v>24.2</v>
       </c>
-      <c r="R33" s="9" t="n">
+      <c r="R33" s="8" t="n">
         <v>22.1</v>
       </c>
       <c r="S33" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>183.4</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="V33" s="9" t="n">
+      <c r="V33" s="8" t="n">
         <v>23</v>
       </c>
-      <c r="W33" s="9" t="n">
+      <c r="W33" s="8" t="n">
         <v>22</v>
       </c>
       <c r="X33" s="3" t="n">
@@ -3337,37 +3325,37 @@
       <c r="C34" s="3" t="n">
         <v>117.2</v>
       </c>
-      <c r="D34" s="9" t="n">
+      <c r="D34" s="8" t="n">
         <v>30.6</v>
       </c>
-      <c r="E34" s="9" t="n">
+      <c r="E34" s="8" t="n">
         <v>19.1</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G34" s="9" t="n">
+      <c r="G34" s="8" t="n">
         <v>11.5</v>
       </c>
-      <c r="H34" s="8" t="n">
+      <c r="H34" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>11.9</v>
+        <v>1.9</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="K34" s="3" t="n">
+      <c r="K34" s="8" t="n">
         <v>5.9</v>
       </c>
-      <c r="L34" s="9" t="n">
+      <c r="L34" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="M34" s="9" t="n">
+      <c r="M34" s="8" t="n">
         <v>20.1</v>
       </c>
-      <c r="N34" s="8" t="n">
+      <c r="N34" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="O34" s="3" t="n">
@@ -3376,10 +3364,10 @@
       <c r="P34" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" s="9" t="n">
+      <c r="Q34" s="8" t="n">
         <v>30.1</v>
       </c>
-      <c r="R34" s="9" t="n">
+      <c r="R34" s="8" t="n">
         <v>25.6</v>
       </c>
       <c r="S34" s="3" t="n">
@@ -3391,10 +3379,10 @@
       <c r="U34" s="3" t="n">
         <v>12.6</v>
       </c>
-      <c r="V34" s="9" t="n">
+      <c r="V34" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W34" s="9" t="n">
+      <c r="W34" s="8" t="n">
         <v>21</v>
       </c>
       <c r="X34" s="3" t="n">
@@ -3422,19 +3410,19 @@
       <c r="C35" s="3" t="n">
         <v>284.4</v>
       </c>
-      <c r="D35" s="9" t="n">
+      <c r="D35" s="8" t="n">
         <v>29.5</v>
       </c>
-      <c r="E35" s="9" t="n">
+      <c r="E35" s="8" t="n">
         <v>18.8</v>
       </c>
-      <c r="F35" s="9" t="n">
+      <c r="F35" s="8" t="n">
         <v>24.1</v>
       </c>
-      <c r="G35" s="9" t="n">
+      <c r="G35" s="8" t="n">
         <v>10.7</v>
       </c>
-      <c r="H35" s="8" t="n">
+      <c r="H35" s="3" t="n">
         <v>17.6</v>
       </c>
       <c r="I35" s="3" t="n">
@@ -3443,17 +3431,17 @@
       <c r="J35" s="3" t="n">
         <v>1.8</v>
       </c>
-      <c r="K35" s="3" t="n">
+      <c r="K35" s="8" t="n">
         <v>2.8</v>
       </c>
-      <c r="L35" s="9" t="n">
+      <c r="L35" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="M35" s="9" t="n">
+      <c r="M35" s="8" t="n">
         <v>19</v>
       </c>
-      <c r="N35" s="8" t="n">
-        <v>13.9</v>
+      <c r="N35" s="3" t="n">
+        <v>20.9</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>100</v>
@@ -3461,35 +3449,35 @@
       <c r="P35" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" s="9" t="n">
+      <c r="Q35" s="8" t="n">
         <v>28.3</v>
       </c>
-      <c r="R35" s="9" t="n">
+      <c r="R35" s="8" t="n">
         <v>24.8</v>
       </c>
       <c r="S35" s="3" t="n">
         <v>29</v>
       </c>
       <c r="T35" s="3" t="n">
-        <v>25.4</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="U35" s="3" t="n">
         <v>9.4</v>
       </c>
-      <c r="V35" s="9" t="n">
+      <c r="V35" s="8" t="n">
         <v>26.3</v>
       </c>
-      <c r="W35" s="9" t="n">
+      <c r="W35" s="8" t="n">
         <v>24.4</v>
       </c>
-      <c r="X35" s="8" t="n">
-        <v>9.300000000000001</v>
+      <c r="X35" s="3" t="n">
+        <v>29.3</v>
       </c>
       <c r="Y35" s="3" t="n">
-        <v>185.8</v>
+        <v>85.8</v>
       </c>
       <c r="Z35" s="3" t="n">
-        <v>14.9</v>
+        <v>4.9</v>
       </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
@@ -3505,22 +3493,22 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1117.2</v>
-      </c>
-      <c r="D36" s="9" t="n">
+        <v>117.2</v>
+      </c>
+      <c r="D36" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="E36" s="9" t="n">
+      <c r="E36" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="8" t="n">
         <v>24.9</v>
       </c>
-      <c r="G36" s="3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="H36" s="8" t="n">
-        <v>119</v>
+      <c r="G36" s="8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.6</v>
@@ -3528,16 +3516,16 @@
       <c r="J36" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="K36" s="3" t="n">
+      <c r="K36" s="8" t="n">
         <v>1.3</v>
       </c>
-      <c r="L36" s="9" t="n">
+      <c r="L36" s="8" t="n">
         <v>21.9</v>
       </c>
-      <c r="M36" s="9" t="n">
+      <c r="M36" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="N36" s="8" t="n">
+      <c r="N36" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="O36" s="3" t="n">
@@ -3546,10 +3534,10 @@
       <c r="P36" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q36" s="9" t="n">
+      <c r="Q36" s="8" t="n">
         <v>21.5</v>
       </c>
-      <c r="R36" s="9" t="n">
+      <c r="R36" s="8" t="n">
         <v>20.9</v>
       </c>
       <c r="S36" s="3" t="n">
@@ -3561,17 +3549,17 @@
       <c r="U36" s="3" t="n">
         <v>1.3</v>
       </c>
-      <c r="V36" s="9" t="n">
+      <c r="V36" s="8" t="n">
         <v>21.4</v>
       </c>
-      <c r="W36" s="9" t="n">
+      <c r="W36" s="8" t="n">
         <v>20.8</v>
       </c>
       <c r="X36" s="3" t="n">
         <v>24.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>194.8</v>
+        <v>94.8</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>1.3</v>
@@ -3592,17 +3580,17 @@
       <c r="C37" s="3" t="n">
         <v>826.4</v>
       </c>
-      <c r="D37" s="9" t="n">
+      <c r="D37" s="8" t="n">
         <v>142.9</v>
       </c>
-      <c r="E37" s="9" t="n">
+      <c r="E37" s="8" t="n">
         <v>100</v>
       </c>
-      <c r="F37" s="9" t="n">
+      <c r="F37" s="8" t="n">
         <v>121.5</v>
       </c>
-      <c r="G37" s="17" t="n">
-        <v>14.3</v>
+      <c r="G37" s="8" t="n">
+        <v>42.9</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.8</v>
@@ -3613,13 +3601,13 @@
       <c r="J37" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="K37" s="16" t="n">
+      <c r="K37" s="8" t="n">
         <v>17.9</v>
       </c>
-      <c r="L37" s="9" t="n">
+      <c r="L37" s="8" t="n">
         <v>103.4</v>
       </c>
-      <c r="M37" s="9" t="n">
+      <c r="M37" s="8" t="n">
         <v>102.9</v>
       </c>
       <c r="N37" s="3" t="n">
@@ -3629,12 +3617,12 @@
         <v>495</v>
       </c>
       <c r="P37" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q37" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="8" t="n">
         <v>133.1</v>
       </c>
-      <c r="R37" s="9" t="n">
+      <c r="R37" s="8" t="n">
         <v>117.9</v>
       </c>
       <c r="S37" s="3" t="n">
@@ -3646,17 +3634,17 @@
       <c r="U37" s="3" t="n">
         <v>40.4</v>
       </c>
-      <c r="V37" s="9" t="n">
+      <c r="V37" s="8" t="n">
         <v>124.1</v>
       </c>
-      <c r="W37" s="16" t="n">
+      <c r="W37" s="8" t="n">
         <v>112.7</v>
       </c>
       <c r="X37" s="3" t="n">
         <v>129.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>416</v>
+        <v>16</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>28</v>
@@ -3675,21 +3663,21 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="D38" s="9" t="n">
+        <v>165.3</v>
+      </c>
+      <c r="D38" s="8" t="n">
         <v>28.6</v>
       </c>
-      <c r="E38" s="9" t="n">
+      <c r="E38" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F38" s="9" t="n">
+      <c r="F38" s="8" t="n">
         <v>24.3</v>
       </c>
-      <c r="G38" s="9" t="n">
+      <c r="G38" s="8" t="n">
         <v>8.6</v>
       </c>
-      <c r="H38" s="8" t="n">
+      <c r="H38" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I38" s="3" t="n">
@@ -3699,12 +3687,12 @@
         <v>1.8</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="L38" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L38" s="8" t="n">
         <v>20.7</v>
       </c>
-      <c r="M38" s="9" t="n">
+      <c r="M38" s="8" t="n">
         <v>20.6</v>
       </c>
       <c r="N38" s="3" t="n">
@@ -3716,35 +3704,35 @@
       <c r="P38" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q38" s="9" t="n">
+      <c r="Q38" s="8" t="n">
         <v>26.6</v>
       </c>
-      <c r="R38" s="9" t="n">
+      <c r="R38" s="8" t="n">
         <v>23.6</v>
       </c>
       <c r="S38" s="3" t="n">
         <v>27.3</v>
       </c>
       <c r="T38" s="3" t="n">
-        <v>78.8</v>
+        <v>78.7</v>
       </c>
       <c r="U38" s="3" t="n">
         <v>8.1</v>
       </c>
-      <c r="V38" s="16" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="W38" s="9" t="n">
+      <c r="V38" s="8" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="W38" s="8" t="n">
         <v>22.5</v>
       </c>
       <c r="X38" s="3" t="n">
         <v>26</v>
       </c>
       <c r="Y38" s="3" t="n">
-        <v>183.2</v>
+        <v>83.2</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>15.6</v>
+        <v>5.6</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3760,37 +3748,37 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>332.3</v>
-      </c>
-      <c r="D39" s="9" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="D39" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="E39" s="9" t="n">
+      <c r="E39" s="8" t="n">
         <v>19.3</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G39" s="9" t="n">
+      <c r="G39" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>18</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>5.8</v>
+        <v>0.8</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="L39" s="9" t="n">
+      <c r="L39" s="8" t="n">
         <v>19.5</v>
       </c>
-      <c r="M39" s="9" t="n">
-        <v>19.2</v>
+      <c r="M39" s="8" t="n">
+        <v>19.5</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>22.6</v>
@@ -3801,32 +3789,32 @@
       <c r="P39" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q39" s="9" t="n">
+      <c r="Q39" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="R39" s="9" t="n">
+      <c r="R39" s="8" t="n">
         <v>25.5</v>
       </c>
       <c r="S39" s="3" t="n">
         <v>29.3</v>
       </c>
       <c r="T39" s="3" t="n">
-        <v>68.5</v>
+        <v>66.5</v>
       </c>
       <c r="U39" s="3" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="V39" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="V39" s="8" t="n">
         <v>27.8</v>
       </c>
-      <c r="W39" s="9" t="n">
+      <c r="W39" s="8" t="n">
         <v>23.9</v>
       </c>
-      <c r="X39" s="8" t="n">
+      <c r="X39" s="3" t="n">
         <v>27.2</v>
       </c>
       <c r="Y39" s="3" t="n">
-        <v>172.9</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="Z39" s="3" t="n">
         <v>0</v>
@@ -3847,23 +3835,23 @@
       <c r="C40" s="3" t="n">
         <v>278.1</v>
       </c>
-      <c r="D40" s="9" t="n">
+      <c r="D40" s="8" t="n">
         <v>30.8</v>
       </c>
-      <c r="E40" s="9" t="n">
-        <v>20.06</v>
-      </c>
-      <c r="F40" s="9" t="n">
+      <c r="E40" s="8" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="F40" s="8" t="n">
         <v>25.7</v>
       </c>
-      <c r="G40" s="9" t="n">
+      <c r="G40" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>11.8</v>
+        <v>1.8</v>
       </c>
       <c r="J40" s="3" t="n">
         <v>3.1</v>
@@ -3871,13 +3859,13 @@
       <c r="K40" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L40" s="9" t="n">
+      <c r="L40" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="M40" s="9" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="N40" s="8" t="n">
+      <c r="M40" s="8" t="n">
+        <v>20.2</v>
+      </c>
+      <c r="N40" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="O40" s="3" t="n">
@@ -3886,25 +3874,25 @@
       <c r="P40" s="3" t="n">
         <v>0.2</v>
       </c>
-      <c r="Q40" s="9" t="n">
+      <c r="Q40" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="R40" s="9" t="n">
+      <c r="R40" s="8" t="n">
         <v>25.3</v>
       </c>
       <c r="S40" s="3" t="n">
         <v>28.8</v>
       </c>
       <c r="T40" s="3" t="n">
-        <v>165.4</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="U40" s="3" t="n">
         <v>15.2</v>
       </c>
-      <c r="V40" s="9" t="n">
+      <c r="V40" s="8" t="n">
         <v>28</v>
       </c>
-      <c r="W40" s="9" t="n">
+      <c r="W40" s="8" t="n">
         <v>24</v>
       </c>
       <c r="X40" s="3" t="n">
@@ -3914,7 +3902,7 @@
         <v>72.2</v>
       </c>
       <c r="Z40" s="3" t="n">
-        <v>120.4</v>
+        <v>10.4</v>
       </c>
       <c r="AA40" s="3" t="inlineStr">
         <is>
@@ -3932,32 +3920,32 @@
       <c r="C41" s="3" t="n">
         <v>242.6</v>
       </c>
-      <c r="D41" s="9" t="n">
+      <c r="D41" s="8" t="n">
         <v>29.6</v>
       </c>
-      <c r="E41" s="9" t="n">
+      <c r="E41" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="F41" s="9" t="n">
+      <c r="F41" s="8" t="n">
         <v>25.2</v>
       </c>
-      <c r="G41" s="9" t="n">
+      <c r="G41" s="8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>18.5</v>
+        <v>1.5</v>
       </c>
       <c r="J41" s="3" t="inlineStr"/>
       <c r="K41" s="3" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="L41" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L41" s="8" t="n">
         <v>20.9</v>
       </c>
-      <c r="M41" s="9" t="n">
+      <c r="M41" s="8" t="n">
         <v>20.2</v>
       </c>
       <c r="N41" s="3" t="n">
@@ -3969,32 +3957,32 @@
       <c r="P41" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q41" s="9" t="n">
+      <c r="Q41" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="R41" s="9" t="n">
+      <c r="R41" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S41" s="3" t="n">
         <v>28.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>720.5</v>
+        <v>70.5</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="V41" s="9" t="n">
+      <c r="V41" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W41" s="9" t="n">
+      <c r="W41" s="8" t="n">
         <v>24.5</v>
       </c>
-      <c r="X41" s="8" t="n">
+      <c r="X41" s="3" t="n">
         <v>29.1</v>
       </c>
       <c r="Y41" s="3" t="n">
-        <v>841.1</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="Z41" s="3" t="n">
         <v>6.7</v>
@@ -4015,23 +4003,23 @@
       <c r="C42" s="3" t="n">
         <v>288.6</v>
       </c>
-      <c r="D42" s="9" t="n">
+      <c r="D42" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="E42" s="9" t="n">
+      <c r="E42" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="F42" s="9" t="n">
+      <c r="F42" s="8" t="n">
         <v>25.6</v>
       </c>
-      <c r="G42" s="9" t="n">
+      <c r="G42" s="8" t="n">
         <v>10.5</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>18.6</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="J42" s="3" t="n">
         <v>2.9</v>
@@ -4039,13 +4027,13 @@
       <c r="K42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L42" s="9" t="n">
+      <c r="L42" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="M42" s="9" t="n">
+      <c r="M42" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="N42" s="8" t="n">
+      <c r="N42" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="O42" s="3" t="n">
@@ -4054,10 +4042,10 @@
       <c r="P42" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" s="9" t="n">
+      <c r="Q42" s="8" t="n">
         <v>30.9</v>
       </c>
-      <c r="R42" s="9" t="n">
+      <c r="R42" s="8" t="n">
         <v>24.9</v>
       </c>
       <c r="S42" s="3" t="n">
@@ -4069,10 +4057,10 @@
       <c r="U42" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="V42" s="9" t="n">
+      <c r="V42" s="8" t="n">
         <v>27.1</v>
       </c>
-      <c r="W42" s="9" t="n">
+      <c r="W42" s="8" t="n">
         <v>24.6</v>
       </c>
       <c r="X42" s="3" t="n">
@@ -4082,7 +4070,7 @@
         <v>81.8</v>
       </c>
       <c r="Z42" s="3" t="n">
-        <v>16.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -4100,23 +4088,23 @@
       <c r="C43" s="3" t="n">
         <v>311.6</v>
       </c>
-      <c r="D43" s="9" t="n">
+      <c r="D43" s="8" t="n">
         <v>30.7</v>
       </c>
-      <c r="E43" s="9" t="n">
+      <c r="E43" s="8" t="n">
         <v>21</v>
       </c>
-      <c r="F43" s="9" t="n">
+      <c r="F43" s="8" t="n">
         <v>25.9</v>
       </c>
-      <c r="G43" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="H43" s="8" t="n">
-        <v>8.6</v>
+      <c r="G43" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>41.6</v>
+        <v>21.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>3</v>
@@ -4124,28 +4112,28 @@
       <c r="K43" s="3" t="n">
         <v>3.9</v>
       </c>
-      <c r="L43" s="9" t="n">
+      <c r="L43" s="8" t="n">
         <v>21.2</v>
       </c>
-      <c r="M43" s="9" t="n">
+      <c r="M43" s="8" t="n">
         <v>21.1</v>
       </c>
-      <c r="N43" s="8" t="n">
+      <c r="N43" s="3" t="n">
         <v>24.9</v>
       </c>
       <c r="O43" s="3" t="n">
         <v>99</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="Q43" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q43" s="8" t="n">
         <v>24.7</v>
       </c>
-      <c r="R43" s="9" t="n">
+      <c r="R43" s="8" t="n">
         <v>21.7</v>
       </c>
-      <c r="S43" s="8" t="n">
+      <c r="S43" s="3" t="n">
         <v>24</v>
       </c>
       <c r="T43" s="3" t="n">
@@ -4154,13 +4142,13 @@
       <c r="U43" s="3" t="n">
         <v>7.1</v>
       </c>
-      <c r="V43" s="9" t="n">
+      <c r="V43" s="8" t="n">
         <v>24</v>
       </c>
-      <c r="W43" s="9" t="n">
+      <c r="W43" s="8" t="n">
         <v>22</v>
       </c>
-      <c r="X43" s="8" t="n">
+      <c r="X43" s="3" t="n">
         <v>25.2</v>
       </c>
       <c r="Y43" s="3" t="n">
@@ -4185,26 +4173,26 @@
       <c r="C44" s="3" t="n">
         <v>0.1</v>
       </c>
-      <c r="D44" s="9" t="inlineStr"/>
-      <c r="E44" s="9" t="inlineStr"/>
-      <c r="F44" s="9" t="inlineStr"/>
+      <c r="D44" s="8" t="inlineStr"/>
+      <c r="E44" s="8" t="inlineStr"/>
+      <c r="F44" s="8" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
       <c r="H44" s="3" t="inlineStr"/>
       <c r="I44" s="3" t="inlineStr"/>
       <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="15" t="inlineStr"/>
-      <c r="L44" s="9" t="inlineStr"/>
-      <c r="M44" s="9" t="inlineStr"/>
+      <c r="K44" s="14" t="inlineStr"/>
+      <c r="L44" s="8" t="inlineStr"/>
+      <c r="M44" s="8" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr"/>
       <c r="O44" s="3" t="inlineStr"/>
       <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="9" t="inlineStr"/>
-      <c r="R44" s="9" t="inlineStr"/>
+      <c r="Q44" s="8" t="inlineStr"/>
+      <c r="R44" s="8" t="inlineStr"/>
       <c r="S44" s="3" t="inlineStr"/>
       <c r="T44" s="3" t="inlineStr"/>
       <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="9" t="inlineStr"/>
-      <c r="W44" s="9" t="inlineStr"/>
+      <c r="V44" s="8" t="inlineStr"/>
+      <c r="W44" s="8" t="inlineStr"/>
       <c r="X44" s="3" t="inlineStr"/>
       <c r="Y44" s="3" t="inlineStr"/>
       <c r="Z44" s="3" t="inlineStr"/>
@@ -4222,19 +4210,19 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1423.4</v>
-      </c>
-      <c r="D45" s="16" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="E45" s="16" t="n">
-        <v>802.1</v>
-      </c>
-      <c r="F45" s="16" t="n">
-        <v>1127.8</v>
-      </c>
-      <c r="G45" s="17" t="n">
-        <v>19.1</v>
+        <v>1453.4</v>
+      </c>
+      <c r="D45" s="8" t="n">
+        <v>152.7</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="F45" s="8" t="n">
+        <v>127.4</v>
+      </c>
+      <c r="G45" s="8" t="n">
+        <v>50.6</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>93.59999999999999</v>
@@ -4243,15 +4231,15 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>114.9</v>
-      </c>
-      <c r="K45" s="16" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="K45" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="L45" s="9" t="n">
+      <c r="L45" s="8" t="n">
         <v>103.8</v>
       </c>
-      <c r="M45" s="16" t="n">
+      <c r="M45" s="15" t="n">
         <v>102.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4261,12 +4249,12 @@
         <v>491.8</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="Q45" s="9" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q45" s="8" t="n">
         <v>146.3</v>
       </c>
-      <c r="R45" s="9" t="n">
+      <c r="R45" s="8" t="n">
         <v>122.3</v>
       </c>
       <c r="S45" s="3" t="n">
@@ -4276,19 +4264,19 @@
         <v>341.4</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>166</v>
-      </c>
-      <c r="V45" s="16" t="n">
-        <v>1234</v>
-      </c>
-      <c r="W45" s="16" t="n">
-        <v>219</v>
+        <v>66</v>
+      </c>
+      <c r="V45" s="15" t="n">
+        <v>234</v>
+      </c>
+      <c r="W45" s="8" t="n">
+        <v>119</v>
       </c>
       <c r="X45" s="3" t="n">
         <v>138.1</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>392.3</v>
+        <v>92.3</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>38</v>
@@ -4309,34 +4297,34 @@
       <c r="C46" s="3" t="n">
         <v>290.7</v>
       </c>
-      <c r="D46" s="9" t="n">
+      <c r="D46" s="8" t="n">
         <v>30.5</v>
       </c>
-      <c r="E46" s="9" t="n">
+      <c r="E46" s="8" t="n">
         <v>20.4</v>
       </c>
-      <c r="F46" s="9" t="n">
+      <c r="F46" s="8" t="n">
         <v>25.5</v>
       </c>
-      <c r="G46" s="9" t="n">
+      <c r="G46" s="8" t="n">
         <v>10.1</v>
       </c>
-      <c r="H46" s="8" t="n">
+      <c r="H46" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="J46" s="3" t="n">
         <v>3</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L46" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L46" s="8" t="n">
         <v>20.8</v>
       </c>
-      <c r="M46" s="9" t="n">
+      <c r="M46" s="8" t="n">
         <v>20.6</v>
       </c>
       <c r="N46" s="3" t="n">
@@ -4348,14 +4336,14 @@
       <c r="P46" s="3" t="n">
         <v>0.4</v>
       </c>
-      <c r="Q46" s="9" t="n">
+      <c r="Q46" s="8" t="n">
         <v>29.3</v>
       </c>
-      <c r="R46" s="16" t="n">
-        <v>2.4</v>
+      <c r="R46" s="8" t="n">
+        <v>24.5</v>
       </c>
       <c r="S46" s="3" t="n">
-        <v>27.8</v>
+        <v>27.7</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>68.3</v>
@@ -4363,20 +4351,20 @@
       <c r="U46" s="3" t="n">
         <v>13.2</v>
       </c>
-      <c r="V46" s="9" t="n">
+      <c r="V46" s="8" t="n">
         <v>26.8</v>
       </c>
-      <c r="W46" s="9" t="n">
+      <c r="W46" s="8" t="n">
         <v>23.8</v>
       </c>
-      <c r="X46" s="8" t="n">
+      <c r="X46" s="3" t="n">
         <v>27.6</v>
       </c>
       <c r="Y46" s="3" t="n">
-        <v>28.5</v>
+        <v>78.5</v>
       </c>
       <c r="Z46" s="3" t="n">
-        <v>78.7</v>
+        <v>7.7</v>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -143,7 +143,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -159,9 +159,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1030,7 +1027,7 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>18.2</v>
+        <v>418.2</v>
       </c>
       <c r="D7" s="8" t="n">
         <v>32.4</v>
@@ -1241,8 +1238,8 @@
       <c r="P9" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q9" s="8" t="n">
-        <v>155.6</v>
+      <c r="Q9" s="9" t="n">
+        <v>156.6</v>
       </c>
       <c r="R9" s="8" t="n">
         <v>124.4</v>
@@ -1300,7 +1297,7 @@
         <v>10.8</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>2.4</v>
@@ -1309,7 +1306,7 @@
         <v>4.2</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="8" t="n">
         <v>21.9</v>
@@ -1339,7 +1336,7 @@
         <v>61.6</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="V10" s="8" t="n">
         <v>27.1</v>
@@ -1370,7 +1367,7 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>33.3</v>
@@ -1391,7 +1388,7 @@
         <v>4.1</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K11" s="8" t="n">
         <v>0</v>
@@ -1455,7 +1452,7 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>18.2</v>
+        <v>418.2</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>32.8</v>
@@ -1965,7 +1962,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>332.5</v>
+        <v>332</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>32.2</v>
@@ -2226,7 +2223,7 @@
         <v>30.1</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
       <c r="F21" s="8" t="n">
         <v>24.1</v>
@@ -2316,8 +2313,8 @@
       <c r="F22" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G22" s="3" t="n">
-        <v>12.9</v>
+      <c r="G22" s="8" t="n">
+        <v>12.4</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>17.4</v>
@@ -2426,7 +2423,7 @@
         <v>113.3</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>94</v>
+        <v>494</v>
       </c>
       <c r="P23" s="3" t="n">
         <v>1.3</v>
@@ -2730,7 +2727,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>18.2</v>
+        <v>418.2</v>
       </c>
       <c r="D27" s="8" t="n">
         <v>32.9</v>
@@ -2815,7 +2812,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>28.2</v>
+        <v>282.4</v>
       </c>
       <c r="D28" s="8" t="n">
         <v>32.6</v>
@@ -3011,7 +3008,7 @@
       <c r="K30" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="L30" s="15" t="n">
+      <c r="L30" s="9" t="n">
         <v>102.2</v>
       </c>
       <c r="M30" s="8" t="n">
@@ -3051,7 +3048,7 @@
         <v>133.7</v>
       </c>
       <c r="Y30" s="3" t="n">
-        <v>11.5</v>
+        <v>411.5</v>
       </c>
       <c r="Z30" s="3" t="n">
         <v>30.9</v>
@@ -3094,9 +3091,9 @@
         <v>3.4</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L31" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="9" t="n">
         <v>20.4</v>
       </c>
       <c r="M31" s="8" t="n">
@@ -3441,7 +3438,7 @@
         <v>19</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>20.9</v>
+        <v>21.9</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>100</v>
@@ -3644,7 +3641,7 @@
         <v>129.8</v>
       </c>
       <c r="Y37" s="3" t="n">
-        <v>16</v>
+        <v>416</v>
       </c>
       <c r="Z37" s="3" t="n">
         <v>28</v>
@@ -3732,7 +3729,7 @@
         <v>83.2</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>5.6</v>
+        <v>15.6</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3769,7 +3766,7 @@
         <v>1.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.8</v>
+        <v>10.1</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>3.5</v>
@@ -3778,7 +3775,7 @@
         <v>19.5</v>
       </c>
       <c r="M39" s="8" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="N39" s="3" t="n">
         <v>22.6</v>
@@ -3863,7 +3860,7 @@
         <v>21</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>20.2</v>
+        <v>20.9</v>
       </c>
       <c r="N40" s="3" t="n">
         <v>24.6</v>
@@ -4233,13 +4230,13 @@
       <c r="J45" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="K45" s="15" t="n">
+      <c r="K45" s="9" t="n">
         <v>5</v>
       </c>
       <c r="L45" s="8" t="n">
         <v>103.8</v>
       </c>
-      <c r="M45" s="15" t="n">
+      <c r="M45" s="9" t="n">
         <v>102.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4266,8 +4263,8 @@
       <c r="U45" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="V45" s="15" t="n">
-        <v>234</v>
+      <c r="V45" s="8" t="n">
+        <v>134</v>
       </c>
       <c r="W45" s="8" t="n">
         <v>119</v>
@@ -4276,10 +4273,10 @@
         <v>138.1</v>
       </c>
       <c r="Y45" s="3" t="n">
-        <v>92.3</v>
+        <v>392.3</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>38</v>
+        <v>38.2</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4319,7 +4316,7 @@
         <v>3</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>2.1</v>
+        <v>0.1</v>
       </c>
       <c r="L46" s="8" t="n">
         <v>20.8</v>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -41,14 +41,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0075696F"/>
-        <bgColor rgb="0075696F"/>
+        <fgColor rgb="00CC3300"/>
+        <bgColor rgb="00CC3300"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CC3300"/>
-        <bgColor rgb="00CC3300"/>
+        <fgColor rgb="0075696F"/>
+        <bgColor rgb="0075696F"/>
       </patternFill>
     </fill>
     <fill>
@@ -1238,8 +1238,8 @@
       <c r="P9" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="Q9" s="9" t="n">
-        <v>156.6</v>
+      <c r="Q9" s="8" t="n">
+        <v>155.6</v>
       </c>
       <c r="R9" s="8" t="n">
         <v>124.4</v>
@@ -1336,7 +1336,7 @@
         <v>61.6</v>
       </c>
       <c r="U10" s="3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="V10" s="8" t="n">
         <v>27.1</v>
@@ -1367,13 +1367,13 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>42.2</v>
+        <v>42</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>33.3</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>19.2</v>
+        <v>19.9</v>
       </c>
       <c r="F11" s="8" t="n">
         <v>26.6</v>
@@ -1798,12 +1798,12 @@
         <v>154.2</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>99.40000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="F16" s="8" t="n">
         <v>126.8</v>
       </c>
-      <c r="G16" s="3" t="n">
+      <c r="G16" s="8" t="n">
         <v>54.5</v>
       </c>
       <c r="H16" s="3" t="n">
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>332</v>
+        <v>332.5</v>
       </c>
       <c r="D18" s="8" t="n">
         <v>32.2</v>
@@ -2223,7 +2223,7 @@
         <v>30.1</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18.2</v>
+        <v>18</v>
       </c>
       <c r="F21" s="8" t="n">
         <v>24.1</v>
@@ -2313,8 +2313,8 @@
       <c r="F22" s="8" t="n">
         <v>25</v>
       </c>
-      <c r="G22" s="8" t="n">
-        <v>12.4</v>
+      <c r="G22" s="3" t="n">
+        <v>12.8</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>17.4</v>
@@ -2583,7 +2583,7 @@
       <c r="K25" s="8" t="n">
         <v>5.6</v>
       </c>
-      <c r="L25" s="10" t="n">
+      <c r="L25" s="9" t="n">
         <v>40.6</v>
       </c>
       <c r="M25" s="8" t="n">
@@ -2626,7 +2626,7 @@
         <v>95.2</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>282.4</v>
+        <v>28.2</v>
       </c>
       <c r="D28" s="8" t="n">
         <v>32.6</v>
@@ -3008,7 +3008,7 @@
       <c r="K30" s="8" t="n">
         <v>23.7</v>
       </c>
-      <c r="L30" s="9" t="n">
+      <c r="L30" s="10" t="n">
         <v>102.2</v>
       </c>
       <c r="M30" s="8" t="n">
@@ -3093,7 +3093,7 @@
       <c r="K31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="L31" s="9" t="n">
+      <c r="L31" s="10" t="n">
         <v>20.4</v>
       </c>
       <c r="M31" s="8" t="n">
@@ -3438,7 +3438,7 @@
         <v>19</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>21.9</v>
+        <v>20.9</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>100</v>
@@ -3556,7 +3556,7 @@
         <v>24.2</v>
       </c>
       <c r="Y36" s="3" t="n">
-        <v>94.8</v>
+        <v>924.8</v>
       </c>
       <c r="Z36" s="3" t="n">
         <v>1.3</v>
@@ -3684,7 +3684,7 @@
         <v>1.8</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L38" s="8" t="n">
         <v>20.7</v>
@@ -3729,7 +3729,7 @@
         <v>83.2</v>
       </c>
       <c r="Z38" s="3" t="n">
-        <v>15.6</v>
+        <v>5.6</v>
       </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>1.8</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>10.1</v>
+        <v>0.1</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>3.5</v>
@@ -4101,7 +4101,7 @@
         <v>18.6</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>21.6</v>
+        <v>1.6</v>
       </c>
       <c r="J43" s="3" t="n">
         <v>3</v>
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="C44" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D44" s="8" t="inlineStr"/>
       <c r="E44" s="8" t="inlineStr"/>
@@ -4207,7 +4207,7 @@
         </is>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1453.4</v>
+        <v>145.3</v>
       </c>
       <c r="D45" s="8" t="n">
         <v>152.7</v>
@@ -4230,13 +4230,13 @@
       <c r="J45" s="3" t="n">
         <v>14.9</v>
       </c>
-      <c r="K45" s="9" t="n">
+      <c r="K45" s="10" t="n">
         <v>5</v>
       </c>
       <c r="L45" s="8" t="n">
         <v>103.8</v>
       </c>
-      <c r="M45" s="9" t="n">
+      <c r="M45" s="10" t="n">
         <v>102.9</v>
       </c>
       <c r="N45" s="3" t="n">
@@ -4270,13 +4270,13 @@
         <v>119</v>
       </c>
       <c r="X45" s="3" t="n">
-        <v>138.1</v>
+        <v>13.8</v>
       </c>
       <c r="Y45" s="3" t="n">
         <v>392.3</v>
       </c>
       <c r="Z45" s="3" t="n">
-        <v>38.2</v>
+        <v>38.5</v>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>3</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="8" t="n">
         <v>20.8</v>

--- a/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_duirnal_temp_range.xlsx
+++ b/results/05_transient_transcription_output/203/203_196906_SF.JPG_stage_duirnal_temp_range.xlsx
@@ -807,7 +807,7 @@
       <c r="J4" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="K4" s="3" t="n">
+      <c r="K4" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
@@ -892,7 +892,7 @@
       <c r="J5" s="3" t="n">
         <v>3.1</v>
       </c>
-      <c r="K5" s="3" t="n">
+      <c r="K5" s="9" t="n">
         <v>1.9</v>
       </c>
       <c r="L5" s="3" t="n">
@@ -977,7 +977,7 @@
       <c r="J6" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K6" s="3" t="n">
+      <c r="K6" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
@@ -1062,7 +1062,7 @@
       <c r="J7" s="8" t="n">
         <v>2.1</v>
       </c>
-      <c r="K7" s="3" t="n">
+      <c r="K7" s="9" t="n">
         <v>0.1</v>
       </c>
       <c r="L7" s="3" t="n">
@@ -1147,7 +1147,7 @@
       <c r="J8" s="3" t="n">
         <v>5.8</v>
       </c>
-      <c r="K8" s="3" t="n">
+      <c r="K8" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="3" t="n">
@@ -1232,7 +1232,7 @@
       <c r="J9" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="K9" s="3" t="n">
+      <c r="K9" s="9" t="n">
         <v>2</v>
       </c>
       <c r="L9" s="3" t="n">
@@ -1403,7 +1403,7 @@
       <c r="J11" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="K11" s="3" t="n">
+      <c r="K11" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="3" t="n">
@@ -1488,7 +1488,7 @@
       <c r="J12" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="K12" s="3" t="n">
+      <c r="K12" s="9" t="n">
         <v>4.8</v>
       </c>
       <c r="L12" s="3" t="n">
@@ -1573,7 +1573,7 @@
       <c r="J13" s="3" t="n">
         <v>2.9</v>
       </c>
-      <c r="K13" s="3" t="n">
+      <c r="K13" s="9" t="n">
         <v>11.6</v>
       </c>
       <c r="L13" s="3" t="n">
@@ -1658,7 +1658,7 @@
       <c r="J14" s="3" t="n">
         <v>11.6</v>
       </c>
-      <c r="K14" s="3" t="n">
+      <c r="K14" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="3" t="n">
@@ -1743,7 +1743,7 @@
       <c r="J15" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="K15" s="3" t="n">
+      <c r="K15" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="3" t="n">
@@ -1828,7 +1828,7 @@
       <c r="J16" s="3" t="n">
         <v>19.7</v>
       </c>
-      <c r="K16" s="3" t="n">
+      <c r="K16" s="9" t="n">
         <v>16.4</v>
       </c>
       <c r="L16" s="3" t="n">
@@ -1998,7 +1998,7 @@
       <c r="J18" s="3" t="n">
         <v>4.1</v>
       </c>
-      <c r="K18" s="3" t="n">
+      <c r="K18" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="8" t="n">
@@ -2083,7 +2083,7 @@
       <c r="J19" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K19" s="3" t="n">
+      <c r="K19" s="9" t="n">
         <v>4.2</v>
       </c>
       <c r="L19" s="3" t="n">
@@ -2168,7 +2168,7 @@
       <c r="J20" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K20" s="3" t="n">
+      <c r="K20" s="9" t="n">
         <v>2.2</v>
       </c>
       <c r="L20" s="3" t="n">
@@ -2253,7 +2253,7 @@
       <c r="J21" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="K21" s="3" t="n">
+      <c r="K21" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="8" t="n">
@@ -2338,7 +2338,7 @@
       <c r="J22" s="3" t="n">
         <v>3.5</v>
       </c>
-      <c r="K22" s="3" t="n">
+      <c r="K22" s="9" t="n">
         <v>0.1</v>
       </c>
       <c r="L22" s="8" t="n">
@@ -2423,7 +2423,7 @@
       <c r="J23" s="3" t="n">
         <v>18.4</v>
       </c>
-      <c r="K23" s="3" t="n">
+      <c r="K23" s="9" t="n">
         <v>6.5</v>
       </c>
       <c r="L23" s="3" t="n">
@@ -3004,7 +3004,7 @@
       <c r="J30" s="3" t="n">
         <v>17.9</v>
       </c>
-      <c r="K30" s="3" t="n">
+      <c r="K30" s="10" t="n">
         <v>23.7</v>
       </c>
       <c r="L30" s="3" t="n">
@@ -3593,7 +3593,7 @@
       <c r="J37" s="3" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="K37" s="3" t="n">
+      <c r="K37" s="10" t="n">
         <v>17.9</v>
       </c>
       <c r="L37" s="3" t="n">
@@ -4225,7 +4225,7 @@
         <v>8.300000000000001</v>
       </c>
       <c r="J45" s="3" t="n"/>
-      <c r="K45" s="3" t="n"/>
+      <c r="K45" s="14" t="n"/>
       <c r="L45" s="3" t="n"/>
       <c r="M45" s="3" t="n">
         <v>10.6</v>
